--- a/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J347"/>
+  <dimension ref="A1:J354"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1121,13 +1121,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>이미지 자리의 비율</v>
+        <v>거르는 단추 — 필터·정렬·탭이 목록을 실제로 바꾸는지</v>
       </c>
       <c r="G10" t="str">
-        <v>'400×400' 처럼 크기가 적힌 이미지 자리가 실제로 그 비율인지 본다.</v>
+        <v>필터 칩을 눌러 목록이 줄어드는지 세어 본다. 칩에 개수가 적혀 있으면(예: 기본 교육 2) 그 수만큼만 남는지 센다. 정렬도 바꿔 보고, 아무것도 안 남는 조건도 눌러 본다. ⚠ 화면을 «보는» 것으로는 안 잡힌다 — 반드시 눌러서 목록 개수를 세어야 한다.</v>
       </c>
       <c r="H10" t="str">
-        <v>적힌 대로 보인다. 목록 안에서 늘어나 타원이 되지 않는다.</v>
+        <v>색만 바뀌지 않고 «보이는 항목»이 달라진다. 적힌 개수와 실제 개수가 같다. 하나도 안 남으면 「결과가 없습니다」가 나온다.</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>공통 요소가 모든 화면에서 같은지</v>
+        <v>썸네일 · 배너 · 겹쳐 놓은 단추가 정말 눌리는지</v>
       </c>
       <c r="G11" t="str">
-        <v>여러 화면을 오가며 헤더·푸터·버튼 모양이 같은지 본다.</v>
+        <v>카드 썸네일과 배너를 하나씩 눌러 어디로 가는지 본다. 사진 위에 얹은 단추(찜 하트·빠른 담기)는 그 자리에서 `document.elementFromPoint(x, y)` 로 맨 위에 무엇이 있는지 본다. ⚠ 그림이라 눌러 보기를 잊기 쉽다.</v>
       </c>
       <c r="H11" t="str">
-        <v>화면마다 다시 만든 흔적 없이 같은 모습이다.</v>
+        <v>썸네일·배너가 모두 어딘가로 간다. 겹쳐 놓은 단추를 누르면 그 단추가 눌리지, 밑에 깔린 링크로 넘어가지 않는다.</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -1185,13 +1185,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>좁은 화면(모바일)에서 가로 스크롤</v>
+        <v>쪽 번호가 걸러진 결과를 따라가는지</v>
       </c>
       <c r="G12" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>조건을 걸어 목록을 줄인 뒤 쪽 번호를 본다. 3쪽을 보다가 조건을 바꿔 본다.</v>
       </c>
       <c r="H12" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>한 쪽에 다 들어가면 쪽 번호가 사라진다. 조건을 바꾸면 1쪽으로 돌아간다. 쪽을 누르면 목록이 실제로 달라진다.</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -1202,28 +1202,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B13" t="str">
-        <v>홈·탐색</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>상단 GNB(로고·검색·내 공구함·로그인)</v>
+        <v>화면끼리 숫자와 고른 값이 맞는지</v>
       </c>
       <c r="G13" t="str">
-        <v>'홈' 화면에서 상단 GNB(로고·검색·내 공구함·로그인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>수량·옵션·할부·기간을 골라 놓고 다음 화면에서 그대로 있는지 본다. 같은 것이 나오는 화면 둘을 나란히 열어 진도·개수·합계·N/M·남은 것을 대 본다. 「이번 주」·「D-3」은 오늘 날짜로 다시 센다.</v>
       </c>
       <c r="H13" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>앞 화면에서 고른 값이 뒤 화면에 그대로 있다. 같은 값이 화면마다 같다. 합계가 항목의 합과 맞고, 12/18이면 남은 것은 6이다.</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>히어로 배너(오늘의 대표 공구, 달성률·남은시간)</v>
+        <v>가게 정보를 바꿨을 때 옛 이름이 남는 곳</v>
       </c>
       <c r="G14" t="str">
-        <v>'홈'에서 히어로 배너(오늘의 대표 공구, 달성률·남은시간)을 눌러 본다.</v>
+        <v>데이터 파일의 상호를 다른 이름으로 바꾸고 사이트를 다시 연다. 화면·머리말·꼬리말은 물론 브라우저 «탭 제목»까지 본다.</v>
       </c>
       <c r="H14" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>어느 화면에도 옛 이름이 남지 않는다. 탭 제목과 검색 설명까지 새 이름으로 바뀐다.</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -1281,13 +1281,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>마감 임박 공구 가로 스크롤(카운트다운 뱃지)</v>
+        <v>이미지 자리의 비율</v>
       </c>
       <c r="G15" t="str">
-        <v>'홈' 화면에서 마감 임박 공구 가로 스크롤(카운트다운 뱃지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'400×400' 처럼 크기가 적힌 이미지 자리가 실제로 그 비율인지 본다.</v>
       </c>
       <c r="H15" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 대로 보인다. 목록 안에서 늘어나 타원이 되지 않는다.</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -1313,13 +1313,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>카테고리 바로가기</v>
+        <v>공통 요소가 모든 화면에서 같은지</v>
       </c>
       <c r="G16" t="str">
-        <v>'홈'에서 카테고리 바로가기를 눌러 본다.</v>
+        <v>여러 화면을 오가며 헤더·푸터·버튼 모양이 같은지 본다.</v>
       </c>
       <c r="H16" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>화면마다 다시 만든 흔적 없이 같은 모습이다.</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -1345,13 +1345,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)</v>
+        <v>읽기 폭이 한 값인지 — 글이 주인공인 화면들</v>
       </c>
       <c r="G17" t="str">
-        <v>'홈'의 지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>상세 본문·안내·약관처럼 글이 긴 화면 서넛을 나란히 열어, 글줄이 시작하고 끝나는 자리가 같은지 본다.</v>
       </c>
       <c r="H17" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>화면마다 본문 폭이 같다. 어떤 화면은 넓고 어떤 화면은 좁아 서로 다른 사이트처럼 보이지 않는다.</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B18" t="str">
         <v/>
@@ -1377,13 +1377,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>곧 열리는 공구 예고와 알림 신청</v>
+        <v>줄어드는 지점이 두 곳뿐인지</v>
       </c>
       <c r="G18" t="str">
-        <v>'홈' 화면에서 곧 열리는 공구 예고와 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>브라우저 폭을 천천히 줄이며 칸 수가 바뀌는 지점을 세어 본다.</v>
       </c>
       <c r="H18" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>태블릿 가로(1024px)와 세로(720px), 두 곳에서만 바뀐다. 그 사이에 지어낸 지점이 없다.</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -1409,13 +1409,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>진행자 모집 배너</v>
+        <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>'홈'에서 진행자 모집 배너를 눌러 본다.</v>
+        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
       </c>
       <c r="H19" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1429,25 +1429,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>홈·탐색</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F20" t="str">
-        <v>이용 안내 3단계</v>
+        <v>상단 GNB(로고·검색·내 공구함·로그인)</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈' 화면을 열고 이용 안내 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면에서 상단 GNB(로고·검색·내 공구함·로그인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H20" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>하단 앱 다운로드/뉴스레터</v>
+        <v>히어로 배너(오늘의 대표 공구, 달성률·남은시간)</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈' 화면에서 하단 앱 다운로드/뉴스레터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 히어로 배너(오늘의 대표 공구, 달성률·남은시간)을 눌러 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1490,28 +1490,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B22" t="str">
-        <v>홈·탐색</v>
+        <v/>
       </c>
       <c r="C22" t="str">
-        <v>공구 목록</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>카테고리 탭</v>
+        <v>마감 임박 공구 가로 스크롤(카운트다운 뱃지)</v>
       </c>
       <c r="G22" t="str">
-        <v>'공구 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면에서 마감 임박 공구 가로 스크롤(카운트다운 뱃지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H22" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>필터(진행 상태·가격대·배송·마감 임박·달성률)</v>
+        <v>카테고리 바로가기</v>
       </c>
       <c r="G23" t="str">
-        <v>'공구 목록'에서 필터(진행 상태·가격대·배송·마감 임박·달성률)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈'에서 카테고리 바로가기를 눌러 본다.</v>
       </c>
       <c r="H23" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1569,13 +1569,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>정렬(마감 임박·인기·달성률 높은순·할인율·최신)</v>
+        <v>지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)</v>
       </c>
       <c r="G24" t="str">
-        <v>'공구 목록'에서 정렬(마감 임박·인기·달성률 높은순·할인율·최신)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈'의 지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H24" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)</v>
+        <v>곧 열리는 공구 예고와 알림 신청</v>
       </c>
       <c r="G25" t="str">
-        <v>'공구 목록'의 공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈' 화면에서 곧 열리는 공구 예고와 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H25" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -1633,13 +1633,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>무한 스크롤</v>
+        <v>진행자 모집 배너</v>
       </c>
       <c r="G26" t="str">
-        <v>'공구 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 진행자 모집 배너를 눌러 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -1665,13 +1665,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>관심 공구 찜</v>
+        <v>이용 안내 3단계</v>
       </c>
       <c r="G27" t="str">
-        <v>'공구 목록' 화면에서 관심 공구 찜이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 이용 안내 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H27" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -1697,13 +1697,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>검색창</v>
+        <v>하단 앱 다운로드/뉴스레터</v>
       </c>
       <c r="G28" t="str">
-        <v>'공구 목록'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'홈' 화면에서 하단 앱 다운로드/뉴스레터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H28" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1714,28 +1714,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B29" t="str">
         <v>홈·탐색</v>
       </c>
       <c r="C29" t="str">
-        <v>마감 임박 타임딜</v>
+        <v>공구 목록</v>
       </c>
       <c r="D29" t="str">
-        <v>HO-03</v>
+        <v>HO-02</v>
       </c>
       <c r="E29" t="str">
         <v>기본</v>
       </c>
       <c r="F29" t="str">
-        <v>실시간 카운트다운 헤더</v>
+        <v>카테고리 탭</v>
       </c>
       <c r="G29" t="str">
-        <v>'마감 임박 타임딜' 화면에서 실시간 카운트다운 헤더가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H29" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)</v>
+        <v>필터(진행 상태·가격대·배송·마감 임박·달성률)</v>
       </c>
       <c r="G30" t="str">
-        <v>'마감 임박 타임딜'에서 마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'공구 목록'에서 필터(진행 상태·가격대·배송·마감 임박·달성률)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H30" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -1793,13 +1793,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>'앞으로 N명이면 성사' 강조</v>
+        <v>정렬(마감 임박·인기·달성률 높은순·할인율·최신)</v>
       </c>
       <c r="G31" t="str">
-        <v>'마감 임박 타임딜' 화면에서 '앞으로 N명이면 성사' 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록'에서 정렬(마감 임박·인기·달성률 높은순·할인율·최신)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H31" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1825,13 +1825,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>함께 참여 독려 문구</v>
+        <v>공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)</v>
       </c>
       <c r="G32" t="str">
-        <v>'마감 임박 타임딜' 화면에서 함께 참여 독려 문구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록'의 공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H32" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -1857,10 +1857,10 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>놓친 딜 다시 알림 신청</v>
+        <v>무한 스크롤</v>
       </c>
       <c r="G33" t="str">
-        <v>'마감 임박 타임딜' 화면에서 놓친 딜 다시 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H33" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1889,13 +1889,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>필터(오늘 마감·1시간 내 마감)</v>
+        <v>관심 공구 찜</v>
       </c>
       <c r="G34" t="str">
-        <v>'마감 임박 타임딜'에서 필터(오늘 마감·1시간 내 마감)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'공구 목록' 화면에서 관심 공구 찜이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H34" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1906,28 +1906,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SCN-004</v>
+        <v>SCN-002</v>
       </c>
       <c r="B35" t="str">
-        <v>홈·탐색</v>
+        <v/>
       </c>
       <c r="C35" t="str">
-        <v>공구 목록 - 결과 없음</v>
+        <v/>
       </c>
       <c r="D35" t="str">
-        <v>HO-04</v>
+        <v/>
       </c>
       <c r="E35" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F35" t="str">
-        <v>검색어</v>
+        <v>검색창</v>
       </c>
       <c r="G35" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 검색어가 보이는지 확인한다.</v>
+        <v>'공구 목록'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H35" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1938,28 +1938,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>홈·탐색</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>마감 임박 타임딜</v>
       </c>
       <c r="D36" t="str">
-        <v/>
+        <v>HO-03</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F36" t="str">
-        <v>필터 포함 안내 문구</v>
+        <v>실시간 카운트다운 헤더</v>
       </c>
       <c r="G36" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 포함 안내 문구가 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 실시간 카운트다운 헤더가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1985,13 +1985,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>필터 초기화 버튼</v>
+        <v>마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)</v>
       </c>
       <c r="G37" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜'에서 마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H37" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -2017,13 +2017,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>인기 공구 추천 4개</v>
+        <v>'앞으로 N명이면 성사' 강조</v>
       </c>
       <c r="G38" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 인기 공구 추천 4개가 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 '앞으로 N명이면 성사' 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H38" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -2049,13 +2049,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>원하는 상품 공구 요청</v>
+        <v>함께 참여 독려 문구</v>
       </c>
       <c r="G39" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 원하는 상품 공구 요청이 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 함께 참여 독려 문구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H39" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -2081,13 +2081,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>알림 신청</v>
+        <v>놓친 딜 다시 알림 신청</v>
       </c>
       <c r="G40" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 알림 신청이 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 놓친 딜 다시 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H40" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>카테고리 둘러보기 링크</v>
+        <v>필터(오늘 마감·1시간 내 마감)</v>
       </c>
       <c r="G41" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 카테고리 둘러보기 링크가 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜'에서 필터(오늘 마감·1시간 내 마감)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H41" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2130,28 +2130,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B42" t="str">
-        <v>공구 상세</v>
+        <v>홈·탐색</v>
       </c>
       <c r="C42" t="str">
-        <v>공구 상세</v>
+        <v>공구 목록 - 결과 없음</v>
       </c>
       <c r="D42" t="str">
-        <v>DE-01</v>
+        <v>HO-04</v>
       </c>
       <c r="E42" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F42" t="str">
-        <v>상품 이미지 갤러리</v>
+        <v>검색어</v>
       </c>
       <c r="G42" t="str">
-        <v>'공구 상세'의 상품 이미지 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 검색어가 보이는지 확인한다.</v>
       </c>
       <c r="H42" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>달성률 게이지와 목표/현재 인원</v>
+        <v>필터 포함 안내 문구</v>
       </c>
       <c r="G43" t="str">
-        <v>'공구 상세' 화면에서 달성률 게이지와 목표/현재 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 포함 안내 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H43" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>마감 카운트다운</v>
+        <v>필터 초기화 버튼</v>
       </c>
       <c r="G44" t="str">
-        <v>'공구 상세' 화면에서 마감 카운트다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H44" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -2241,13 +2241,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>단계별 가격표(N명 도달 시 추가 할인)</v>
+        <v>인기 공구 추천 4개</v>
       </c>
       <c r="G45" t="str">
-        <v>'공구 상세'의 단계별 가격표(N명 도달 시 추가 할인)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 인기 공구 추천 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H45" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -2273,13 +2273,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>현재 적용가와 정가 대비 할인율</v>
+        <v>원하는 상품 공구 요청</v>
       </c>
       <c r="G46" t="str">
-        <v>'공구 상세' 화면에서 현재 적용가와 정가 대비 할인율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 원하는 상품 공구 요청이 보이는지 확인한다.</v>
       </c>
       <c r="H46" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2305,13 +2305,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>실시간 참여 현황(최근 참여자·증가 애니메이션)</v>
+        <v>알림 신청</v>
       </c>
       <c r="G47" t="str">
-        <v>'공구 상세'의 실시간 참여 현황(최근 참여자·증가 애니메이션)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H47" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -2337,13 +2337,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>옵션 요약</v>
+        <v>카테고리 둘러보기 링크</v>
       </c>
       <c r="G48" t="str">
-        <v>'공구 상세' 화면에서 옵션 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 카테고리 둘러보기 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H48" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2357,25 +2357,25 @@
         <v>SCN-005</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="D49" t="str">
-        <v/>
+        <v>DE-01</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F49" t="str">
-        <v>조건부 결제 안내(미달 시 자동 환불)</v>
+        <v>상품 이미지 갤러리</v>
       </c>
       <c r="G49" t="str">
-        <v>'공구 상세'에서 조건부 결제 안내(미달 시 자동 환불)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 상세'의 상품 이미지 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H49" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2401,10 +2401,10 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>배송</v>
+        <v>달성률 게이지와 목표/현재 인원</v>
       </c>
       <c r="G50" t="str">
-        <v>'공구 상세' 화면에서 배송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 달성률 게이지와 목표/현재 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H50" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>정산 정보</v>
+        <v>마감 카운트다운</v>
       </c>
       <c r="G51" t="str">
-        <v>'공구 상세'에서 정산 정보를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 상세' 화면에서 마감 카운트다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H51" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>진행자 프로필과 신뢰 지표</v>
+        <v>단계별 가격표(N명 도달 시 추가 할인)</v>
       </c>
       <c r="G52" t="str">
-        <v>'공구 상세' 화면에서 진행자 프로필과 신뢰 지표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'의 단계별 가격표(N명 도달 시 추가 할인)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H52" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2497,10 +2497,10 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>후기</v>
+        <v>현재 적용가와 정가 대비 할인율</v>
       </c>
       <c r="G53" t="str">
-        <v>'공구 상세' 화면에서 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 현재 적용가와 정가 대비 할인율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H53" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2529,13 +2529,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>별점</v>
+        <v>실시간 참여 현황(최근 참여자·증가 애니메이션)</v>
       </c>
       <c r="G54" t="str">
-        <v>'공구 상세' 화면에서 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'의 실시간 참여 현황(최근 참여자·증가 애니메이션)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H54" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2561,10 +2561,10 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>상품 문의</v>
+        <v>옵션 요약</v>
       </c>
       <c r="G55" t="str">
-        <v>'공구 상세' 화면에서 상품 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 옵션 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H55" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2593,13 +2593,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>하단 고정 참여 버튼</v>
+        <v>조건부 결제 안내(미달 시 자동 환불)</v>
       </c>
       <c r="G56" t="str">
-        <v>'공구 상세'에서 하단 고정 참여 버튼을 눌러 본다.</v>
+        <v>'공구 상세'에서 조건부 결제 안내(미달 시 자동 환불)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H56" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2610,25 +2610,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B57" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v>상품 상세정보·거래 조건</v>
+        <v/>
       </c>
       <c r="D57" t="str">
-        <v>DE-02</v>
+        <v/>
       </c>
       <c r="E57" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F57" t="str">
-        <v>상품 상세 설명</v>
+        <v>배송</v>
       </c>
       <c r="G57" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 상품 상세 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 배송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H57" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -2657,13 +2657,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>이미지</v>
+        <v>정산 정보</v>
       </c>
       <c r="G58" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'에서 정산 정보를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H58" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -2689,10 +2689,10 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>구성/옵션별 안내</v>
+        <v>진행자 프로필과 신뢰 지표</v>
       </c>
       <c r="G59" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 구성/옵션별 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 진행자 프로필과 신뢰 지표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H59" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -2721,13 +2721,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>배송 정보(성사 후 발송 일정·배송비·지역 제한)</v>
+        <v>후기</v>
       </c>
       <c r="G60" t="str">
-        <v>'상품 상세정보·거래 조건'의 배송 정보(성사 후 발송 일정·배송비·지역 제한)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'공구 상세' 화면에서 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H60" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B61" t="str">
         <v/>
@@ -2753,13 +2753,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)</v>
+        <v>별점</v>
       </c>
       <c r="G61" t="str">
-        <v>'상품 상세정보·거래 조건'에서 조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 상세' 화면에서 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H61" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B62" t="str">
         <v/>
@@ -2785,10 +2785,10 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>교환</v>
+        <v>상품 문의</v>
       </c>
       <c r="G62" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 교환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 상품 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H62" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B63" t="str">
         <v/>
@@ -2817,13 +2817,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>반품 규정</v>
+        <v>하단 고정 참여 버튼</v>
       </c>
       <c r="G63" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 반품 규정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'에서 하단 고정 참여 버튼을 눌러 본다.</v>
       </c>
       <c r="H63" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2837,22 +2837,22 @@
         <v>SCN-006</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>상품 상세정보·거래 조건</v>
       </c>
       <c r="D64" t="str">
-        <v/>
+        <v>DE-02</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F64" t="str">
-        <v>진행자</v>
+        <v>상품 상세 설명</v>
       </c>
       <c r="G64" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 진행자가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 상품 상세 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H64" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2881,13 +2881,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>판매자 사업자 정보</v>
+        <v>이미지</v>
       </c>
       <c r="G65" t="str">
-        <v>'상품 상세정보·거래 조건'의 판매자 사업자 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H65" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2913,10 +2913,10 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>유의사항 아코디언</v>
+        <v>구성/옵션별 안내</v>
       </c>
       <c r="G66" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 유의사항 아코디언이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 구성/옵션별 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H66" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2930,28 +2930,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B67" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>공구 마감 - 성사</v>
+        <v/>
       </c>
       <c r="D67" t="str">
-        <v>DE-03</v>
+        <v/>
       </c>
       <c r="E67" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F67" t="str">
-        <v>성사 축하 배너와 최종 달성 인원</v>
+        <v>배송 정보(성사 후 발송 일정·배송비·지역 제한)</v>
       </c>
       <c r="G67" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 성사 축하 배너와 최종 달성 인원이 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건'의 배송 정보(성사 후 발송 일정·배송비·지역 제한)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H67" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B68" t="str">
         <v/>
@@ -2977,13 +2977,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>적용가</v>
+        <v>조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)</v>
       </c>
       <c r="G68" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 적용가가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건'에서 조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H68" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B69" t="str">
         <v/>
@@ -3009,13 +3009,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>확정된 할인 단계 안내</v>
+        <v>교환</v>
       </c>
       <c r="G69" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 확정된 할인 단계 안내가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 교환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H69" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B70" t="str">
         <v/>
@@ -3041,13 +3041,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>배송 예정 일정</v>
+        <v>반품 규정</v>
       </c>
       <c r="G70" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 배송 예정 일정이 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 반품 규정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H70" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B71" t="str">
         <v/>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>내 참여 확인 유도</v>
+        <v>진행자</v>
       </c>
       <c r="G71" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 내 참여 확인 유도가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 진행자가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H71" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B72" t="str">
         <v/>
@@ -3105,13 +3105,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>후기 예고</v>
+        <v>판매자 사업자 정보</v>
       </c>
       <c r="G72" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 후기 예고가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건'의 판매자 사업자 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H72" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B73" t="str">
         <v/>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>비슷한 진행 중 공구 추천</v>
+        <v>유의사항 아코디언</v>
       </c>
       <c r="G73" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 유의사항 아코디언이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H73" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3157,22 +3157,22 @@
         <v>SCN-007</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>공구 마감 - 성사</v>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>DE-03</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F74" t="str">
-        <v>재오픈 알림 신청</v>
+        <v>성사 축하 배너와 최종 달성 인원</v>
       </c>
       <c r="G74" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 재오픈 알림 신청이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 성사 축하 배너와 최종 달성 인원이 보이는지 확인한다.</v>
       </c>
       <c r="H74" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3186,25 +3186,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B75" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C75" t="str">
-        <v>공구 마감 - 불발(미달)</v>
+        <v/>
       </c>
       <c r="D75" t="str">
-        <v>DE-04</v>
+        <v/>
       </c>
       <c r="E75" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F75" t="str">
-        <v>미달 안내 문구와 최종 인원/목표</v>
+        <v>적용가</v>
       </c>
       <c r="G75" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 미달 안내 문구와 최종 인원/목표가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 적용가가 보이는지 확인한다.</v>
       </c>
       <c r="H75" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B76" t="str">
         <v/>
@@ -3233,10 +3233,10 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>자동 전액 환불 안내와 환불 예정 시점</v>
+        <v>확정된 할인 단계 안내</v>
       </c>
       <c r="G76" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 자동 전액 환불 안내와 환불 예정 시점이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 확정된 할인 단계 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H76" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B77" t="str">
         <v/>
@@ -3265,10 +3265,10 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>환불 진행 상태 표시</v>
+        <v>배송 예정 일정</v>
       </c>
       <c r="G77" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 환불 진행 상태 표시가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 배송 예정 일정이 보이는지 확인한다.</v>
       </c>
       <c r="H77" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B78" t="str">
         <v/>
@@ -3297,10 +3297,10 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>아쉬움 위로 카피</v>
+        <v>내 참여 확인 유도</v>
       </c>
       <c r="G78" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 아쉬움 위로 카피가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 내 참여 확인 유도가 보이는지 확인한다.</v>
       </c>
       <c r="H78" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B79" t="str">
         <v/>
@@ -3329,10 +3329,10 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>재도전(재오픈) 알림 신청</v>
+        <v>후기 예고</v>
       </c>
       <c r="G79" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 재도전(재오픈) 알림 신청이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 후기 예고가 보이는지 확인한다.</v>
       </c>
       <c r="H79" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B80" t="str">
         <v/>
@@ -3364,7 +3364,7 @@
         <v>비슷한 진행 중 공구 추천</v>
       </c>
       <c r="G80" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H80" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B81" t="str">
         <v/>
@@ -3393,10 +3393,10 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>문의 링크</v>
+        <v>재오픈 알림 신청</v>
       </c>
       <c r="G81" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 재오픈 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H81" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3410,28 +3410,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B82" t="str">
-        <v>참여·결제</v>
+        <v>공구 상세</v>
       </c>
       <c r="C82" t="str">
-        <v>옵션·수량 선택</v>
+        <v>공구 마감 - 불발(미달)</v>
       </c>
       <c r="D82" t="str">
-        <v>JO-01</v>
+        <v>DE-04</v>
       </c>
       <c r="E82" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F82" t="str">
-        <v>옵션 조합 선택(색상·용량 등)</v>
+        <v>미달 안내 문구와 최종 인원/목표</v>
       </c>
       <c r="G82" t="str">
-        <v>'옵션·수량 선택' 화면에서 옵션 조합 선택(색상·용량 등)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 미달 안내 문구와 최종 인원/목표가 보이는지 확인한다.</v>
       </c>
       <c r="H82" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B83" t="str">
         <v/>
@@ -3457,13 +3457,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>수량 선택</v>
+        <v>자동 전액 환불 안내와 환불 예정 시점</v>
       </c>
       <c r="G83" t="str">
-        <v>'옵션·수량 선택' 화면에서 수량 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 자동 전액 환불 안내와 환불 예정 시점이 보이는지 확인한다.</v>
       </c>
       <c r="H83" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B84" t="str">
         <v/>
@@ -3489,13 +3489,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>현재 적용 단계 가격 반영</v>
+        <v>환불 진행 상태 표시</v>
       </c>
       <c r="G84" t="str">
-        <v>'옵션·수량 선택'의 현재 적용 단계 가격 반영이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 환불 진행 상태 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H84" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -3521,13 +3521,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>'내 참여로 달성률 얼마나 오르는지' 안내</v>
+        <v>아쉬움 위로 카피</v>
       </c>
       <c r="G85" t="str">
-        <v>'옵션·수량 선택' 화면에서 '내 참여로 달성률 얼마나 오르는지' 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 아쉬움 위로 카피가 보이는지 확인한다.</v>
       </c>
       <c r="H85" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>배송지 확인</v>
+        <v>재도전(재오픈) 알림 신청</v>
       </c>
       <c r="G86" t="str">
-        <v>'옵션·수량 선택' 화면에서 배송지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 재도전(재오픈) 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H86" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>예상 결제 금액</v>
+        <v>비슷한 진행 중 공구 추천</v>
       </c>
       <c r="G87" t="str">
-        <v>'옵션·수량 선택'에서 예상 결제 금액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H87" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B88" t="str">
         <v/>
@@ -3617,13 +3617,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>다음 단계까지 남은 인원 안내</v>
+        <v>문의 링크</v>
       </c>
       <c r="G88" t="str">
-        <v>'옵션·수량 선택'의 다음 단계까지 남은 인원 안내가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H88" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3637,22 +3637,22 @@
         <v>SCN-009</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>참여·결제</v>
       </c>
       <c r="C89" t="str">
-        <v/>
+        <v>옵션·수량 선택</v>
       </c>
       <c r="D89" t="str">
-        <v/>
+        <v>JO-01</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F89" t="str">
-        <v>관심 공구 담기</v>
+        <v>옵션 조합 선택(색상·용량 등)</v>
       </c>
       <c r="G89" t="str">
-        <v>'옵션·수량 선택' 화면에서 관심 공구 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 옵션 조합 선택(색상·용량 등)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H89" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>결제로 이동</v>
+        <v>수량 선택</v>
       </c>
       <c r="G90" t="str">
-        <v>'옵션·수량 선택'에서 결제로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 수량 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H90" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3698,28 +3698,28 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B91" t="str">
-        <v>참여·결제</v>
+        <v/>
       </c>
       <c r="C91" t="str">
-        <v>참여 결제</v>
+        <v/>
       </c>
       <c r="D91" t="str">
-        <v>JO-02</v>
+        <v/>
       </c>
       <c r="E91" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F91" t="str">
-        <v>참여 상품</v>
+        <v>현재 적용 단계 가격 반영</v>
       </c>
       <c r="G91" t="str">
-        <v>'참여 결제' 화면에서 참여 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택'의 현재 적용 단계 가격 반영이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H91" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -3745,10 +3745,10 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>옵션</v>
+        <v>'내 참여로 달성률 얼마나 오르는지' 안내</v>
       </c>
       <c r="G92" t="str">
-        <v>'참여 결제' 화면에서 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 '내 참여로 달성률 얼마나 오르는지' 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H92" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -3777,10 +3777,10 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>수량 요약</v>
+        <v>배송지 확인</v>
       </c>
       <c r="G93" t="str">
-        <v>'참여 결제' 화면에서 수량 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 배송지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H93" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -3809,13 +3809,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>배송지 입력/선택</v>
+        <v>예상 결제 금액</v>
       </c>
       <c r="G94" t="str">
-        <v>'참여 결제'의 배송지 입력/선택에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'옵션·수량 선택'에서 예상 결제 금액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H94" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -3841,13 +3841,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>쿠폰</v>
+        <v>다음 단계까지 남은 인원 안내</v>
       </c>
       <c r="G95" t="str">
-        <v>'참여 결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택'의 다음 단계까지 남은 인원 안내가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H95" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B96" t="str">
         <v/>
@@ -3873,10 +3873,10 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>적립금 적용</v>
+        <v>관심 공구 담기</v>
       </c>
       <c r="G96" t="str">
-        <v>'참여 결제' 화면에서 적립금 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 관심 공구 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H96" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B97" t="str">
         <v/>
@@ -3905,10 +3905,10 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>결제 수단 선택</v>
+        <v>결제로 이동</v>
       </c>
       <c r="G97" t="str">
-        <v>'참여 결제'에서 결제 수단 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'옵션·수량 선택'에서 결제로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H97" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -3925,25 +3925,25 @@
         <v>SCN-010</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>참여·결제</v>
       </c>
       <c r="C98" t="str">
-        <v/>
+        <v>참여 결제</v>
       </c>
       <c r="D98" t="str">
-        <v/>
+        <v>JO-02</v>
       </c>
       <c r="E98" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F98" t="str">
-        <v>조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의</v>
+        <v>참여 상품</v>
       </c>
       <c r="G98" t="str">
-        <v>'참여 결제'에서 조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 결제' 화면에서 참여 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -3969,13 +3969,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>개인정보 제3자 제공(진행자) 동의</v>
+        <v>옵션</v>
       </c>
       <c r="G99" t="str">
-        <v>'참여 결제'의 개인정보 제3자 제공(진행자) 동의가 실제 데이터와 같은지 대조한다.</v>
+        <v>'참여 결제' 화면에서 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H99" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -4001,13 +4001,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>최종 금액과 예상 성사 시 추가할인 안내</v>
+        <v>수량 요약</v>
       </c>
       <c r="G100" t="str">
-        <v>'참여 결제'의 최종 금액과 예상 성사 시 추가할인 안내가 실제 데이터와 같은지 대조한다.</v>
+        <v>'참여 결제' 화면에서 수량 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H100" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4033,13 +4033,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>결제 버튼</v>
+        <v>배송지 입력/선택</v>
       </c>
       <c r="G101" t="str">
-        <v>'참여 결제'에서 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 결제'의 배송지 입력/선택에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H101" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4050,25 +4050,25 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B102" t="str">
-        <v>참여·결제</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>참여 완료</v>
+        <v/>
       </c>
       <c r="D102" t="str">
-        <v>JO-03</v>
+        <v/>
       </c>
       <c r="E102" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F102" t="str">
-        <v>참여 완료 메시지와 참여 번호</v>
+        <v>쿠폰</v>
       </c>
       <c r="G102" t="str">
-        <v>'참여 완료' 화면에서 참여 완료 메시지와 참여 번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H102" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B103" t="str">
         <v/>
@@ -4097,13 +4097,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>갱신된 달성률과 남은 시간</v>
+        <v>적립금 적용</v>
       </c>
       <c r="G103" t="str">
-        <v>'참여 완료'의 갱신된 달성률과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
+        <v>'참여 결제' 화면에서 적립금 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H103" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B104" t="str">
         <v/>
@@ -4129,13 +4129,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>'친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내</v>
+        <v>결제 수단 선택</v>
       </c>
       <c r="G104" t="str">
-        <v>'참여 완료'에서 '친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내를 눌러 본다.</v>
+        <v>'참여 결제'에서 결제 수단 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H104" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B105" t="str">
         <v/>
@@ -4161,13 +4161,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>성사/미달 시 각각 어떻게 되는지 안내</v>
+        <v>조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의</v>
       </c>
       <c r="G105" t="str">
-        <v>'참여 완료' 화면에서 성사/미달 시 각각 어떻게 되는지 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 결제'에서 조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H105" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -4193,13 +4193,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>내 참여 상세로 이동</v>
+        <v>개인정보 제3자 제공(진행자) 동의</v>
       </c>
       <c r="G106" t="str">
-        <v>'참여 완료'에서 내 참여 상세로 이동을 눌러 본다.</v>
+        <v>'참여 결제'의 개인정보 제3자 제공(진행자) 동의가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H106" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -4225,13 +4225,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>다른 공구 추천</v>
+        <v>최종 금액과 예상 성사 시 추가할인 안내</v>
       </c>
       <c r="G107" t="str">
-        <v>'참여 완료' 화면에서 다른 공구 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 결제'의 최종 금액과 예상 성사 시 추가할인 안내가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H107" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4242,28 +4242,28 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SCN-012</v>
+        <v>SCN-010</v>
       </c>
       <c r="B108" t="str">
-        <v>참여·결제</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>결제 실패</v>
+        <v/>
       </c>
       <c r="D108" t="str">
-        <v>JO-04</v>
+        <v/>
       </c>
       <c r="E108" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F108" t="str">
-        <v>실패 사유를 쉬운 문장으로 안내</v>
+        <v>결제 버튼</v>
       </c>
       <c r="G108" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 사유를 쉬운 문장으로 안내가 보이는지 확인한다.</v>
+        <v>'참여 결제'에서 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H108" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4274,28 +4274,28 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>참여·결제</v>
       </c>
       <c r="C109" t="str">
-        <v/>
+        <v>참여 완료</v>
       </c>
       <c r="D109" t="str">
-        <v/>
+        <v>JO-03</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F109" t="str">
-        <v>참여 정보 유지 안내</v>
+        <v>참여 완료 메시지와 참여 번호</v>
       </c>
       <c r="G109" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 참여 정보 유지 안내가 보이는지 확인한다.</v>
+        <v>'참여 완료' 화면에서 참여 완료 메시지와 참여 번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H109" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B110" t="str">
         <v/>
@@ -4321,13 +4321,13 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>다시 시도 버튼</v>
+        <v>갱신된 달성률과 남은 시간</v>
       </c>
       <c r="G110" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
+        <v>'참여 완료'의 갱신된 달성률과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H110" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B111" t="str">
         <v/>
@@ -4353,13 +4353,13 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>다른 결제 수단 선택</v>
+        <v>'친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내</v>
       </c>
       <c r="G111" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 선택이 보이는지 확인한다.</v>
+        <v>'참여 완료'에서 '친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내를 눌러 본다.</v>
       </c>
       <c r="H111" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B112" t="str">
         <v/>
@@ -4385,13 +4385,13 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>마감 임박 시 서두름 안내</v>
+        <v>성사/미달 시 각각 어떻게 되는지 안내</v>
       </c>
       <c r="G112" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 마감 임박 시 서두름 안내가 보이는지 확인한다.</v>
+        <v>'참여 완료' 화면에서 성사/미달 시 각각 어떻게 되는지 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H112" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B113" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>문의 링크</v>
+        <v>내 참여 상세로 이동</v>
       </c>
       <c r="G113" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
+        <v>'참여 완료'에서 내 참여 상세로 이동을 눌러 본다.</v>
       </c>
       <c r="H113" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4434,28 +4434,28 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SCN-013</v>
+        <v>SCN-011</v>
       </c>
       <c r="B114" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="D114" t="str">
-        <v>MY-01</v>
+        <v/>
       </c>
       <c r="E114" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F114" t="str">
-        <v>상태 탭(진행 중·성사·불발·배송/완료)</v>
+        <v>다른 공구 추천</v>
       </c>
       <c r="G114" t="str">
-        <v>'내 공구함'에서 상태 탭(진행 중·성사·불발·배송/완료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'참여 완료' 화면에서 다른 공구 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H114" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4466,28 +4466,28 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>참여·결제</v>
       </c>
       <c r="C115" t="str">
-        <v/>
+        <v>결제 실패</v>
       </c>
       <c r="D115" t="str">
-        <v/>
+        <v>JO-04</v>
       </c>
       <c r="E115" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F115" t="str">
-        <v>참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)</v>
+        <v>실패 사유를 쉬운 문장으로 안내</v>
       </c>
       <c r="G115" t="str">
-        <v>'내 공구함'의 참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 사유를 쉬운 문장으로 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H115" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B116" t="str">
         <v/>
@@ -4513,13 +4513,13 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>진행 중은 달성률</v>
+        <v>참여 정보 유지 안내</v>
       </c>
       <c r="G116" t="str">
-        <v>'내 공구함' 화면에서 진행 중은 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 참여 정보 유지 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H116" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B117" t="str">
         <v/>
@@ -4545,13 +4545,13 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>공유 유도</v>
+        <v>다시 시도 버튼</v>
       </c>
       <c r="G117" t="str">
-        <v>'내 공구함' 화면에서 공유 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H117" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B118" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>불발은 환불 상태</v>
+        <v>다른 결제 수단 선택</v>
       </c>
       <c r="G118" t="str">
-        <v>'내 공구함'에서 불발은 환불 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 선택이 보이는지 확인한다.</v>
       </c>
       <c r="H118" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B119" t="str">
         <v/>
@@ -4609,13 +4609,13 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>배송은 송장</v>
+        <v>마감 임박 시 서두름 안내</v>
       </c>
       <c r="G119" t="str">
-        <v>'내 공구함' 화면에서 배송은 송장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 마감 임박 시 서두름 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H119" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B120" t="str">
         <v/>
@@ -4641,13 +4641,13 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>배송 조회</v>
+        <v>문의 링크</v>
       </c>
       <c r="G120" t="str">
-        <v>'내 공구함' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H120" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4661,25 +4661,25 @@
         <v>SCN-013</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C121" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="D121" t="str">
-        <v/>
+        <v>MY-01</v>
       </c>
       <c r="E121" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F121" t="str">
-        <v>후기 미작성 알림</v>
+        <v>상태 탭(진행 중·성사·불발·배송/완료)</v>
       </c>
       <c r="G121" t="str">
-        <v>'내 공구함'의 후기 미작성 알림에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 공구함'에서 상태 탭(진행 중·성사·불발·배송/완료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H121" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4705,13 +4705,13 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>정렬</v>
+        <v>참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)</v>
       </c>
       <c r="G122" t="str">
-        <v>'내 공구함'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 공구함'의 참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H122" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -4737,13 +4737,13 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>검색</v>
+        <v>진행 중은 달성률</v>
       </c>
       <c r="G123" t="str">
-        <v>'내 공구함'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 공구함' 화면에서 진행 중은 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H123" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4754,25 +4754,25 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B124" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C124" t="str">
-        <v>참여 상세</v>
+        <v/>
       </c>
       <c r="D124" t="str">
-        <v>MY-02</v>
+        <v/>
       </c>
       <c r="E124" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F124" t="str">
-        <v>공구</v>
+        <v>공유 유도</v>
       </c>
       <c r="G124" t="str">
-        <v>'참여 상세' 화면에서 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함' 화면에서 공유 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H124" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B125" t="str">
         <v/>
@@ -4801,13 +4801,13 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>상품 요약</v>
+        <v>불발은 환불 상태</v>
       </c>
       <c r="G125" t="str">
-        <v>'참여 상세' 화면에서 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함'에서 불발은 환불 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H125" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B126" t="str">
         <v/>
@@ -4833,13 +4833,13 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>내 참여 정보(옵션·수량·결제액·참여일)</v>
+        <v>배송은 송장</v>
       </c>
       <c r="G126" t="str">
-        <v>'참여 상세'의 내 참여 정보(옵션·수량·결제액·참여일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 공구함' 화면에서 배송은 송장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H126" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B127" t="str">
         <v/>
@@ -4865,13 +4865,13 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)</v>
+        <v>배송 조회</v>
       </c>
       <c r="G127" t="str">
-        <v>'참여 상세'의 진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 공구함' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H127" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B128" t="str">
         <v/>
@@ -4897,13 +4897,13 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>현재 달성률과 남은 시간(진행 중)</v>
+        <v>후기 미작성 알림</v>
       </c>
       <c r="G128" t="str">
-        <v>'참여 상세'의 현재 달성률과 남은 시간(진행 중)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 공구함'의 후기 미작성 알림에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H128" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B129" t="str">
         <v/>
@@ -4929,13 +4929,13 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>성사 시 차액 환급 내역</v>
+        <v>정렬</v>
       </c>
       <c r="G129" t="str">
-        <v>'참여 상세' 화면에서 성사 시 차액 환급 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H129" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -4961,13 +4961,13 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>배송 조회</v>
+        <v>검색</v>
       </c>
       <c r="G130" t="str">
-        <v>'참여 상세' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H130" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -4981,25 +4981,25 @@
         <v>SCN-014</v>
       </c>
       <c r="B131" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C131" t="str">
-        <v/>
+        <v>참여 상세</v>
       </c>
       <c r="D131" t="str">
-        <v/>
+        <v>MY-02</v>
       </c>
       <c r="E131" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F131" t="str">
-        <v>취소</v>
+        <v>공구</v>
       </c>
       <c r="G131" t="str">
-        <v>'참여 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H131" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -5025,13 +5025,13 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>환불 요청</v>
+        <v>상품 요약</v>
       </c>
       <c r="G132" t="str">
-        <v>'참여 상세'에서 환불 요청을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H132" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -5057,13 +5057,13 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>영수증</v>
+        <v>내 참여 정보(옵션·수량·결제액·참여일)</v>
       </c>
       <c r="G133" t="str">
-        <v>'참여 상세' 화면에서 영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세'의 내 참여 정보(옵션·수량·결제액·참여일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H133" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -5089,13 +5089,13 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>문의</v>
+        <v>진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)</v>
       </c>
       <c r="G134" t="str">
-        <v>'참여 상세' 화면에서 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세'의 진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H134" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -5106,28 +5106,28 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B135" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C135" t="str">
-        <v>참여 취소·환불 요청</v>
+        <v/>
       </c>
       <c r="D135" t="str">
-        <v>MY-03</v>
+        <v/>
       </c>
       <c r="E135" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F135" t="str">
-        <v>취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)</v>
+        <v>현재 달성률과 남은 시간(진행 중)</v>
       </c>
       <c r="G135" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세'의 현재 달성률과 남은 시간(진행 중)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H135" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B136" t="str">
         <v/>
@@ -5153,13 +5153,13 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>취소 시 달성률 영향 안내</v>
+        <v>성사 시 차액 환급 내역</v>
       </c>
       <c r="G136" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 시 달성률 영향 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 성사 시 차액 환급 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H136" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B137" t="str">
         <v/>
@@ -5185,13 +5185,13 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>취소 사유 선택</v>
+        <v>배송 조회</v>
       </c>
       <c r="G137" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H137" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B138" t="str">
         <v/>
@@ -5217,10 +5217,10 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>환불 예정 금액과 수단</v>
+        <v>취소</v>
       </c>
       <c r="G138" t="str">
-        <v>'참여 취소·환불 요청'에서 환불 예정 금액과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H138" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B139" t="str">
         <v/>
@@ -5249,13 +5249,13 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>시점</v>
+        <v>환불 요청</v>
       </c>
       <c r="G139" t="str">
-        <v>'참여 취소·환불 요청' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세'에서 환불 요청을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H139" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B140" t="str">
         <v/>
@@ -5281,10 +5281,10 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>성사 후 반품은 배송 규정 안내</v>
+        <v>영수증</v>
       </c>
       <c r="G140" t="str">
-        <v>'참여 취소·환불 요청' 화면에서 성사 후 반품은 배송 규정 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세' 화면에서 영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H140" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B141" t="str">
         <v/>
@@ -5313,13 +5313,13 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>취소 확정 버튼(확인 모달)</v>
+        <v>문의</v>
       </c>
       <c r="G141" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 확정 버튼(확인 모달)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H141" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5333,22 +5333,22 @@
         <v>SCN-015</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C142" t="str">
-        <v/>
+        <v>참여 취소·환불 요청</v>
       </c>
       <c r="D142" t="str">
-        <v/>
+        <v>MY-03</v>
       </c>
       <c r="E142" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F142" t="str">
-        <v>취소 대신 유지 유도</v>
+        <v>취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)</v>
       </c>
       <c r="G142" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 대신 유지 유도를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H142" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -5362,28 +5362,28 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B143" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C143" t="str">
-        <v>내 공구함 - 비어 있음</v>
+        <v/>
       </c>
       <c r="D143" t="str">
-        <v>MY-04</v>
+        <v/>
       </c>
       <c r="E143" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F143" t="str">
-        <v>참여 내역 없음 안내와 일러스트</v>
+        <v>취소 시 달성률 영향 안내</v>
       </c>
       <c r="G143" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 참여 내역 없음 안내와 일러스트가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 시 달성률 영향 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H143" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B144" t="str">
         <v/>
@@ -5409,13 +5409,13 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>공구 둘러보기 CTA</v>
+        <v>취소 사유 선택</v>
       </c>
       <c r="G144" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 공구 둘러보기 CTA가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H144" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B145" t="str">
         <v/>
@@ -5441,13 +5441,13 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>첫 참여 할인 쿠폰 안내</v>
+        <v>환불 예정 금액과 수단</v>
       </c>
       <c r="G145" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 첫 참여 할인 쿠폰 안내가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 환불 예정 금액과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H145" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -5473,13 +5473,13 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>인기</v>
+        <v>시점</v>
       </c>
       <c r="G146" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 인기가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H146" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -5505,13 +5505,13 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>마감 임박 공구 추천</v>
+        <v>성사 후 반품은 배송 규정 안내</v>
       </c>
       <c r="G147" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 마감 임박 공구 추천이 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청' 화면에서 성사 후 반품은 배송 규정 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H147" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -5537,13 +5537,13 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>관심 공구로 이동</v>
+        <v>취소 확정 버튼(확인 모달)</v>
       </c>
       <c r="G148" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 관심 공구로 이동이 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 확정 버튼(확인 모달)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H148" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5554,28 +5554,28 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SCN-017</v>
+        <v>SCN-015</v>
       </c>
       <c r="B149" t="str">
-        <v>후기·문의·알림</v>
+        <v/>
       </c>
       <c r="C149" t="str">
-        <v>후기 작성·목록</v>
+        <v/>
       </c>
       <c r="D149" t="str">
-        <v>RV-01</v>
+        <v/>
       </c>
       <c r="E149" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F149" t="str">
-        <v>별점 선택</v>
+        <v>취소 대신 유지 유도</v>
       </c>
       <c r="G149" t="str">
-        <v>'후기 작성·목록' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 대신 유지 유도를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H149" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -5586,28 +5586,28 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B150" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C150" t="str">
-        <v/>
+        <v>내 공구함 - 비어 있음</v>
       </c>
       <c r="D150" t="str">
-        <v/>
+        <v>MY-04</v>
       </c>
       <c r="E150" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F150" t="str">
-        <v>포토</v>
+        <v>참여 내역 없음 안내와 일러스트</v>
       </c>
       <c r="G150" t="str">
-        <v>'후기 작성·목록' 화면에서 포토가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 참여 내역 없음 안내와 일러스트가 보이는지 확인한다.</v>
       </c>
       <c r="H150" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -5633,13 +5633,13 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>동영상 첨부</v>
+        <v>공구 둘러보기 CTA</v>
       </c>
       <c r="G151" t="str">
-        <v>'후기 작성·목록'의 동영상 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 공구 둘러보기 CTA가 보이는지 확인한다.</v>
       </c>
       <c r="H151" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -5665,13 +5665,13 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>옵션 선택 정보 자동 표시</v>
+        <v>첫 참여 할인 쿠폰 안내</v>
       </c>
       <c r="G152" t="str">
-        <v>'후기 작성·목록'의 옵션 선택 정보 자동 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 첫 참여 할인 쿠폰 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H152" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -5697,13 +5697,13 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>후기 본문</v>
+        <v>인기</v>
       </c>
       <c r="G153" t="str">
-        <v>'후기 작성·목록' 화면에서 후기 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 인기가 보이는지 확인한다.</v>
       </c>
       <c r="H153" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -5729,13 +5729,13 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>재구매 의사</v>
+        <v>마감 임박 공구 추천</v>
       </c>
       <c r="G154" t="str">
-        <v>'후기 작성·목록' 화면에서 재구매 의사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 마감 임박 공구 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H154" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -5761,13 +5761,13 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>도움돼요 추천</v>
+        <v>관심 공구로 이동</v>
       </c>
       <c r="G155" t="str">
-        <v>'후기 작성·목록' 화면에서 도움돼요 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 관심 공구로 이동이 보이는지 확인한다.</v>
       </c>
       <c r="H155" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -5781,25 +5781,25 @@
         <v>SCN-017</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>후기·문의·알림</v>
       </c>
       <c r="C156" t="str">
-        <v/>
+        <v>후기 작성·목록</v>
       </c>
       <c r="D156" t="str">
-        <v/>
+        <v>RV-01</v>
       </c>
       <c r="E156" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F156" t="str">
-        <v>후기 목록(별점 분포·정렬·포토후기 필터)</v>
+        <v>별점 선택</v>
       </c>
       <c r="G156" t="str">
-        <v>'후기 작성·목록'의 후기 목록(별점 분포·정렬·포토후기 필터)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H156" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -5825,10 +5825,10 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>진행자 답글</v>
+        <v>포토</v>
       </c>
       <c r="G157" t="str">
-        <v>'후기 작성·목록' 화면에서 진행자 답글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 포토가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H157" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5857,13 +5857,13 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>신고</v>
+        <v>동영상 첨부</v>
       </c>
       <c r="G158" t="str">
-        <v>'후기 작성·목록' 화면에서 신고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록'의 동영상 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H158" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -5889,13 +5889,13 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>후기 작성 보상 안내</v>
+        <v>옵션 선택 정보 자동 표시</v>
       </c>
       <c r="G159" t="str">
-        <v>'후기 작성·목록'의 후기 작성 보상 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 작성·목록'의 옵션 선택 정보 자동 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H159" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -5906,28 +5906,28 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B160" t="str">
-        <v>후기·문의·알림</v>
+        <v/>
       </c>
       <c r="C160" t="str">
-        <v>상품 문의(Q&amp;A)</v>
+        <v/>
       </c>
       <c r="D160" t="str">
-        <v>RV-02</v>
+        <v/>
       </c>
       <c r="E160" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F160" t="str">
-        <v>문의 작성(유형 선택·비공개 옵션)</v>
+        <v>후기 본문</v>
       </c>
       <c r="G160" t="str">
-        <v>'상품 문의(Q&amp;A)'의 문의 작성(유형 선택·비공개 옵션)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 작성·목록' 화면에서 후기 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H160" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>문의 목록(질문·답변·상태 배지)</v>
+        <v>재구매 의사</v>
       </c>
       <c r="G161" t="str">
-        <v>'상품 문의(Q&amp;A)'의 문의 목록(질문·답변·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 재구매 의사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H161" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -5985,10 +5985,10 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>자주 묻는 질문 상단 노출</v>
+        <v>도움돼요 추천</v>
       </c>
       <c r="G162" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 자주 묻는 질문 상단 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 도움돼요 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H162" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B163" t="str">
         <v/>
@@ -6017,13 +6017,13 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>답변 알림 안내</v>
+        <v>후기 목록(별점 분포·정렬·포토후기 필터)</v>
       </c>
       <c r="G163" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 답변 알림 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록'의 후기 목록(별점 분포·정렬·포토후기 필터)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H163" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B164" t="str">
         <v/>
@@ -6049,13 +6049,13 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>검색</v>
+        <v>진행자 답글</v>
       </c>
       <c r="G164" t="str">
-        <v>'상품 문의(Q&amp;A)'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 작성·목록' 화면에서 진행자 답글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H164" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B165" t="str">
         <v/>
@@ -6081,13 +6081,13 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>진행자 답변 대기 표시</v>
+        <v>신고</v>
       </c>
       <c r="G165" t="str">
-        <v>'상품 문의(Q&amp;A)'의 진행자 답변 대기 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'후기 작성·목록' 화면에서 신고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H165" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B166" t="str">
         <v/>
@@ -6113,13 +6113,13 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>성사</v>
+        <v>후기 작성 보상 안내</v>
       </c>
       <c r="G166" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 성사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록'의 후기 작성 보상 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H166" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -6133,25 +6133,25 @@
         <v>SCN-018</v>
       </c>
       <c r="B167" t="str">
-        <v/>
+        <v>후기·문의·알림</v>
       </c>
       <c r="C167" t="str">
-        <v/>
+        <v>상품 문의(Q&amp;A)</v>
       </c>
       <c r="D167" t="str">
-        <v/>
+        <v>RV-02</v>
       </c>
       <c r="E167" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F167" t="str">
-        <v>배송 관련 문의 분류</v>
+        <v>문의 작성(유형 선택·비공개 옵션)</v>
       </c>
       <c r="G167" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 배송 관련 문의 분류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'의 문의 작성(유형 선택·비공개 옵션)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H167" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -6162,25 +6162,25 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B168" t="str">
-        <v>후기·문의·알림</v>
+        <v/>
       </c>
       <c r="C168" t="str">
-        <v>관심 공구·알림함</v>
+        <v/>
       </c>
       <c r="D168" t="str">
-        <v>RV-03</v>
+        <v/>
       </c>
       <c r="E168" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F168" t="str">
-        <v>찜한 공구 목록(달성률·남은 시간·상태 변화 표시)</v>
+        <v>문의 목록(질문·답변·상태 배지)</v>
       </c>
       <c r="G168" t="str">
-        <v>'관심 공구·알림함'의 찜한 공구 목록(달성률·남은 시간·상태 변화 표시)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'의 문의 목록(질문·답변·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H168" t="str">
         <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>오픈 예정 공구 알림 신청 목록</v>
+        <v>자주 묻는 질문 상단 노출</v>
       </c>
       <c r="G169" t="str">
-        <v>'관심 공구·알림함'의 오픈 예정 공구 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 자주 묻는 질문 상단 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H169" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B170" t="str">
         <v/>
@@ -6241,10 +6241,10 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>알림 내역(성사·마감 임박·재오픈·배송)</v>
+        <v>답변 알림 안내</v>
       </c>
       <c r="G170" t="str">
-        <v>'관심 공구·알림함' 화면에서 알림 내역(성사·마감 임박·재오픈·배송)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 답변 알림 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H170" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B171" t="str">
         <v/>
@@ -6273,13 +6273,13 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>읽음 처리</v>
+        <v>검색</v>
       </c>
       <c r="G171" t="str">
-        <v>'관심 공구·알림함' 화면에서 읽음 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H171" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B172" t="str">
         <v/>
@@ -6305,13 +6305,13 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>관심 공구에서 바로 참여</v>
+        <v>진행자 답변 대기 표시</v>
       </c>
       <c r="G172" t="str">
-        <v>'관심 공구·알림함' 화면에서 관심 공구에서 바로 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'의 진행자 답변 대기 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H172" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B173" t="str">
         <v/>
@@ -6337,13 +6337,13 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>알림 설정 링크</v>
+        <v>성사</v>
       </c>
       <c r="G173" t="str">
-        <v>'관심 공구·알림함'에서 알림 설정 링크를 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 성사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H173" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -6354,28 +6354,28 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SCN-020</v>
+        <v>SCN-018</v>
       </c>
       <c r="B174" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C174" t="str">
-        <v>로그인·회원가입</v>
+        <v/>
       </c>
       <c r="D174" t="str">
-        <v>AC-01</v>
+        <v/>
       </c>
       <c r="E174" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F174" t="str">
-        <v>소셜 로그인(카카오·네이버·구글)</v>
+        <v>배송 관련 문의 분류</v>
       </c>
       <c r="G174" t="str">
-        <v>'로그인·회원가입'에서 소셜 로그인(카카오·네이버·구글)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 배송 관련 문의 분류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H174" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -6386,28 +6386,28 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B175" t="str">
-        <v/>
+        <v>후기·문의·알림</v>
       </c>
       <c r="C175" t="str">
-        <v/>
+        <v>관심 공구·알림함</v>
       </c>
       <c r="D175" t="str">
-        <v/>
+        <v>RV-03</v>
       </c>
       <c r="E175" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F175" t="str">
-        <v>이메일 로그인</v>
+        <v>찜한 공구 목록(달성률·남은 시간·상태 변화 표시)</v>
       </c>
       <c r="G175" t="str">
-        <v>'로그인·회원가입'에서 이메일 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'관심 공구·알림함'의 찜한 공구 목록(달성률·남은 시간·상태 변화 표시)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -6433,13 +6433,13 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>회원가입 전환</v>
+        <v>오픈 예정 공구 알림 신청 목록</v>
       </c>
       <c r="G176" t="str">
-        <v>'로그인·회원가입'에서 회원가입 전환을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'관심 공구·알림함'의 오픈 예정 공구 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -6465,10 +6465,10 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>휴대폰 인증</v>
+        <v>알림 내역(성사·마감 임박·재오픈·배송)</v>
       </c>
       <c r="G177" t="str">
-        <v>'로그인·회원가입' 화면에서 휴대폰 인증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'관심 공구·알림함' 화면에서 알림 내역(성사·마감 임박·재오픈·배송)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H177" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B178" t="str">
         <v/>
@@ -6497,10 +6497,10 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>약관</v>
+        <v>읽음 처리</v>
       </c>
       <c r="G178" t="str">
-        <v>'로그인·회원가입' 화면에서 약관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'관심 공구·알림함' 화면에서 읽음 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H178" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6514,7 +6514,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B179" t="str">
         <v/>
@@ -6529,13 +6529,13 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>개인정보</v>
+        <v>관심 공구에서 바로 참여</v>
       </c>
       <c r="G179" t="str">
-        <v>'로그인·회원가입'의 개인정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'관심 공구·알림함' 화면에서 관심 공구에서 바로 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H179" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B180" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>마케팅 수신 동의</v>
+        <v>알림 설정 링크</v>
       </c>
       <c r="G180" t="str">
-        <v>'로그인·회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'관심 공구·알림함'에서 알림 설정 링크를 눌러 본다.</v>
       </c>
       <c r="H180" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -6581,25 +6581,25 @@
         <v>SCN-020</v>
       </c>
       <c r="B181" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C181" t="str">
-        <v/>
+        <v>로그인·회원가입</v>
       </c>
       <c r="D181" t="str">
-        <v/>
+        <v>AC-01</v>
       </c>
       <c r="E181" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F181" t="str">
-        <v>첫 가입 쿠폰 안내</v>
+        <v>소셜 로그인(카카오·네이버·구글)</v>
       </c>
       <c r="G181" t="str">
-        <v>'로그인·회원가입' 화면에서 첫 가입 쿠폰 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'에서 소셜 로그인(카카오·네이버·구글)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H181" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6625,13 +6625,13 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>비회원 주문 조회</v>
+        <v>이메일 로그인</v>
       </c>
       <c r="G182" t="str">
-        <v>'로그인·회원가입' 화면에서 비회원 주문 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'에서 이메일 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H182" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -6657,13 +6657,13 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>비밀번호 찾기</v>
+        <v>회원가입 전환</v>
       </c>
       <c r="G183" t="str">
-        <v>'로그인·회원가입' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'에서 회원가입 전환을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H183" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,25 +6674,25 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B184" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C184" t="str">
-        <v>내 정보·배송지</v>
+        <v/>
       </c>
       <c r="D184" t="str">
-        <v>AC-02</v>
+        <v/>
       </c>
       <c r="E184" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F184" t="str">
-        <v>프로필(닉네임·프로필 사진)</v>
+        <v>휴대폰 인증</v>
       </c>
       <c r="G184" t="str">
-        <v>'내 정보·배송지' 화면에서 프로필(닉네임·프로필 사진)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 휴대폰 인증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H184" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,10 +6721,10 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>휴대폰</v>
+        <v>약관</v>
       </c>
       <c r="G185" t="str">
-        <v>'내 정보·배송지' 화면에서 휴대폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 약관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H185" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B186" t="str">
         <v/>
@@ -6753,13 +6753,13 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>이메일</v>
+        <v>개인정보</v>
       </c>
       <c r="G186" t="str">
-        <v>'내 정보·배송지' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'의 개인정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H186" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B187" t="str">
         <v/>
@@ -6785,13 +6785,13 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)</v>
+        <v>마케팅 수신 동의</v>
       </c>
       <c r="G187" t="str">
-        <v>'내 정보·배송지'의 배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H187" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B188" t="str">
         <v/>
@@ -6817,13 +6817,13 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>결제 수단 관리</v>
+        <v>첫 가입 쿠폰 안내</v>
       </c>
       <c r="G188" t="str">
-        <v>'내 정보·배송지'에서 결제 수단 관리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'로그인·회원가입' 화면에서 첫 가입 쿠폰 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H188" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B189" t="str">
         <v/>
@@ -6849,10 +6849,10 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>쿠폰</v>
+        <v>비회원 주문 조회</v>
       </c>
       <c r="G189" t="str">
-        <v>'내 정보·배송지' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 비회원 주문 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H189" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6866,7 +6866,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B190" t="str">
         <v/>
@@ -6881,10 +6881,10 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>적립금 잔액</v>
+        <v>비밀번호 찾기</v>
       </c>
       <c r="G190" t="str">
-        <v>'내 정보·배송지' 화면에서 적립금 잔액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H190" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6901,22 +6901,22 @@
         <v>SCN-021</v>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C191" t="str">
-        <v/>
+        <v>내 정보·배송지</v>
       </c>
       <c r="D191" t="str">
-        <v/>
+        <v>AC-02</v>
       </c>
       <c r="E191" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F191" t="str">
-        <v>참여</v>
+        <v>프로필(닉네임·프로필 사진)</v>
       </c>
       <c r="G191" t="str">
-        <v>'내 정보·배송지' 화면에서 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 프로필(닉네임·프로필 사진)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H191" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6945,13 +6945,13 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>후기 통계</v>
+        <v>휴대폰</v>
       </c>
       <c r="G192" t="str">
-        <v>'내 정보·배송지'의 후기 통계가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 정보·배송지' 화면에서 휴대폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H192" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -6977,10 +6977,10 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>진행자 전환/진행자 페이지 진입</v>
+        <v>이메일</v>
       </c>
       <c r="G193" t="str">
-        <v>'내 정보·배송지' 화면에서 진행자 전환/진행자 페이지 진입이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H193" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7009,13 +7009,13 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>회원 탈퇴 안내</v>
+        <v>배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)</v>
       </c>
       <c r="G194" t="str">
-        <v>'내 정보·배송지' 화면에서 회원 탈퇴 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지'의 배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H194" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7026,28 +7026,28 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B195" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C195" t="str">
-        <v>알림 설정</v>
+        <v/>
       </c>
       <c r="D195" t="str">
-        <v>AC-03</v>
+        <v/>
       </c>
       <c r="E195" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F195" t="str">
-        <v>알림 채널(앱 푸시·카카오·문자·이메일) 토글</v>
+        <v>결제 수단 관리</v>
       </c>
       <c r="G195" t="str">
-        <v>'알림 설정' 화면에서 알림 채널(앱 푸시·카카오·문자·이메일) 토글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지'에서 결제 수단 관리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H195" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -7058,7 +7058,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B196" t="str">
         <v/>
@@ -7073,10 +7073,10 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)</v>
+        <v>쿠폰</v>
       </c>
       <c r="G196" t="str">
-        <v>'알림 설정' 화면에서 알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H196" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7090,7 +7090,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B197" t="str">
         <v/>
@@ -7105,10 +7105,10 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>야간 방해금지 시간</v>
+        <v>적립금 잔액</v>
       </c>
       <c r="G197" t="str">
-        <v>'알림 설정' 화면에서 야간 방해금지 시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 적립금 잔액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H197" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B198" t="str">
         <v/>
@@ -7137,10 +7137,10 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>마케팅 수신 동의와 철회</v>
+        <v>참여</v>
       </c>
       <c r="G198" t="str">
-        <v>'알림 설정' 화면에서 마케팅 수신 동의와 철회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H198" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B199" t="str">
         <v/>
@@ -7169,13 +7169,13 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>관심 카테고리 알림</v>
+        <v>후기 통계</v>
       </c>
       <c r="G199" t="str">
-        <v>'알림 설정' 화면에서 관심 카테고리 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지'의 후기 통계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H199" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B200" t="str">
         <v/>
@@ -7201,10 +7201,10 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>저장</v>
+        <v>진행자 전환/진행자 페이지 진입</v>
       </c>
       <c r="G200" t="str">
-        <v>'알림 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 진행자 전환/진행자 페이지 진입이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H200" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7218,25 +7218,25 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SCN-023</v>
+        <v>SCN-021</v>
       </c>
       <c r="B201" t="str">
-        <v>공구 개설(진행자)</v>
+        <v/>
       </c>
       <c r="C201" t="str">
-        <v>진행자 시작 안내</v>
+        <v/>
       </c>
       <c r="D201" t="str">
-        <v>HS-01</v>
+        <v/>
       </c>
       <c r="E201" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F201" t="str">
-        <v>공구 진행자가 하는 일 소개</v>
+        <v>회원 탈퇴 안내</v>
       </c>
       <c r="G201" t="str">
-        <v>'진행자 시작 안내' 화면에서 공구 진행자가 하는 일 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 회원 탈퇴 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H201" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7250,25 +7250,25 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C202" t="str">
-        <v/>
+        <v>알림 설정</v>
       </c>
       <c r="D202" t="str">
-        <v/>
+        <v>AC-03</v>
       </c>
       <c r="E202" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F202" t="str">
-        <v>수익 구조와 수수료 안내</v>
+        <v>알림 채널(앱 푸시·카카오·문자·이메일) 토글</v>
       </c>
       <c r="G202" t="str">
-        <v>'진행자 시작 안내' 화면에서 수익 구조와 수수료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 알림 채널(앱 푸시·카카오·문자·이메일) 토글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H202" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B203" t="str">
         <v/>
@@ -7297,13 +7297,13 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>정산 방식</v>
+        <v>알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)</v>
       </c>
       <c r="G203" t="str">
-        <v>'진행자 시작 안내'에서 정산 방식을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'알림 설정' 화면에서 알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H203" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I203" t="str">
         <v/>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -7329,10 +7329,10 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>시점</v>
+        <v>야간 방해금지 시간</v>
       </c>
       <c r="G204" t="str">
-        <v>'진행자 시작 안내' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 야간 방해금지 시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B205" t="str">
         <v/>
@@ -7361,10 +7361,10 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>성공 사례와 팁</v>
+        <v>마케팅 수신 동의와 철회</v>
       </c>
       <c r="G205" t="str">
-        <v>'진행자 시작 안내' 화면에서 성공 사례와 팁이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 마케팅 수신 동의와 철회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H205" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B206" t="str">
         <v/>
@@ -7393,10 +7393,10 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>필요한 준비물(상품·공급처·사업자 여부)</v>
+        <v>관심 카테고리 알림</v>
       </c>
       <c r="G206" t="str">
-        <v>'진행자 시작 안내' 화면에서 필요한 준비물(상품·공급처·사업자 여부)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 관심 카테고리 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H206" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B207" t="str">
         <v/>
@@ -7425,10 +7425,10 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>자격 요건과 신뢰 등급</v>
+        <v>저장</v>
       </c>
       <c r="G207" t="str">
-        <v>'진행자 시작 안내' 화면에서 자격 요건과 신뢰 등급이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H207" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7445,25 +7445,25 @@
         <v>SCN-023</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>공구 개설(진행자)</v>
       </c>
       <c r="C208" t="str">
-        <v/>
+        <v>진행자 시작 안내</v>
       </c>
       <c r="D208" t="str">
-        <v/>
+        <v>HS-01</v>
       </c>
       <c r="E208" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F208" t="str">
-        <v>시작하기 CTA</v>
+        <v>공구 진행자가 하는 일 소개</v>
       </c>
       <c r="G208" t="str">
-        <v>'진행자 시작 안내'에서 시작하기 CTA를 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 공구 진행자가 하는 일 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H208" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7489,10 +7489,10 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>자주 묻는 질문</v>
+        <v>수익 구조와 수수료 안내</v>
       </c>
       <c r="G209" t="str">
-        <v>'진행자 시작 안내' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 수익 구조와 수수료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H209" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7506,28 +7506,28 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B210" t="str">
-        <v>공구 개설(진행자)</v>
+        <v/>
       </c>
       <c r="C210" t="str">
-        <v>공구 개설 폼</v>
+        <v/>
       </c>
       <c r="D210" t="str">
-        <v>HS-02</v>
+        <v/>
       </c>
       <c r="E210" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F210" t="str">
-        <v>상품명</v>
+        <v>정산 방식</v>
       </c>
       <c r="G210" t="str">
-        <v>'공구 개설 폼' 화면에서 상품명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내'에서 정산 방식을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H210" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B211" t="str">
         <v/>
@@ -7553,10 +7553,10 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>카테고리</v>
+        <v>시점</v>
       </c>
       <c r="G211" t="str">
-        <v>'공구 개설 폼' 화면에서 카테고리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H211" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B212" t="str">
         <v/>
@@ -7585,13 +7585,13 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>이미지 업로드</v>
+        <v>성공 사례와 팁</v>
       </c>
       <c r="G212" t="str">
-        <v>'공구 개설 폼'의 이미지 업로드에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 성공 사례와 팁이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H212" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B213" t="str">
         <v/>
@@ -7617,10 +7617,10 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>상세 설명 에디터</v>
+        <v>필요한 준비물(상품·공급처·사업자 여부)</v>
       </c>
       <c r="G213" t="str">
-        <v>'공구 개설 폼' 화면에서 상세 설명 에디터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 필요한 준비물(상품·공급처·사업자 여부)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H213" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B214" t="str">
         <v/>
@@ -7649,13 +7649,13 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>정가와 단계별 가격 설정(인원 구간별 할인가)</v>
+        <v>자격 요건과 신뢰 등급</v>
       </c>
       <c r="G214" t="str">
-        <v>'공구 개설 폼'의 정가와 단계별 가격 설정(인원 구간별 할인가)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'진행자 시작 안내' 화면에서 자격 요건과 신뢰 등급이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H214" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B215" t="str">
         <v/>
@@ -7681,13 +7681,13 @@
         <v/>
       </c>
       <c r="F215" t="str">
-        <v>목표 인원</v>
+        <v>시작하기 CTA</v>
       </c>
       <c r="G215" t="str">
-        <v>'공구 개설 폼' 화면에서 목표 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내'에서 시작하기 CTA를 눌러 본다.</v>
       </c>
       <c r="H215" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7698,7 +7698,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B216" t="str">
         <v/>
@@ -7713,10 +7713,10 @@
         <v/>
       </c>
       <c r="F216" t="str">
-        <v>최소 성사 조건</v>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="G216" t="str">
-        <v>'공구 개설 폼' 화면에서 최소 성사 조건이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H216" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7733,22 +7733,22 @@
         <v>SCN-024</v>
       </c>
       <c r="B217" t="str">
-        <v/>
+        <v>공구 개설(진행자)</v>
       </c>
       <c r="C217" t="str">
-        <v/>
+        <v>공구 개설 폼</v>
       </c>
       <c r="D217" t="str">
-        <v/>
+        <v>HS-02</v>
       </c>
       <c r="E217" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F217" t="str">
-        <v>모집 기간(시작·마감일시)</v>
+        <v>상품명</v>
       </c>
       <c r="G217" t="str">
-        <v>'공구 개설 폼' 화면에서 모집 기간(시작·마감일시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 상품명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H217" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7777,10 +7777,10 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>1인 최대 수량</v>
+        <v>카테고리</v>
       </c>
       <c r="G218" t="str">
-        <v>'공구 개설 폼' 화면에서 1인 최대 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 카테고리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H218" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7809,13 +7809,13 @@
         <v/>
       </c>
       <c r="F219" t="str">
-        <v>총 수량 한도</v>
+        <v>이미지 업로드</v>
       </c>
       <c r="G219" t="str">
-        <v>'공구 개설 폼' 화면에서 총 수량 한도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼'의 이미지 업로드에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H219" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -7841,10 +7841,10 @@
         <v/>
       </c>
       <c r="F220" t="str">
-        <v>옵션 관리</v>
+        <v>상세 설명 에디터</v>
       </c>
       <c r="G220" t="str">
-        <v>'공구 개설 폼' 화면에서 옵션 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 상세 설명 에디터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H220" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7873,13 +7873,13 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v>배송비</v>
+        <v>정가와 단계별 가격 설정(인원 구간별 할인가)</v>
       </c>
       <c r="G221" t="str">
-        <v>'공구 개설 폼' 화면에서 배송비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼'의 정가와 단계별 가격 설정(인원 구간별 할인가)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H221" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -7905,10 +7905,10 @@
         <v/>
       </c>
       <c r="F222" t="str">
-        <v>발송 일정</v>
+        <v>목표 인원</v>
       </c>
       <c r="G222" t="str">
-        <v>'공구 개설 폼' 화면에서 발송 일정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 목표 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H222" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7937,10 +7937,10 @@
         <v/>
       </c>
       <c r="F223" t="str">
-        <v>지역 제한</v>
+        <v>최소 성사 조건</v>
       </c>
       <c r="G223" t="str">
-        <v>'공구 개설 폼' 화면에서 지역 제한이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 최소 성사 조건이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H223" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7969,13 +7969,13 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>조건부 환불 정책 확인</v>
+        <v>모집 기간(시작·마감일시)</v>
       </c>
       <c r="G224" t="str">
-        <v>'공구 개설 폼'에서 조건부 환불 정책 확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 개설 폼' 화면에서 모집 기간(시작·마감일시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H224" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -8001,10 +8001,10 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>공급가</v>
+        <v>1인 최대 수량</v>
       </c>
       <c r="G225" t="str">
-        <v>'공구 개설 폼' 화면에서 공급가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 1인 최대 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H225" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8033,10 +8033,10 @@
         <v/>
       </c>
       <c r="F226" t="str">
-        <v>예상 수익 계산</v>
+        <v>총 수량 한도</v>
       </c>
       <c r="G226" t="str">
-        <v>'공구 개설 폼' 화면에서 예상 수익 계산이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 총 수량 한도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H226" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8065,10 +8065,10 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>임시 저장</v>
+        <v>옵션 관리</v>
       </c>
       <c r="G227" t="str">
-        <v>'공구 개설 폼' 화면에서 임시 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 옵션 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H227" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8097,10 +8097,10 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>검수 제출</v>
+        <v>배송비</v>
       </c>
       <c r="G228" t="str">
-        <v>'공구 개설 폼' 화면에서 검수 제출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 배송비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H228" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8114,28 +8114,28 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B229" t="str">
-        <v>공구 개설(진행자)</v>
+        <v/>
       </c>
       <c r="C229" t="str">
-        <v>개설 검수 대기·반려</v>
+        <v/>
       </c>
       <c r="D229" t="str">
-        <v>HS-03</v>
+        <v/>
       </c>
       <c r="E229" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F229" t="str">
-        <v>제출한 공구 미리보기</v>
+        <v>발송 일정</v>
       </c>
       <c r="G229" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 제출한 공구 미리보기가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 발송 일정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H229" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B230" t="str">
         <v/>
@@ -8161,13 +8161,13 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>검수 상태(대기·승인·반려) 표시</v>
+        <v>지역 제한</v>
       </c>
       <c r="G230" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 상태(대기·승인·반려) 표시가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 지역 제한이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H230" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B231" t="str">
         <v/>
@@ -8193,13 +8193,13 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>반려 사유와 수정 안내</v>
+        <v>조건부 환불 정책 확인</v>
       </c>
       <c r="G231" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 반려 사유와 수정 안내가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼'에서 조건부 환불 정책 확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H231" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B232" t="str">
         <v/>
@@ -8225,13 +8225,13 @@
         <v/>
       </c>
       <c r="F232" t="str">
-        <v>예상 검수 소요 시간</v>
+        <v>공급가</v>
       </c>
       <c r="G232" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 예상 검수 소요 시간이 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 공급가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H232" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B233" t="str">
         <v/>
@@ -8257,13 +8257,13 @@
         <v/>
       </c>
       <c r="F233" t="str">
-        <v>승인 시 자동 오픈 예약 안내</v>
+        <v>예상 수익 계산</v>
       </c>
       <c r="G233" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 승인 시 자동 오픈 예약 안내가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 예상 수익 계산이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H233" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I233" t="str">
         <v/>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B234" t="str">
         <v/>
@@ -8289,13 +8289,13 @@
         <v/>
       </c>
       <c r="F234" t="str">
-        <v>수정 후 재제출</v>
+        <v>임시 저장</v>
       </c>
       <c r="G234" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 수정 후 재제출이 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 임시 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H234" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B235" t="str">
         <v/>
@@ -8321,13 +8321,13 @@
         <v/>
       </c>
       <c r="F235" t="str">
-        <v>진행자 대시보드로 이동</v>
+        <v>검수 제출</v>
       </c>
       <c r="G235" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 진행자 대시보드로 이동이 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 검수 제출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H235" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I235" t="str">
         <v/>
@@ -8341,22 +8341,22 @@
         <v>SCN-025</v>
       </c>
       <c r="B236" t="str">
-        <v/>
+        <v>공구 개설(진행자)</v>
       </c>
       <c r="C236" t="str">
-        <v/>
+        <v>개설 검수 대기·반려</v>
       </c>
       <c r="D236" t="str">
-        <v/>
+        <v>HS-03</v>
       </c>
       <c r="E236" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F236" t="str">
-        <v>검수 가이드 링크</v>
+        <v>제출한 공구 미리보기</v>
       </c>
       <c r="G236" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 가이드 링크가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 제출한 공구 미리보기가 보이는지 확인한다.</v>
       </c>
       <c r="H236" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8370,28 +8370,28 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B237" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C237" t="str">
-        <v>진행자 대시보드</v>
+        <v/>
       </c>
       <c r="D237" t="str">
-        <v>HM-01</v>
+        <v/>
       </c>
       <c r="E237" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F237" t="str">
-        <v>요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)</v>
+        <v>검수 상태(대기·승인·반려) 표시</v>
       </c>
       <c r="G237" t="str">
-        <v>'진행자 대시보드' 화면에서 요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 상태(대기·승인·반려) 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H237" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B238" t="str">
         <v/>
@@ -8417,13 +8417,13 @@
         <v/>
       </c>
       <c r="F238" t="str">
-        <v>내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)</v>
+        <v>반려 사유와 수정 안내</v>
       </c>
       <c r="G238" t="str">
-        <v>'진행자 대시보드'의 내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 반려 사유와 수정 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H238" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I238" t="str">
         <v/>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B239" t="str">
         <v/>
@@ -8449,13 +8449,13 @@
         <v/>
       </c>
       <c r="F239" t="str">
-        <v>마감 임박/미달 위험 공구 강조</v>
+        <v>예상 검수 소요 시간</v>
       </c>
       <c r="G239" t="str">
-        <v>'진행자 대시보드' 화면에서 마감 임박/미달 위험 공구 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 예상 검수 소요 시간이 보이는지 확인한다.</v>
       </c>
       <c r="H239" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -8481,13 +8481,13 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>처리 필요 항목(발주 대기·배송 대기·문의 미답변)</v>
+        <v>승인 시 자동 오픈 예약 안내</v>
       </c>
       <c r="G240" t="str">
-        <v>'진행자 대시보드' 화면에서 처리 필요 항목(발주 대기·배송 대기·문의 미답변)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 승인 시 자동 오픈 예약 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H240" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I240" t="str">
         <v/>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B241" t="str">
         <v/>
@@ -8513,13 +8513,13 @@
         <v/>
       </c>
       <c r="F241" t="str">
-        <v>신규 공구 개설 버튼</v>
+        <v>수정 후 재제출</v>
       </c>
       <c r="G241" t="str">
-        <v>'진행자 대시보드'에서 신규 공구 개설 버튼을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 수정 후 재제출이 보이는지 확인한다.</v>
       </c>
       <c r="H241" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I241" t="str">
         <v/>
@@ -8530,7 +8530,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B242" t="str">
         <v/>
@@ -8545,13 +8545,13 @@
         <v/>
       </c>
       <c r="F242" t="str">
-        <v>성사율</v>
+        <v>진행자 대시보드로 이동</v>
       </c>
       <c r="G242" t="str">
-        <v>'진행자 대시보드' 화면에서 성사율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 진행자 대시보드로 이동이 보이는지 확인한다.</v>
       </c>
       <c r="H242" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B243" t="str">
         <v/>
@@ -8577,13 +8577,13 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>후기 평점</v>
+        <v>검수 가이드 링크</v>
       </c>
       <c r="G243" t="str">
-        <v>'진행자 대시보드' 화면에서 후기 평점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 가이드 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H243" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I243" t="str">
         <v/>
@@ -8594,25 +8594,25 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B244" t="str">
         <v>공구 관리(진행자)</v>
       </c>
       <c r="C244" t="str">
-        <v>공구별 참여 현황</v>
+        <v>진행자 대시보드</v>
       </c>
       <c r="D244" t="str">
-        <v>HM-02</v>
+        <v>HM-01</v>
       </c>
       <c r="E244" t="str">
         <v>기본</v>
       </c>
       <c r="F244" t="str">
-        <v>선택 공구 실시간 달성률</v>
+        <v>요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)</v>
       </c>
       <c r="G244" t="str">
-        <v>'공구별 참여 현황' 화면에서 선택 공구 실시간 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드' 화면에서 요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H244" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B245" t="str">
         <v/>
@@ -8641,13 +8641,13 @@
         <v/>
       </c>
       <c r="F245" t="str">
-        <v>목표 대비 그래프</v>
+        <v>내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)</v>
       </c>
       <c r="G245" t="str">
-        <v>'공구별 참여 현황' 화면에서 목표 대비 그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드'의 내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H245" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B246" t="str">
         <v/>
@@ -8673,10 +8673,10 @@
         <v/>
       </c>
       <c r="F246" t="str">
-        <v>시간대별 참여 추이</v>
+        <v>마감 임박/미달 위험 공구 강조</v>
       </c>
       <c r="G246" t="str">
-        <v>'공구별 참여 현황' 화면에서 시간대별 참여 추이가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드' 화면에서 마감 임박/미달 위험 공구 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H246" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B247" t="str">
         <v/>
@@ -8705,13 +8705,13 @@
         <v/>
       </c>
       <c r="F247" t="str">
-        <v>현재 단계와 다음 단계까지 남은 인원</v>
+        <v>처리 필요 항목(발주 대기·배송 대기·문의 미답변)</v>
       </c>
       <c r="G247" t="str">
-        <v>'공구별 참여 현황'의 현재 단계와 다음 단계까지 남은 인원이 실제 데이터와 같은지 대조한다.</v>
+        <v>'진행자 대시보드' 화면에서 처리 필요 항목(발주 대기·배송 대기·문의 미답변)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H247" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B248" t="str">
         <v/>
@@ -8737,13 +8737,13 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)</v>
+        <v>신규 공구 개설 버튼</v>
       </c>
       <c r="G248" t="str">
-        <v>'공구별 참여 현황'의 참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'진행자 대시보드'에서 신규 공구 개설 버튼을 눌러 본다.</v>
       </c>
       <c r="H248" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -8769,13 +8769,13 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>검색</v>
+        <v>성사율</v>
       </c>
       <c r="G249" t="str">
-        <v>'공구별 참여 현황'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'진행자 대시보드' 화면에서 성사율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H249" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B250" t="str">
         <v/>
@@ -8801,13 +8801,13 @@
         <v/>
       </c>
       <c r="F250" t="str">
-        <v>필터</v>
+        <v>후기 평점</v>
       </c>
       <c r="G250" t="str">
-        <v>'공구별 참여 현황'에서 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'진행자 대시보드' 화면에서 후기 평점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H250" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -8821,25 +8821,25 @@
         <v>SCN-027</v>
       </c>
       <c r="B251" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C251" t="str">
-        <v/>
+        <v>공구별 참여 현황</v>
       </c>
       <c r="D251" t="str">
-        <v/>
+        <v>HM-02</v>
       </c>
       <c r="E251" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F251" t="str">
-        <v>취소</v>
+        <v>선택 공구 실시간 달성률</v>
       </c>
       <c r="G251" t="str">
-        <v>'공구별 참여 현황'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 선택 공구 실시간 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H251" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -8865,13 +8865,13 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v>환불 참여 표시</v>
+        <v>목표 대비 그래프</v>
       </c>
       <c r="G252" t="str">
-        <v>'공구별 참여 현황'에서 환불 참여 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 목표 대비 그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H252" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -8897,10 +8897,10 @@
         <v/>
       </c>
       <c r="F253" t="str">
-        <v>참여자에게 공지 발송</v>
+        <v>시간대별 참여 추이</v>
       </c>
       <c r="G253" t="str">
-        <v>'공구별 참여 현황' 화면에서 참여자에게 공지 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 시간대별 참여 추이가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H253" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8929,13 +8929,13 @@
         <v/>
       </c>
       <c r="F254" t="str">
-        <v>엑셀 내보내기</v>
+        <v>현재 단계와 다음 단계까지 남은 인원</v>
       </c>
       <c r="G254" t="str">
-        <v>'공구별 참여 현황' 화면에서 엑셀 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'의 현재 단계와 다음 단계까지 남은 인원이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H254" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -8946,28 +8946,28 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B255" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C255" t="str">
-        <v>마감·성사 처리</v>
+        <v/>
       </c>
       <c r="D255" t="str">
-        <v>HM-03</v>
+        <v/>
       </c>
       <c r="E255" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F255" t="str">
-        <v>마감 임박 공구 요약과 최종 달성 여부 판정</v>
+        <v>참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)</v>
       </c>
       <c r="G255" t="str">
-        <v>'마감·성사 처리' 화면에서 마감 임박 공구 요약과 최종 달성 여부 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'의 참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H255" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B256" t="str">
         <v/>
@@ -8993,13 +8993,13 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>성사 확정 처리</v>
+        <v>검색</v>
       </c>
       <c r="G256" t="str">
-        <v>'마감·성사 처리' 화면에서 성사 확정 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H256" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B257" t="str">
         <v/>
@@ -9025,13 +9025,13 @@
         <v/>
       </c>
       <c r="F257" t="str">
-        <v>목표 근접 시 마감 연장 옵션</v>
+        <v>필터</v>
       </c>
       <c r="G257" t="str">
-        <v>'마감·성사 처리' 화면에서 목표 근접 시 마감 연장 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'에서 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H257" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B258" t="str">
         <v/>
@@ -9057,10 +9057,10 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>미달 시 불발 처리와 자동 환불 실행 안내</v>
+        <v>취소</v>
       </c>
       <c r="G258" t="str">
-        <v>'마감·성사 처리'에서 미달 시 불발 처리와 자동 환불 실행 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구별 참여 현황'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H258" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B259" t="str">
         <v/>
@@ -9089,13 +9089,13 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v>참여자 일괄 알림(성사/환불)</v>
+        <v>환불 참여 표시</v>
       </c>
       <c r="G259" t="str">
-        <v>'마감·성사 처리' 화면에서 참여자 일괄 알림(성사/환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'에서 환불 참여 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H259" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B260" t="str">
         <v/>
@@ -9121,10 +9121,10 @@
         <v/>
       </c>
       <c r="F260" t="str">
-        <v>성사분 수량 집계와 발주 준비</v>
+        <v>참여자에게 공지 발송</v>
       </c>
       <c r="G260" t="str">
-        <v>'마감·성사 처리' 화면에서 성사분 수량 집계와 발주 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 참여자에게 공지 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H260" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B261" t="str">
         <v/>
@@ -9153,10 +9153,10 @@
         <v/>
       </c>
       <c r="F261" t="str">
-        <v>처리 확인 모달</v>
+        <v>엑셀 내보내기</v>
       </c>
       <c r="G261" t="str">
-        <v>'마감·성사 처리' 화면에서 처리 확인 모달이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 엑셀 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H261" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9170,25 +9170,25 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B262" t="str">
         <v>공구 관리(진행자)</v>
       </c>
       <c r="C262" t="str">
-        <v>발주·배송 관리</v>
+        <v>마감·성사 처리</v>
       </c>
       <c r="D262" t="str">
-        <v>HM-04</v>
+        <v>HM-03</v>
       </c>
       <c r="E262" t="str">
         <v>기본</v>
       </c>
       <c r="F262" t="str">
-        <v>성사분 총 수량</v>
+        <v>마감 임박 공구 요약과 최종 달성 여부 판정</v>
       </c>
       <c r="G262" t="str">
-        <v>'발주·배송 관리' 화면에서 성사분 총 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 마감 임박 공구 요약과 최종 달성 여부 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H262" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B263" t="str">
         <v/>
@@ -9217,10 +9217,10 @@
         <v/>
       </c>
       <c r="F263" t="str">
-        <v>옵션별 집계</v>
+        <v>성사 확정 처리</v>
       </c>
       <c r="G263" t="str">
-        <v>'발주·배송 관리' 화면에서 옵션별 집계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 성사 확정 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H263" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9234,7 +9234,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B264" t="str">
         <v/>
@@ -9249,10 +9249,10 @@
         <v/>
       </c>
       <c r="F264" t="str">
-        <v>공급처 발주서 생성</v>
+        <v>목표 근접 시 마감 연장 옵션</v>
       </c>
       <c r="G264" t="str">
-        <v>'발주·배송 관리' 화면에서 공급처 발주서 생성이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 목표 근접 시 마감 연장 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H264" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B265" t="str">
         <v/>
@@ -9281,13 +9281,13 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>다운로드</v>
+        <v>미달 시 불발 처리와 자동 환불 실행 안내</v>
       </c>
       <c r="G265" t="str">
-        <v>'발주·배송 관리' 화면에서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리'에서 미달 시 불발 처리와 자동 환불 실행 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H265" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I265" t="str">
         <v/>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B266" t="str">
         <v/>
@@ -9313,13 +9313,13 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>배송 상태 관리(준비·발송·완료)</v>
+        <v>참여자 일괄 알림(성사/환불)</v>
       </c>
       <c r="G266" t="str">
-        <v>'발주·배송 관리'의 배송 상태 관리(준비·발송·완료)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'마감·성사 처리' 화면에서 참여자 일괄 알림(성사/환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H266" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I266" t="str">
         <v/>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B267" t="str">
         <v/>
@@ -9345,13 +9345,13 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)</v>
+        <v>성사분 수량 집계와 발주 준비</v>
       </c>
       <c r="G267" t="str">
-        <v>'발주·배송 관리'의 참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'마감·성사 처리' 화면에서 성사분 수량 집계와 발주 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H267" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I267" t="str">
         <v/>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B268" t="str">
         <v/>
@@ -9377,10 +9377,10 @@
         <v/>
       </c>
       <c r="F268" t="str">
-        <v>배송 출발 알림 발송</v>
+        <v>처리 확인 모달</v>
       </c>
       <c r="G268" t="str">
-        <v>'발주·배송 관리' 화면에서 배송 출발 알림 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 처리 확인 모달이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H268" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9397,22 +9397,22 @@
         <v>SCN-029</v>
       </c>
       <c r="B269" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C269" t="str">
-        <v/>
+        <v>발주·배송 관리</v>
       </c>
       <c r="D269" t="str">
-        <v/>
+        <v>HM-04</v>
       </c>
       <c r="E269" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F269" t="str">
-        <v>반품</v>
+        <v>성사분 총 수량</v>
       </c>
       <c r="G269" t="str">
-        <v>'발주·배송 관리' 화면에서 반품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 성사분 총 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H269" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9441,10 +9441,10 @@
         <v/>
       </c>
       <c r="F270" t="str">
-        <v>교환 접수</v>
+        <v>옵션별 집계</v>
       </c>
       <c r="G270" t="str">
-        <v>'발주·배송 관리' 화면에서 교환 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 옵션별 집계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H270" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9473,10 +9473,10 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>배송 지연 공지</v>
+        <v>공급처 발주서 생성</v>
       </c>
       <c r="G271" t="str">
-        <v>'발주·배송 관리' 화면에서 배송 지연 공지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 공급처 발주서 생성이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H271" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9505,13 +9505,13 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v>진행률 표시</v>
+        <v>다운로드</v>
       </c>
       <c r="G272" t="str">
-        <v>'발주·배송 관리'의 진행률 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'발주·배송 관리' 화면에서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H272" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -9522,28 +9522,28 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B273" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C273" t="str">
-        <v>참여자 공지·알림 발송</v>
+        <v/>
       </c>
       <c r="D273" t="str">
-        <v>HM-05</v>
+        <v/>
       </c>
       <c r="E273" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F273" t="str">
-        <v>대상 공구</v>
+        <v>배송 상태 관리(준비·발송·완료)</v>
       </c>
       <c r="G273" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 대상 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리'의 배송 상태 관리(준비·발송·완료)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H273" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I273" t="str">
         <v/>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B274" t="str">
         <v/>
@@ -9569,13 +9569,13 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v>참여자 세그먼트 선택</v>
+        <v>참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)</v>
       </c>
       <c r="G274" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 참여자 세그먼트 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리'의 참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H274" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B275" t="str">
         <v/>
@@ -9601,10 +9601,10 @@
         <v/>
       </c>
       <c r="F275" t="str">
-        <v>공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)</v>
+        <v>배송 출발 알림 발송</v>
       </c>
       <c r="G275" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 배송 출발 알림 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H275" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B276" t="str">
         <v/>
@@ -9633,10 +9633,10 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>템플릿 불러오기와 치환 변수</v>
+        <v>반품</v>
       </c>
       <c r="G276" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 템플릿 불러오기와 치환 변수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 반품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H276" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B277" t="str">
         <v/>
@@ -9665,10 +9665,10 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v>발송 채널(앱 알림·카톡·문자)</v>
+        <v>교환 접수</v>
       </c>
       <c r="G277" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 발송 채널(앱 알림·카톡·문자)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 교환 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H277" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B278" t="str">
         <v/>
@@ -9697,10 +9697,10 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v>예상 도달 수</v>
+        <v>배송 지연 공지</v>
       </c>
       <c r="G278" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 예상 도달 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 배송 지연 공지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H278" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B279" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>비용</v>
+        <v>진행률 표시</v>
       </c>
       <c r="G279" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 비용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리'의 진행률 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H279" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -9749,22 +9749,22 @@
         <v>SCN-030</v>
       </c>
       <c r="B280" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C280" t="str">
-        <v/>
+        <v>참여자 공지·알림 발송</v>
       </c>
       <c r="D280" t="str">
-        <v/>
+        <v>HM-05</v>
       </c>
       <c r="E280" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F280" t="str">
-        <v>미리보기</v>
+        <v>대상 공구</v>
       </c>
       <c r="G280" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 대상 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H280" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9793,10 +9793,10 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v>즉시</v>
+        <v>참여자 세그먼트 선택</v>
       </c>
       <c r="G281" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 즉시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 참여자 세그먼트 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H281" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9825,10 +9825,10 @@
         <v/>
       </c>
       <c r="F282" t="str">
-        <v>예약 발송</v>
+        <v>공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)</v>
       </c>
       <c r="G282" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 예약 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H282" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9857,10 +9857,10 @@
         <v/>
       </c>
       <c r="F283" t="str">
-        <v>발송 이력</v>
+        <v>템플릿 불러오기와 치환 변수</v>
       </c>
       <c r="G283" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 발송 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 템플릿 불러오기와 치환 변수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H283" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9874,28 +9874,28 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B284" t="str">
-        <v>정산(진행자)</v>
+        <v/>
       </c>
       <c r="C284" t="str">
-        <v>정산 내역</v>
+        <v/>
       </c>
       <c r="D284" t="str">
-        <v>SE-01</v>
+        <v/>
       </c>
       <c r="E284" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F284" t="str">
-        <v>정산 요약(정산 예정·정산 완료·보류 금액)</v>
+        <v>발송 채널(앱 알림·카톡·문자)</v>
       </c>
       <c r="G284" t="str">
-        <v>'정산 내역'에서 정산 요약(정산 예정·정산 완료·보류 금액)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 발송 채널(앱 알림·카톡·문자)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H284" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I284" t="str">
         <v/>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B285" t="str">
         <v/>
@@ -9921,13 +9921,13 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>공구별 정산 표(매출·수수료·환불·순정산액·상태)</v>
+        <v>예상 도달 수</v>
       </c>
       <c r="G285" t="str">
-        <v>'정산 내역'에서 공구별 정산 표(매출·수수료·환불·순정산액·상태)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 예상 도달 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H285" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B286" t="str">
         <v/>
@@ -9953,13 +9953,13 @@
         <v/>
       </c>
       <c r="F286" t="str">
-        <v>정산 주기</v>
+        <v>비용</v>
       </c>
       <c r="G286" t="str">
-        <v>'정산 내역'에서 정산 주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 비용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H286" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B287" t="str">
         <v/>
@@ -9985,10 +9985,10 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>예정일 안내</v>
+        <v>미리보기</v>
       </c>
       <c r="G287" t="str">
-        <v>'정산 내역' 화면에서 예정일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H287" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B288" t="str">
         <v/>
@@ -10017,13 +10017,13 @@
         <v/>
       </c>
       <c r="F288" t="str">
-        <v>기간 필터</v>
+        <v>즉시</v>
       </c>
       <c r="G288" t="str">
-        <v>'정산 내역'에서 기간 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 즉시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H288" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I288" t="str">
         <v/>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B289" t="str">
         <v/>
@@ -10049,13 +10049,13 @@
         <v/>
       </c>
       <c r="F289" t="str">
-        <v>정산 상세로 이동</v>
+        <v>예약 발송</v>
       </c>
       <c r="G289" t="str">
-        <v>'정산 내역'에서 정산 상세로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 예약 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H289" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B290" t="str">
         <v/>
@@ -10081,10 +10081,10 @@
         <v/>
       </c>
       <c r="F290" t="str">
-        <v>세금계산서</v>
+        <v>발송 이력</v>
       </c>
       <c r="G290" t="str">
-        <v>'정산 내역' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 발송 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H290" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10101,25 +10101,25 @@
         <v>SCN-031</v>
       </c>
       <c r="B291" t="str">
-        <v/>
+        <v>정산(진행자)</v>
       </c>
       <c r="C291" t="str">
-        <v/>
+        <v>정산 내역</v>
       </c>
       <c r="D291" t="str">
-        <v/>
+        <v>SE-01</v>
       </c>
       <c r="E291" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F291" t="str">
-        <v>명세서</v>
+        <v>정산 요약(정산 예정·정산 완료·보류 금액)</v>
       </c>
       <c r="G291" t="str">
-        <v>'정산 내역' 화면에서 명세서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역'에서 정산 요약(정산 예정·정산 완료·보류 금액)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H291" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -10145,10 +10145,10 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>정산 계좌 설정 링크</v>
+        <v>공구별 정산 표(매출·수수료·환불·순정산액·상태)</v>
       </c>
       <c r="G292" t="str">
-        <v>'정산 내역'에서 정산 계좌 설정 링크를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역'에서 공구별 정산 표(매출·수수료·환불·순정산액·상태)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H292" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10177,13 +10177,13 @@
         <v/>
       </c>
       <c r="F293" t="str">
-        <v>내보내기</v>
+        <v>정산 주기</v>
       </c>
       <c r="G293" t="str">
-        <v>'정산 내역' 화면에서 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역'에서 정산 주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H293" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -10194,28 +10194,28 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B294" t="str">
-        <v>정산(진행자)</v>
+        <v/>
       </c>
       <c r="C294" t="str">
-        <v>정산 계좌·세금 설정</v>
+        <v/>
       </c>
       <c r="D294" t="str">
-        <v>SE-02</v>
+        <v/>
       </c>
       <c r="E294" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F294" t="str">
-        <v>정산 받을 계좌 등록(은행·계좌·예금주 인증)</v>
+        <v>예정일 안내</v>
       </c>
       <c r="G294" t="str">
-        <v>'정산 계좌·세금 설정'에서 정산 받을 계좌 등록(은행·계좌·예금주 인증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역' 화면에서 예정일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H294" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I294" t="str">
         <v/>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B295" t="str">
         <v/>
@@ -10241,13 +10241,13 @@
         <v/>
       </c>
       <c r="F295" t="str">
-        <v>사업자/개인 구분과 사업자등록증</v>
+        <v>기간 필터</v>
       </c>
       <c r="G295" t="str">
-        <v>'정산 계좌·세금 설정'의 사업자/개인 구분과 사업자등록증에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'정산 내역'에서 기간 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H295" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B296" t="str">
         <v/>
@@ -10273,13 +10273,13 @@
         <v/>
       </c>
       <c r="F296" t="str">
-        <v>세금 유형(과세·간이·면세)</v>
+        <v>정산 상세로 이동</v>
       </c>
       <c r="G296" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 세금 유형(과세·간이·면세)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역'에서 정산 상세로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H296" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B297" t="str">
         <v/>
@@ -10305,10 +10305,10 @@
         <v/>
       </c>
       <c r="F297" t="str">
-        <v>원천징수</v>
+        <v>세금계산서</v>
       </c>
       <c r="G297" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 원천징수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H297" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10322,7 +10322,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B298" t="str">
         <v/>
@@ -10337,10 +10337,10 @@
         <v/>
       </c>
       <c r="F298" t="str">
-        <v>부가세 안내</v>
+        <v>명세서</v>
       </c>
       <c r="G298" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 부가세 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역' 화면에서 명세서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H298" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B299" t="str">
         <v/>
@@ -10369,13 +10369,13 @@
         <v/>
       </c>
       <c r="F299" t="str">
-        <v>세금계산서 발행 정보</v>
+        <v>정산 계좌 설정 링크</v>
       </c>
       <c r="G299" t="str">
-        <v>'정산 계좌·세금 설정'의 세금계산서 발행 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 내역'에서 정산 계좌 설정 링크를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H299" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -10401,13 +10401,13 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>정산 주기 선택</v>
+        <v>내보내기</v>
       </c>
       <c r="G300" t="str">
-        <v>'정산 계좌·세금 설정'에서 정산 주기 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역' 화면에서 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H300" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I300" t="str">
         <v/>
@@ -10421,25 +10421,25 @@
         <v>SCN-032</v>
       </c>
       <c r="B301" t="str">
-        <v/>
+        <v>정산(진행자)</v>
       </c>
       <c r="C301" t="str">
-        <v/>
+        <v>정산 계좌·세금 설정</v>
       </c>
       <c r="D301" t="str">
-        <v/>
+        <v>SE-02</v>
       </c>
       <c r="E301" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F301" t="str">
-        <v>저장</v>
+        <v>정산 받을 계좌 등록(은행·계좌·예금주 인증)</v>
       </c>
       <c r="G301" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정'에서 정산 받을 계좌 등록(은행·계좌·예금주 인증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H301" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10465,13 +10465,13 @@
         <v/>
       </c>
       <c r="F302" t="str">
-        <v>민감정보 보안 안내</v>
+        <v>사업자/개인 구분과 사업자등록증</v>
       </c>
       <c r="G302" t="str">
-        <v>'정산 계좌·세금 설정'의 민감정보 보안 안내가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 계좌·세금 설정'의 사업자/개인 구분과 사업자등록증에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H302" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10482,28 +10482,28 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B303" t="str">
-        <v>정산(진행자)</v>
+        <v/>
       </c>
       <c r="C303" t="str">
-        <v>정산 상세</v>
+        <v/>
       </c>
       <c r="D303" t="str">
-        <v>SE-03</v>
+        <v/>
       </c>
       <c r="E303" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F303" t="str">
-        <v>선택 공구 정산 상세 내역</v>
+        <v>세금 유형(과세·간이·면세)</v>
       </c>
       <c r="G303" t="str">
-        <v>'정산 상세'에서 선택 공구 정산 상세 내역을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 세금 유형(과세·간이·면세)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I303" t="str">
         <v/>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B304" t="str">
         <v/>
@@ -10529,10 +10529,10 @@
         <v/>
       </c>
       <c r="F304" t="str">
-        <v>매출 구성(참여 건별 결제액 합계)</v>
+        <v>원천징수</v>
       </c>
       <c r="G304" t="str">
-        <v>'정산 상세' 화면에서 매출 구성(참여 건별 결제액 합계)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 원천징수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10546,7 +10546,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B305" t="str">
         <v/>
@@ -10561,10 +10561,10 @@
         <v/>
       </c>
       <c r="F305" t="str">
-        <v>차감 항목(수수료·환불·배송비·쿠폰 분담)</v>
+        <v>부가세 안내</v>
       </c>
       <c r="G305" t="str">
-        <v>'정산 상세' 화면에서 차감 항목(수수료·환불·배송비·쿠폰 분담)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 부가세 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H305" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10578,7 +10578,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B306" t="str">
         <v/>
@@ -10593,13 +10593,13 @@
         <v/>
       </c>
       <c r="F306" t="str">
-        <v>최종 순정산액</v>
+        <v>세금계산서 발행 정보</v>
       </c>
       <c r="G306" t="str">
-        <v>'정산 상세'에서 최종 순정산액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정'의 세금계산서 발행 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H306" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I306" t="str">
         <v/>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B307" t="str">
         <v/>
@@ -10625,10 +10625,10 @@
         <v/>
       </c>
       <c r="F307" t="str">
-        <v>정산 상태 타임라인</v>
+        <v>정산 주기 선택</v>
       </c>
       <c r="G307" t="str">
-        <v>'정산 상세'에서 정산 상태 타임라인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정'에서 정산 주기 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H307" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B308" t="str">
         <v/>
@@ -10657,10 +10657,10 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>세금계산서</v>
+        <v>저장</v>
       </c>
       <c r="G308" t="str">
-        <v>'정산 상세' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H308" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B309" t="str">
         <v/>
@@ -10689,13 +10689,13 @@
         <v/>
       </c>
       <c r="F309" t="str">
-        <v>거래명세서 다운로드</v>
+        <v>민감정보 보안 안내</v>
       </c>
       <c r="G309" t="str">
-        <v>'정산 상세' 화면에서 거래명세서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정'의 민감정보 보안 안내가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H309" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I309" t="str">
         <v/>
@@ -10709,22 +10709,22 @@
         <v>SCN-033</v>
       </c>
       <c r="B310" t="str">
-        <v/>
+        <v>정산(진행자)</v>
       </c>
       <c r="C310" t="str">
-        <v/>
+        <v>정산 상세</v>
       </c>
       <c r="D310" t="str">
-        <v/>
+        <v>SE-03</v>
       </c>
       <c r="E310" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F310" t="str">
-        <v>정산 문의</v>
+        <v>선택 공구 정산 상세 내역</v>
       </c>
       <c r="G310" t="str">
-        <v>'정산 상세'에서 정산 문의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 상세'에서 선택 공구 정산 상세 내역을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H310" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10753,13 +10753,13 @@
         <v/>
       </c>
       <c r="F311" t="str">
-        <v>이전/다음 정산 이동</v>
+        <v>매출 구성(참여 건별 결제액 합계)</v>
       </c>
       <c r="G311" t="str">
-        <v>'정산 상세'에서 이전/다음 정산 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 상세' 화면에서 매출 구성(참여 건별 결제액 합계)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H311" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I311" t="str">
         <v/>
@@ -10770,25 +10770,25 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B312" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C312" t="str">
-        <v>이용 안내·자주 묻는 질문</v>
+        <v/>
       </c>
       <c r="D312" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E312" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F312" t="str">
-        <v>공동구매 개념 설명(성사·불발·조건부 결제)</v>
+        <v>차감 항목(수수료·환불·배송비·쿠폰 분담)</v>
       </c>
       <c r="G312" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 공동구매 개념 설명(성사·불발·조건부 결제)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세' 화면에서 차감 항목(수수료·환불·배송비·쿠폰 분담)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H312" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B313" t="str">
         <v/>
@@ -10817,13 +10817,13 @@
         <v/>
       </c>
       <c r="F313" t="str">
-        <v>참여자용 3단계 이용법</v>
+        <v>최종 순정산액</v>
       </c>
       <c r="G313" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면을 열고 참여자용 3단계 이용법이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'정산 상세'에서 최종 순정산액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H313" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I313" t="str">
         <v/>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B314" t="str">
         <v/>
@@ -10849,13 +10849,13 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>진행자용 이용법</v>
+        <v>정산 상태 타임라인</v>
       </c>
       <c r="G314" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 진행자용 이용법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세'에서 정산 상태 타임라인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H314" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I314" t="str">
         <v/>
@@ -10866,7 +10866,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B315" t="str">
         <v/>
@@ -10881,10 +10881,10 @@
         <v/>
       </c>
       <c r="F315" t="str">
-        <v>카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)</v>
+        <v>세금계산서</v>
       </c>
       <c r="G315" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H315" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B316" t="str">
         <v/>
@@ -10913,13 +10913,13 @@
         <v/>
       </c>
       <c r="F316" t="str">
-        <v>검색</v>
+        <v>거래명세서 다운로드</v>
       </c>
       <c r="G316" t="str">
-        <v>'이용 안내·자주 묻는 질문'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'정산 상세' 화면에서 거래명세서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H316" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I316" t="str">
         <v/>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B317" t="str">
         <v/>
@@ -10945,13 +10945,13 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v>인기 질문</v>
+        <v>정산 문의</v>
       </c>
       <c r="G317" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 인기 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세'에서 정산 문의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H317" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I317" t="str">
         <v/>
@@ -10962,7 +10962,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B318" t="str">
         <v/>
@@ -10977,13 +10977,13 @@
         <v/>
       </c>
       <c r="F318" t="str">
-        <v>해결 안 되면 1:1 문의 유도</v>
+        <v>이전/다음 정산 이동</v>
       </c>
       <c r="G318" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 해결 안 되면 1:1 문의 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세'에서 이전/다음 정산 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H318" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I318" t="str">
         <v/>
@@ -10997,22 +10997,22 @@
         <v>SCN-034</v>
       </c>
       <c r="B319" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C319" t="str">
-        <v/>
+        <v>이용 안내·자주 묻는 질문</v>
       </c>
       <c r="D319" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E319" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F319" t="str">
-        <v>용어 설명</v>
+        <v>공동구매 개념 설명(성사·불발·조건부 결제)</v>
       </c>
       <c r="G319" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 용어 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 공동구매 개념 설명(성사·불발·조건부 결제)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H319" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11026,28 +11026,28 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B320" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C320" t="str">
-        <v>1:1 문의</v>
+        <v/>
       </c>
       <c r="D320" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E320" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F320" t="str">
-        <v>문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)</v>
+        <v>참여자용 3단계 이용법</v>
       </c>
       <c r="G320" t="str">
-        <v>'1:1 문의' 화면에서 문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면을 열고 참여자용 3단계 이용법이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H320" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I320" t="str">
         <v/>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B321" t="str">
         <v/>
@@ -11073,10 +11073,10 @@
         <v/>
       </c>
       <c r="F321" t="str">
-        <v>관련 공구</v>
+        <v>진행자용 이용법</v>
       </c>
       <c r="G321" t="str">
-        <v>'1:1 문의' 화면에서 관련 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 진행자용 이용법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H321" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B322" t="str">
         <v/>
@@ -11105,10 +11105,10 @@
         <v/>
       </c>
       <c r="F322" t="str">
-        <v>주문 연결</v>
+        <v>카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)</v>
       </c>
       <c r="G322" t="str">
-        <v>'1:1 문의' 화면에서 주문 연결이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H322" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B323" t="str">
         <v/>
@@ -11137,13 +11137,13 @@
         <v/>
       </c>
       <c r="F323" t="str">
-        <v>내용과 첨부</v>
+        <v>검색</v>
       </c>
       <c r="G323" t="str">
-        <v>'1:1 문의'의 내용과 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'이용 안내·자주 묻는 질문'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H323" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I323" t="str">
         <v/>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B324" t="str">
         <v/>
@@ -11169,10 +11169,10 @@
         <v/>
       </c>
       <c r="F324" t="str">
-        <v>연락처</v>
+        <v>인기 질문</v>
       </c>
       <c r="G324" t="str">
-        <v>'1:1 문의' 화면에서 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 인기 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H324" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11186,7 +11186,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B325" t="str">
         <v/>
@@ -11201,10 +11201,10 @@
         <v/>
       </c>
       <c r="F325" t="str">
-        <v>답변 방식 선택</v>
+        <v>해결 안 되면 1:1 문의 유도</v>
       </c>
       <c r="G325" t="str">
-        <v>'1:1 문의' 화면에서 답변 방식 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 해결 안 되면 1:1 문의 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H325" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B326" t="str">
         <v/>
@@ -11233,10 +11233,10 @@
         <v/>
       </c>
       <c r="F326" t="str">
-        <v>예상 답변 시간 안내</v>
+        <v>용어 설명</v>
       </c>
       <c r="G326" t="str">
-        <v>'1:1 문의' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 용어 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H326" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11253,25 +11253,25 @@
         <v>SCN-035</v>
       </c>
       <c r="B327" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C327" t="str">
-        <v/>
+        <v>1:1 문의</v>
       </c>
       <c r="D327" t="str">
-        <v/>
+        <v>CS-02</v>
       </c>
       <c r="E327" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F327" t="str">
-        <v>내 문의 내역과 상태</v>
+        <v>문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)</v>
       </c>
       <c r="G327" t="str">
-        <v>'1:1 문의'의 내 문의 내역과 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'1:1 문의' 화면에서 문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H327" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I327" t="str">
         <v/>
@@ -11297,10 +11297,10 @@
         <v/>
       </c>
       <c r="F328" t="str">
-        <v>답변 확인</v>
+        <v>관련 공구</v>
       </c>
       <c r="G328" t="str">
-        <v>'1:1 문의' 화면에서 답변 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 관련 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H328" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11329,10 +11329,10 @@
         <v/>
       </c>
       <c r="F329" t="str">
-        <v>챗봇 우선 안내</v>
+        <v>주문 연결</v>
       </c>
       <c r="G329" t="str">
-        <v>'1:1 문의' 화면에서 챗봇 우선 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 주문 연결이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H329" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11346,28 +11346,28 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B330" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C330" t="str">
-        <v>공지·이벤트</v>
+        <v/>
       </c>
       <c r="D330" t="str">
-        <v>CS-03</v>
+        <v/>
       </c>
       <c r="E330" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F330" t="str">
-        <v>공지사항 목록(중요 공지 상단 고정)</v>
+        <v>내용과 첨부</v>
       </c>
       <c r="G330" t="str">
-        <v>'공지·이벤트'의 공지사항 목록(중요 공지 상단 고정)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'1:1 문의'의 내용과 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H330" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I330" t="str">
         <v/>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B331" t="str">
         <v/>
@@ -11393,10 +11393,10 @@
         <v/>
       </c>
       <c r="F331" t="str">
-        <v>이벤트</v>
+        <v>연락처</v>
       </c>
       <c r="G331" t="str">
-        <v>'공지·이벤트' 화면에서 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H331" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11410,7 +11410,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B332" t="str">
         <v/>
@@ -11425,13 +11425,13 @@
         <v/>
       </c>
       <c r="F332" t="str">
-        <v>기획전 배너</v>
+        <v>답변 방식 선택</v>
       </c>
       <c r="G332" t="str">
-        <v>'공지·이벤트'에서 기획전 배너를 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 답변 방식 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H332" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I332" t="str">
         <v/>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B333" t="str">
         <v/>
@@ -11457,10 +11457,10 @@
         <v/>
       </c>
       <c r="F333" t="str">
-        <v>점검</v>
+        <v>예상 답변 시간 안내</v>
       </c>
       <c r="G333" t="str">
-        <v>'공지·이벤트' 화면에서 점검이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H333" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11474,7 +11474,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B334" t="str">
         <v/>
@@ -11489,13 +11489,13 @@
         <v/>
       </c>
       <c r="F334" t="str">
-        <v>정책 변경 안내</v>
+        <v>내 문의 내역과 상태</v>
       </c>
       <c r="G334" t="str">
-        <v>'공지·이벤트' 화면에서 정책 변경 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'의 내 문의 내역과 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H334" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I334" t="str">
         <v/>
@@ -11506,7 +11506,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B335" t="str">
         <v/>
@@ -11521,13 +11521,13 @@
         <v/>
       </c>
       <c r="F335" t="str">
-        <v>카테고리 필터</v>
+        <v>답변 확인</v>
       </c>
       <c r="G335" t="str">
-        <v>'공지·이벤트'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'1:1 문의' 화면에서 답변 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H335" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I335" t="str">
         <v/>
@@ -11538,7 +11538,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B336" t="str">
         <v/>
@@ -11553,10 +11553,10 @@
         <v/>
       </c>
       <c r="F336" t="str">
-        <v>상세 보기</v>
+        <v>챗봇 우선 안내</v>
       </c>
       <c r="G336" t="str">
-        <v>'공지·이벤트' 화면에서 상세 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 챗봇 우선 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H336" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11573,25 +11573,25 @@
         <v>SCN-036</v>
       </c>
       <c r="B337" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C337" t="str">
-        <v/>
+        <v>공지·이벤트</v>
       </c>
       <c r="D337" t="str">
-        <v/>
+        <v>CS-03</v>
       </c>
       <c r="E337" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F337" t="str">
-        <v>이벤트 참여 유도</v>
+        <v>공지사항 목록(중요 공지 상단 고정)</v>
       </c>
       <c r="G337" t="str">
-        <v>'공지·이벤트' 화면에서 이벤트 참여 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트'의 공지사항 목록(중요 공지 상단 고정)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H337" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I337" t="str">
         <v/>
@@ -11617,10 +11617,10 @@
         <v/>
       </c>
       <c r="F338" t="str">
-        <v>신규 진행자 지원 이벤트</v>
+        <v>이벤트</v>
       </c>
       <c r="G338" t="str">
-        <v>'공지·이벤트' 화면에서 신규 진행자 지원 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H338" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11634,28 +11634,28 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B339" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C339" t="str">
-        <v>환불·분쟁 정책 안내</v>
+        <v/>
       </c>
       <c r="D339" t="str">
-        <v>CS-04</v>
+        <v/>
       </c>
       <c r="E339" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F339" t="str">
-        <v>조건부 결제</v>
+        <v>기획전 배너</v>
       </c>
       <c r="G339" t="str">
-        <v>'환불·분쟁 정책 안내'에서 조건부 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트'에서 기획전 배너를 눌러 본다.</v>
       </c>
       <c r="H339" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I339" t="str">
         <v/>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B340" t="str">
         <v/>
@@ -11681,13 +11681,13 @@
         <v/>
       </c>
       <c r="F340" t="str">
-        <v>자동 환불 원칙 정리</v>
+        <v>점검</v>
       </c>
       <c r="G340" t="str">
-        <v>'환불·분쟁 정책 안내'에서 자동 환불 원칙 정리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트' 화면에서 점검이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H340" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I340" t="str">
         <v/>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B341" t="str">
         <v/>
@@ -11713,13 +11713,13 @@
         <v/>
       </c>
       <c r="F341" t="str">
-        <v>상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표</v>
+        <v>정책 변경 안내</v>
       </c>
       <c r="G341" t="str">
-        <v>'환불·분쟁 정책 안내'에서 상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트' 화면에서 정책 변경 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H341" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I341" t="str">
         <v/>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B342" t="str">
         <v/>
@@ -11745,13 +11745,13 @@
         <v/>
       </c>
       <c r="F342" t="str">
-        <v>환불 소요 시간과 수단</v>
+        <v>카테고리 필터</v>
       </c>
       <c r="G342" t="str">
-        <v>'환불·분쟁 정책 안내'에서 환불 소요 시간과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H342" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I342" t="str">
         <v/>
@@ -11762,7 +11762,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B343" t="str">
         <v/>
@@ -11777,10 +11777,10 @@
         <v/>
       </c>
       <c r="F343" t="str">
-        <v>진행자-참여자 분쟁 처리 절차</v>
+        <v>상세 보기</v>
       </c>
       <c r="G343" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 진행자-참여자 분쟁 처리 절차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 상세 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H343" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B344" t="str">
         <v/>
@@ -11809,10 +11809,10 @@
         <v/>
       </c>
       <c r="F344" t="str">
-        <v>소비자 보호</v>
+        <v>이벤트 참여 유도</v>
       </c>
       <c r="G344" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 소비자 보호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 이벤트 참여 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H344" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B345" t="str">
         <v/>
@@ -11841,10 +11841,10 @@
         <v/>
       </c>
       <c r="F345" t="str">
-        <v>에스크로 안내</v>
+        <v>신규 진행자 지원 이벤트</v>
       </c>
       <c r="G345" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 에스크로 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 신규 진행자 지원 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H345" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11861,25 +11861,25 @@
         <v>SCN-037</v>
       </c>
       <c r="B346" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C346" t="str">
-        <v/>
+        <v>환불·분쟁 정책 안내</v>
       </c>
       <c r="D346" t="str">
-        <v/>
+        <v>CS-04</v>
       </c>
       <c r="E346" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F346" t="str">
-        <v>신고 접수</v>
+        <v>조건부 결제</v>
       </c>
       <c r="G346" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환불·분쟁 정책 안내'에서 조건부 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H346" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I346" t="str">
         <v/>
@@ -11905,24 +11905,248 @@
         <v/>
       </c>
       <c r="F347" t="str">
+        <v>자동 환불 원칙 정리</v>
+      </c>
+      <c r="G347" t="str">
+        <v>'환불·분쟁 정책 안내'에서 자동 환불 원칙 정리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H347" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I347" t="str">
+        <v/>
+      </c>
+      <c r="J347" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B348" t="str">
+        <v/>
+      </c>
+      <c r="C348" t="str">
+        <v/>
+      </c>
+      <c r="D348" t="str">
+        <v/>
+      </c>
+      <c r="E348" t="str">
+        <v/>
+      </c>
+      <c r="F348" t="str">
+        <v>상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표</v>
+      </c>
+      <c r="G348" t="str">
+        <v>'환불·분쟁 정책 안내'에서 상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H348" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I348" t="str">
+        <v/>
+      </c>
+      <c r="J348" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B349" t="str">
+        <v/>
+      </c>
+      <c r="C349" t="str">
+        <v/>
+      </c>
+      <c r="D349" t="str">
+        <v/>
+      </c>
+      <c r="E349" t="str">
+        <v/>
+      </c>
+      <c r="F349" t="str">
+        <v>환불 소요 시간과 수단</v>
+      </c>
+      <c r="G349" t="str">
+        <v>'환불·분쟁 정책 안내'에서 환불 소요 시간과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H349" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I349" t="str">
+        <v/>
+      </c>
+      <c r="J349" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B350" t="str">
+        <v/>
+      </c>
+      <c r="C350" t="str">
+        <v/>
+      </c>
+      <c r="D350" t="str">
+        <v/>
+      </c>
+      <c r="E350" t="str">
+        <v/>
+      </c>
+      <c r="F350" t="str">
+        <v>진행자-참여자 분쟁 처리 절차</v>
+      </c>
+      <c r="G350" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 진행자-참여자 분쟁 처리 절차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H350" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I350" t="str">
+        <v/>
+      </c>
+      <c r="J350" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B351" t="str">
+        <v/>
+      </c>
+      <c r="C351" t="str">
+        <v/>
+      </c>
+      <c r="D351" t="str">
+        <v/>
+      </c>
+      <c r="E351" t="str">
+        <v/>
+      </c>
+      <c r="F351" t="str">
+        <v>소비자 보호</v>
+      </c>
+      <c r="G351" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 소비자 보호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H351" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I351" t="str">
+        <v/>
+      </c>
+      <c r="J351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B352" t="str">
+        <v/>
+      </c>
+      <c r="C352" t="str">
+        <v/>
+      </c>
+      <c r="D352" t="str">
+        <v/>
+      </c>
+      <c r="E352" t="str">
+        <v/>
+      </c>
+      <c r="F352" t="str">
+        <v>에스크로 안내</v>
+      </c>
+      <c r="G352" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 에스크로 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H352" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I352" t="str">
+        <v/>
+      </c>
+      <c r="J352" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B353" t="str">
+        <v/>
+      </c>
+      <c r="C353" t="str">
+        <v/>
+      </c>
+      <c r="D353" t="str">
+        <v/>
+      </c>
+      <c r="E353" t="str">
+        <v/>
+      </c>
+      <c r="F353" t="str">
+        <v>신고 접수</v>
+      </c>
+      <c r="G353" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H353" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I353" t="str">
+        <v/>
+      </c>
+      <c r="J353" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B354" t="str">
+        <v/>
+      </c>
+      <c r="C354" t="str">
+        <v/>
+      </c>
+      <c r="D354" t="str">
+        <v/>
+      </c>
+      <c r="E354" t="str">
+        <v/>
+      </c>
+      <c r="F354" t="str">
         <v>관련 문의 링크</v>
       </c>
-      <c r="G347" t="str">
+      <c r="G354" t="str">
         <v>'환불·분쟁 정책 안내'에서 관련 문의 링크를 눌러 본다.</v>
       </c>
-      <c r="H347" t="str">
+      <c r="H354" t="str">
         <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
-      <c r="I347" t="str">
-        <v/>
-      </c>
-      <c r="J347" t="str">
+      <c r="I354" t="str">
+        <v/>
+      </c>
+      <c r="J354" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J347"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J354"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J360"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1426,28 +1426,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B20" t="str">
-        <v>홈·탐색</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>상단 GNB(로고·검색·내 공구함·로그인)</v>
+        <v>끊어진 링크 — 갈 곳이 실제로 있는지</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈' 화면에서 상단 GNB(로고·검색·내 공구함·로그인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>스펙팩 7-9-2 의 검사 글을 사이트 «뿌리»에서 한 번 돌린다. ⚠ pages/ 만 주면 한 층 위의 화면 목록을 못 봐서 멀쩡한 화면이 외톨이로 잘못 잡힌다.</v>
       </c>
       <c r="H20" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>끊어진 링크 0건. `href` 가 가리키는 .html 이 모두 실제로 있다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>히어로 배너(오늘의 대표 공구, 달성률·남은시간)</v>
+        <v>없는 그림 · 빈 파일</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈'에서 히어로 배너(오늘의 대표 공구, 달성률·남은시간)을 눌러 본다.</v>
+        <v>같은 검사 글의 결과에서 «없는 그림»과 «빈 파일» 줄을 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>둘 다 0건. `src` 가 가리키는 파일이 모두 있고, 0바이트로 남은 화면이 없다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>마감 임박 공구 가로 스크롤(카운트다운 뱃지)</v>
+        <v>외톨이 화면 — 아무 데서도 안 이어지는 화면</v>
       </c>
       <c r="G22" t="str">
-        <v>'홈' 화면에서 마감 임박 공구 가로 스크롤(카운트다운 뱃지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>같은 검사 글의 «외톨이» 줄을 본다. 나온 화면은 어디서 이어져야 맞는지 정하고 그 링크를 놓는다.</v>
       </c>
       <c r="H22" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>외톨이 0건. 만들어 놓고 갈 길이 없는 화면이 없다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>카테고리 바로가기</v>
+        <v>화면 수가 약속한 수와 같은지</v>
       </c>
       <c r="G23" t="str">
-        <v>'홈'에서 카테고리 바로가기를 눌러 본다.</v>
+        <v>만든 .html 수를 세어 스펙팩 4장의 화면 수와 견준다.</v>
       </c>
       <c r="H23" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>두 수가 같다. 목록에는 있는데 안 만든 화면, 만들었는데 목록에 없는 화면 둘 다 0.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1569,13 +1569,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)</v>
+        <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>'홈'의 지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>곧 열리는 공구 예고와 알림 신청</v>
+        <v>굳은 날짜 — 견본 날짜가 오늘에서 거꾸로 잡혔는지</v>
       </c>
       <c r="G25" t="str">
-        <v>'홈' 화면에서 곧 열리는 공구 예고와 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>목록·상세의 날짜와 요일을 오늘 기준으로 다시 센다. 요일은 눈으로 세지 말고 달력과 맞춘다.</v>
       </c>
       <c r="H25" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>지난 날짜가 「예정」으로 보이지 않는다. 요일이 그 날짜의 실제 요일과 같다.</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1621,25 +1621,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>홈·탐색</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F26" t="str">
-        <v>진행자 모집 배너</v>
+        <v>상단 GNB(로고·검색·내 공구함·로그인)</v>
       </c>
       <c r="G26" t="str">
-        <v>'홈'에서 진행자 모집 배너를 눌러 본다.</v>
+        <v>'홈' 화면에서 상단 GNB(로고·검색·내 공구함·로그인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1665,13 +1665,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>이용 안내 3단계</v>
+        <v>히어로 배너(오늘의 대표 공구, 달성률·남은시간)</v>
       </c>
       <c r="G27" t="str">
-        <v>'홈' 화면을 열고 이용 안내 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈'에서 히어로 배너(오늘의 대표 공구, 달성률·남은시간)을 눌러 본다.</v>
       </c>
       <c r="H27" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1697,10 +1697,10 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>하단 앱 다운로드/뉴스레터</v>
+        <v>마감 임박 공구 가로 스크롤(카운트다운 뱃지)</v>
       </c>
       <c r="G28" t="str">
-        <v>'홈' 화면에서 하단 앱 다운로드/뉴스레터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 마감 임박 공구 가로 스크롤(카운트다운 뱃지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H28" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1714,28 +1714,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B29" t="str">
-        <v>홈·탐색</v>
+        <v/>
       </c>
       <c r="C29" t="str">
-        <v>공구 목록</v>
+        <v/>
       </c>
       <c r="D29" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E29" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F29" t="str">
-        <v>카테고리 탭</v>
+        <v>카테고리 바로가기</v>
       </c>
       <c r="G29" t="str">
-        <v>'공구 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈'에서 카테고리 바로가기를 눌러 본다.</v>
       </c>
       <c r="H29" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1761,13 +1761,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>필터(진행 상태·가격대·배송·마감 임박·달성률)</v>
+        <v>지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)</v>
       </c>
       <c r="G30" t="str">
-        <v>'공구 목록'에서 필터(진행 상태·가격대·배송·마감 임박·달성률)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈'의 지금 뜨는 공구 그리드(달성률 게이지·참여 인원·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H30" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -1793,13 +1793,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>정렬(마감 임박·인기·달성률 높은순·할인율·최신)</v>
+        <v>곧 열리는 공구 예고와 알림 신청</v>
       </c>
       <c r="G31" t="str">
-        <v>'공구 목록'에서 정렬(마감 임박·인기·달성률 높은순·할인율·최신)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면에서 곧 열리는 공구 예고와 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H31" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1825,13 +1825,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)</v>
+        <v>진행자 모집 배너</v>
       </c>
       <c r="G32" t="str">
-        <v>'공구 목록'의 공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈'에서 진행자 모집 배너를 눌러 본다.</v>
       </c>
       <c r="H32" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>무한 스크롤</v>
+        <v>이용 안내 3단계</v>
       </c>
       <c r="G33" t="str">
-        <v>'공구 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 이용 안내 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H33" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1889,10 +1889,10 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>관심 공구 찜</v>
+        <v>하단 앱 다운로드/뉴스레터</v>
       </c>
       <c r="G34" t="str">
-        <v>'공구 목록' 화면에서 관심 공구 찜이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 하단 앱 다운로드/뉴스레터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H34" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1909,25 +1909,25 @@
         <v>SCN-002</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>홈·탐색</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>공구 목록</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>HO-02</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F35" t="str">
-        <v>검색창</v>
+        <v>카테고리 탭</v>
       </c>
       <c r="G35" t="str">
-        <v>'공구 목록'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'공구 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H35" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1938,28 +1938,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B36" t="str">
-        <v>홈·탐색</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>마감 임박 타임딜</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>HO-03</v>
+        <v/>
       </c>
       <c r="E36" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v>실시간 카운트다운 헤더</v>
+        <v>필터(진행 상태·가격대·배송·마감 임박·달성률)</v>
       </c>
       <c r="G36" t="str">
-        <v>'마감 임박 타임딜' 화면에서 실시간 카운트다운 헤더가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록'에서 필터(진행 상태·가격대·배송·마감 임박·달성률)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1985,10 +1985,10 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)</v>
+        <v>정렬(마감 임박·인기·달성률 높은순·할인율·최신)</v>
       </c>
       <c r="G37" t="str">
-        <v>'마감 임박 타임딜'에서 마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'공구 목록'에서 정렬(마감 임박·인기·달성률 높은순·할인율·최신)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H37" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -2017,13 +2017,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>'앞으로 N명이면 성사' 강조</v>
+        <v>공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)</v>
       </c>
       <c r="G38" t="str">
-        <v>'마감 임박 타임딜' 화면에서 '앞으로 N명이면 성사' 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록'의 공구 카드 그리드(이미지·할인율·달성률 게이지·참여 인원·남은 시간·최저가)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H38" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>함께 참여 독려 문구</v>
+        <v>무한 스크롤</v>
       </c>
       <c r="G39" t="str">
-        <v>'마감 임박 타임딜' 화면에서 함께 참여 독려 문구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H39" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -2081,10 +2081,10 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>놓친 딜 다시 알림 신청</v>
+        <v>관심 공구 찜</v>
       </c>
       <c r="G40" t="str">
-        <v>'마감 임박 타임딜' 화면에서 놓친 딜 다시 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 목록' 화면에서 관심 공구 찜이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H40" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>필터(오늘 마감·1시간 내 마감)</v>
+        <v>검색창</v>
       </c>
       <c r="G41" t="str">
-        <v>'마감 임박 타임딜'에서 필터(오늘 마감·1시간 내 마감)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'공구 목록'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H41" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2130,28 +2130,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B42" t="str">
         <v>홈·탐색</v>
       </c>
       <c r="C42" t="str">
-        <v>공구 목록 - 결과 없음</v>
+        <v>마감 임박 타임딜</v>
       </c>
       <c r="D42" t="str">
-        <v>HO-04</v>
+        <v>HO-03</v>
       </c>
       <c r="E42" t="str">
-        <v>예외·상태</v>
+        <v>기본</v>
       </c>
       <c r="F42" t="str">
-        <v>검색어</v>
+        <v>실시간 카운트다운 헤더</v>
       </c>
       <c r="G42" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 검색어가 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 실시간 카운트다운 헤더가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H42" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>필터 포함 안내 문구</v>
+        <v>마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)</v>
       </c>
       <c r="G43" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 포함 안내 문구가 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜'에서 마감 임박순 정렬 공구 리스트(남은 시간·달성률·부족 인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H43" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>필터 초기화 버튼</v>
+        <v>'앞으로 N명이면 성사' 강조</v>
       </c>
       <c r="G44" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 '앞으로 N명이면 성사' 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H44" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -2241,13 +2241,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>인기 공구 추천 4개</v>
+        <v>함께 참여 독려 문구</v>
       </c>
       <c r="G45" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 인기 공구 추천 4개가 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 함께 참여 독려 문구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H45" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -2273,13 +2273,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>원하는 상품 공구 요청</v>
+        <v>놓친 딜 다시 알림 신청</v>
       </c>
       <c r="G46" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 원하는 상품 공구 요청이 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜' 화면에서 놓친 딜 다시 알림 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H46" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2305,13 +2305,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>알림 신청</v>
+        <v>필터(오늘 마감·1시간 내 마감)</v>
       </c>
       <c r="G47" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 알림 신청이 보이는지 확인한다.</v>
+        <v>'마감 임박 타임딜'에서 필터(오늘 마감·1시간 내 마감)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H47" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2325,22 +2325,22 @@
         <v>SCN-004</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>홈·탐색</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>공구 목록 - 결과 없음</v>
       </c>
       <c r="D48" t="str">
-        <v/>
+        <v>HO-04</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F48" t="str">
-        <v>카테고리 둘러보기 링크</v>
+        <v>검색어</v>
       </c>
       <c r="G48" t="str">
-        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 카테고리 둘러보기 링크가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 검색어가 보이는지 확인한다.</v>
       </c>
       <c r="H48" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -2354,28 +2354,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B49" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C49" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="D49" t="str">
-        <v>DE-01</v>
+        <v/>
       </c>
       <c r="E49" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>상품 이미지 갤러리</v>
+        <v>필터 포함 안내 문구</v>
       </c>
       <c r="G49" t="str">
-        <v>'공구 상세'의 상품 이미지 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 포함 안내 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H49" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2401,13 +2401,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>달성률 게이지와 목표/현재 인원</v>
+        <v>필터 초기화 버튼</v>
       </c>
       <c r="G50" t="str">
-        <v>'공구 상세' 화면에서 달성률 게이지와 목표/현재 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H50" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>마감 카운트다운</v>
+        <v>인기 공구 추천 4개</v>
       </c>
       <c r="G51" t="str">
-        <v>'공구 상세' 화면에서 마감 카운트다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 인기 공구 추천 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H51" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>단계별 가격표(N명 도달 시 추가 할인)</v>
+        <v>원하는 상품 공구 요청</v>
       </c>
       <c r="G52" t="str">
-        <v>'공구 상세'의 단계별 가격표(N명 도달 시 추가 할인)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 원하는 상품 공구 요청이 보이는지 확인한다.</v>
       </c>
       <c r="H52" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -2497,13 +2497,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>현재 적용가와 정가 대비 할인율</v>
+        <v>알림 신청</v>
       </c>
       <c r="G53" t="str">
-        <v>'공구 상세' 화면에서 현재 적용가와 정가 대비 할인율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H53" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -2529,13 +2529,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>실시간 참여 현황(최근 참여자·증가 애니메이션)</v>
+        <v>카테고리 둘러보기 링크</v>
       </c>
       <c r="G54" t="str">
-        <v>'공구 상세'의 실시간 참여 현황(최근 참여자·증가 애니메이션)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 목록 - 결과 없음' 화면이 나오게 한 뒤, 카테고리 둘러보기 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H54" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2549,25 +2549,25 @@
         <v>SCN-005</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>DE-01</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F55" t="str">
-        <v>옵션 요약</v>
+        <v>상품 이미지 갤러리</v>
       </c>
       <c r="G55" t="str">
-        <v>'공구 상세' 화면에서 옵션 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'의 상품 이미지 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H55" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>조건부 결제 안내(미달 시 자동 환불)</v>
+        <v>달성률 게이지와 목표/현재 인원</v>
       </c>
       <c r="G56" t="str">
-        <v>'공구 상세'에서 조건부 결제 안내(미달 시 자동 환불)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 상세' 화면에서 달성률 게이지와 목표/현재 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H56" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2625,10 +2625,10 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>배송</v>
+        <v>마감 카운트다운</v>
       </c>
       <c r="G57" t="str">
-        <v>'공구 상세' 화면에서 배송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 마감 카운트다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H57" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2657,13 +2657,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>정산 정보</v>
+        <v>단계별 가격표(N명 도달 시 추가 할인)</v>
       </c>
       <c r="G58" t="str">
-        <v>'공구 상세'에서 정산 정보를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 상세'의 단계별 가격표(N명 도달 시 추가 할인)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H58" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2689,10 +2689,10 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>진행자 프로필과 신뢰 지표</v>
+        <v>현재 적용가와 정가 대비 할인율</v>
       </c>
       <c r="G59" t="str">
-        <v>'공구 상세' 화면에서 진행자 프로필과 신뢰 지표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 현재 적용가와 정가 대비 할인율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H59" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2721,13 +2721,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>후기</v>
+        <v>실시간 참여 현황(최근 참여자·증가 애니메이션)</v>
       </c>
       <c r="G60" t="str">
-        <v>'공구 상세' 화면에서 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'의 실시간 참여 현황(최근 참여자·증가 애니메이션)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H60" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2753,10 +2753,10 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>별점</v>
+        <v>옵션 요약</v>
       </c>
       <c r="G61" t="str">
-        <v>'공구 상세' 화면에서 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 옵션 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H61" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2785,13 +2785,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>상품 문의</v>
+        <v>조건부 결제 안내(미달 시 자동 환불)</v>
       </c>
       <c r="G62" t="str">
-        <v>'공구 상세' 화면에서 상품 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'에서 조건부 결제 안내(미달 시 자동 환불)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H62" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2817,13 +2817,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>하단 고정 참여 버튼</v>
+        <v>배송</v>
       </c>
       <c r="G63" t="str">
-        <v>'공구 상세'에서 하단 고정 참여 버튼을 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 배송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H63" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2834,28 +2834,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B64" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>상품 상세정보·거래 조건</v>
+        <v/>
       </c>
       <c r="D64" t="str">
-        <v>DE-02</v>
+        <v/>
       </c>
       <c r="E64" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F64" t="str">
-        <v>상품 상세 설명</v>
+        <v>정산 정보</v>
       </c>
       <c r="G64" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 상품 상세 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'에서 정산 정보를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H64" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B65" t="str">
         <v/>
@@ -2881,10 +2881,10 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>이미지</v>
+        <v>진행자 프로필과 신뢰 지표</v>
       </c>
       <c r="G65" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 진행자 프로필과 신뢰 지표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H65" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B66" t="str">
         <v/>
@@ -2913,10 +2913,10 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>구성/옵션별 안내</v>
+        <v>후기</v>
       </c>
       <c r="G66" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 구성/옵션별 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세' 화면에서 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H66" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B67" t="str">
         <v/>
@@ -2945,13 +2945,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>배송 정보(성사 후 발송 일정·배송비·지역 제한)</v>
+        <v>별점</v>
       </c>
       <c r="G67" t="str">
-        <v>'상품 상세정보·거래 조건'의 배송 정보(성사 후 발송 일정·배송비·지역 제한)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'공구 상세' 화면에서 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H67" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B68" t="str">
         <v/>
@@ -2977,13 +2977,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)</v>
+        <v>상품 문의</v>
       </c>
       <c r="G68" t="str">
-        <v>'상품 상세정보·거래 조건'에서 조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 상세' 화면에서 상품 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H68" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B69" t="str">
         <v/>
@@ -3009,13 +3009,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>교환</v>
+        <v>하단 고정 참여 버튼</v>
       </c>
       <c r="G69" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 교환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 상세'에서 하단 고정 참여 버튼을 눌러 본다.</v>
       </c>
       <c r="H69" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3029,22 +3029,22 @@
         <v>SCN-006</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>상품 상세정보·거래 조건</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>DE-02</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F70" t="str">
-        <v>반품 규정</v>
+        <v>상품 상세 설명</v>
       </c>
       <c r="G70" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 반품 규정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 상품 상세 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H70" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3073,10 +3073,10 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>진행자</v>
+        <v>이미지</v>
       </c>
       <c r="G71" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 진행자가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H71" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3105,13 +3105,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>판매자 사업자 정보</v>
+        <v>구성/옵션별 안내</v>
       </c>
       <c r="G72" t="str">
-        <v>'상품 상세정보·거래 조건'의 판매자 사업자 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 구성/옵션별 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H72" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>유의사항 아코디언</v>
+        <v>배송 정보(성사 후 발송 일정·배송비·지역 제한)</v>
       </c>
       <c r="G73" t="str">
-        <v>'상품 상세정보·거래 조건' 화면에서 유의사항 아코디언이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세정보·거래 조건'의 배송 정보(성사 후 발송 일정·배송비·지역 제한)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H73" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3154,28 +3154,28 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B74" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C74" t="str">
-        <v>공구 마감 - 성사</v>
+        <v/>
       </c>
       <c r="D74" t="str">
-        <v>DE-03</v>
+        <v/>
       </c>
       <c r="E74" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F74" t="str">
-        <v>성사 축하 배너와 최종 달성 인원</v>
+        <v>조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)</v>
       </c>
       <c r="G74" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 성사 축하 배너와 최종 달성 인원이 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건'에서 조건부 결제 규정(성사 조건·자동 환불 시점·환불 방법)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H74" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B75" t="str">
         <v/>
@@ -3201,13 +3201,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>적용가</v>
+        <v>교환</v>
       </c>
       <c r="G75" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 적용가가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 교환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H75" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B76" t="str">
         <v/>
@@ -3233,13 +3233,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>확정된 할인 단계 안내</v>
+        <v>반품 규정</v>
       </c>
       <c r="G76" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 확정된 할인 단계 안내가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 반품 규정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H76" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B77" t="str">
         <v/>
@@ -3265,13 +3265,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>배송 예정 일정</v>
+        <v>진행자</v>
       </c>
       <c r="G77" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 배송 예정 일정이 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 진행자가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H77" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B78" t="str">
         <v/>
@@ -3297,13 +3297,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>내 참여 확인 유도</v>
+        <v>판매자 사업자 정보</v>
       </c>
       <c r="G78" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 내 참여 확인 유도가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건'의 판매자 사업자 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H78" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B79" t="str">
         <v/>
@@ -3329,13 +3329,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>후기 예고</v>
+        <v>유의사항 아코디언</v>
       </c>
       <c r="G79" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 후기 예고가 보이는지 확인한다.</v>
+        <v>'상품 상세정보·거래 조건' 화면에서 유의사항 아코디언이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H79" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3349,22 +3349,22 @@
         <v>SCN-007</v>
       </c>
       <c r="B80" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C80" t="str">
-        <v/>
+        <v>공구 마감 - 성사</v>
       </c>
       <c r="D80" t="str">
-        <v/>
+        <v>DE-03</v>
       </c>
       <c r="E80" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F80" t="str">
-        <v>비슷한 진행 중 공구 추천</v>
+        <v>성사 축하 배너와 최종 달성 인원</v>
       </c>
       <c r="G80" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 성사 축하 배너와 최종 달성 인원이 보이는지 확인한다.</v>
       </c>
       <c r="H80" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3393,10 +3393,10 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>재오픈 알림 신청</v>
+        <v>적용가</v>
       </c>
       <c r="G81" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 재오픈 알림 신청이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 적용가가 보이는지 확인한다.</v>
       </c>
       <c r="H81" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3410,25 +3410,25 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B82" t="str">
-        <v>공구 상세</v>
+        <v/>
       </c>
       <c r="C82" t="str">
-        <v>공구 마감 - 불발(미달)</v>
+        <v/>
       </c>
       <c r="D82" t="str">
-        <v>DE-04</v>
+        <v/>
       </c>
       <c r="E82" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F82" t="str">
-        <v>미달 안내 문구와 최종 인원/목표</v>
+        <v>확정된 할인 단계 안내</v>
       </c>
       <c r="G82" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 미달 안내 문구와 최종 인원/목표가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 확정된 할인 단계 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H82" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B83" t="str">
         <v/>
@@ -3457,10 +3457,10 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>자동 전액 환불 안내와 환불 예정 시점</v>
+        <v>배송 예정 일정</v>
       </c>
       <c r="G83" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 자동 전액 환불 안내와 환불 예정 시점이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 배송 예정 일정이 보이는지 확인한다.</v>
       </c>
       <c r="H83" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B84" t="str">
         <v/>
@@ -3489,10 +3489,10 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>환불 진행 상태 표시</v>
+        <v>내 참여 확인 유도</v>
       </c>
       <c r="G84" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 환불 진행 상태 표시가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 내 참여 확인 유도가 보이는지 확인한다.</v>
       </c>
       <c r="H84" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -3521,10 +3521,10 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>아쉬움 위로 카피</v>
+        <v>후기 예고</v>
       </c>
       <c r="G85" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 아쉬움 위로 카피가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 후기 예고가 보이는지 확인한다.</v>
       </c>
       <c r="H85" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -3553,10 +3553,10 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>재도전(재오픈) 알림 신청</v>
+        <v>비슷한 진행 중 공구 추천</v>
       </c>
       <c r="G86" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 재도전(재오픈) 알림 신청이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H86" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -3585,10 +3585,10 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>비슷한 진행 중 공구 추천</v>
+        <v>재오픈 알림 신청</v>
       </c>
       <c r="G87" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 성사' 화면이 나오게 한 뒤, 재오픈 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H87" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3605,22 +3605,22 @@
         <v>SCN-008</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>공구 상세</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>공구 마감 - 불발(미달)</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>DE-04</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F88" t="str">
-        <v>문의 링크</v>
+        <v>미달 안내 문구와 최종 인원/목표</v>
       </c>
       <c r="G88" t="str">
-        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 미달 안내 문구와 최종 인원/목표가 보이는지 확인한다.</v>
       </c>
       <c r="H88" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -3634,28 +3634,28 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B89" t="str">
-        <v>참여·결제</v>
+        <v/>
       </c>
       <c r="C89" t="str">
-        <v>옵션·수량 선택</v>
+        <v/>
       </c>
       <c r="D89" t="str">
-        <v>JO-01</v>
+        <v/>
       </c>
       <c r="E89" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F89" t="str">
-        <v>옵션 조합 선택(색상·용량 등)</v>
+        <v>자동 전액 환불 안내와 환불 예정 시점</v>
       </c>
       <c r="G89" t="str">
-        <v>'옵션·수량 선택' 화면에서 옵션 조합 선택(색상·용량 등)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 자동 전액 환불 안내와 환불 예정 시점이 보이는지 확인한다.</v>
       </c>
       <c r="H89" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B90" t="str">
         <v/>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>수량 선택</v>
+        <v>환불 진행 상태 표시</v>
       </c>
       <c r="G90" t="str">
-        <v>'옵션·수량 선택' 화면에서 수량 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 환불 진행 상태 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H90" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B91" t="str">
         <v/>
@@ -3713,13 +3713,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>현재 적용 단계 가격 반영</v>
+        <v>아쉬움 위로 카피</v>
       </c>
       <c r="G91" t="str">
-        <v>'옵션·수량 선택'의 현재 적용 단계 가격 반영이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 아쉬움 위로 카피가 보이는지 확인한다.</v>
       </c>
       <c r="H91" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -3745,13 +3745,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>'내 참여로 달성률 얼마나 오르는지' 안내</v>
+        <v>재도전(재오픈) 알림 신청</v>
       </c>
       <c r="G92" t="str">
-        <v>'옵션·수량 선택' 화면에서 '내 참여로 달성률 얼마나 오르는지' 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 재도전(재오픈) 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H92" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -3777,13 +3777,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>배송지 확인</v>
+        <v>비슷한 진행 중 공구 추천</v>
       </c>
       <c r="G93" t="str">
-        <v>'옵션·수량 선택' 화면에서 배송지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 비슷한 진행 중 공구 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H93" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -3809,13 +3809,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>예상 결제 금액</v>
+        <v>문의 링크</v>
       </c>
       <c r="G94" t="str">
-        <v>'옵션·수량 선택'에서 예상 결제 금액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '공구 마감 - 불발(미달)' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H94" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3829,25 +3829,25 @@
         <v>SCN-009</v>
       </c>
       <c r="B95" t="str">
-        <v/>
+        <v>참여·결제</v>
       </c>
       <c r="C95" t="str">
-        <v/>
+        <v>옵션·수량 선택</v>
       </c>
       <c r="D95" t="str">
-        <v/>
+        <v>JO-01</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F95" t="str">
-        <v>다음 단계까지 남은 인원 안내</v>
+        <v>옵션 조합 선택(색상·용량 등)</v>
       </c>
       <c r="G95" t="str">
-        <v>'옵션·수량 선택'의 다음 단계까지 남은 인원 안내가 실제 데이터와 같은지 대조한다.</v>
+        <v>'옵션·수량 선택' 화면에서 옵션 조합 선택(색상·용량 등)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H95" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3873,10 +3873,10 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>관심 공구 담기</v>
+        <v>수량 선택</v>
       </c>
       <c r="G96" t="str">
-        <v>'옵션·수량 선택' 화면에서 관심 공구 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 수량 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H96" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3905,13 +3905,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>결제로 이동</v>
+        <v>현재 적용 단계 가격 반영</v>
       </c>
       <c r="G97" t="str">
-        <v>'옵션·수량 선택'에서 결제로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'옵션·수량 선택'의 현재 적용 단계 가격 반영이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H97" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3922,25 +3922,25 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B98" t="str">
-        <v>참여·결제</v>
+        <v/>
       </c>
       <c r="C98" t="str">
-        <v>참여 결제</v>
+        <v/>
       </c>
       <c r="D98" t="str">
-        <v>JO-02</v>
+        <v/>
       </c>
       <c r="E98" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F98" t="str">
-        <v>참여 상품</v>
+        <v>'내 참여로 달성률 얼마나 오르는지' 안내</v>
       </c>
       <c r="G98" t="str">
-        <v>'참여 결제' 화면에서 참여 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 '내 참여로 달성률 얼마나 오르는지' 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B99" t="str">
         <v/>
@@ -3969,10 +3969,10 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>옵션</v>
+        <v>배송지 확인</v>
       </c>
       <c r="G99" t="str">
-        <v>'참여 결제' 화면에서 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 배송지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H99" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B100" t="str">
         <v/>
@@ -4001,13 +4001,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>수량 요약</v>
+        <v>예상 결제 금액</v>
       </c>
       <c r="G100" t="str">
-        <v>'참여 결제' 화면에서 수량 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택'에서 예상 결제 금액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H100" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B101" t="str">
         <v/>
@@ -4033,13 +4033,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>배송지 입력/선택</v>
+        <v>다음 단계까지 남은 인원 안내</v>
       </c>
       <c r="G101" t="str">
-        <v>'참여 결제'의 배송지 입력/선택에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'옵션·수량 선택'의 다음 단계까지 남은 인원 안내가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H101" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B102" t="str">
         <v/>
@@ -4065,10 +4065,10 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>쿠폰</v>
+        <v>관심 공구 담기</v>
       </c>
       <c r="G102" t="str">
-        <v>'참여 결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택' 화면에서 관심 공구 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H102" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B103" t="str">
         <v/>
@@ -4097,13 +4097,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>적립금 적용</v>
+        <v>결제로 이동</v>
       </c>
       <c r="G103" t="str">
-        <v>'참여 결제' 화면에서 적립금 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·수량 선택'에서 결제로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H103" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4117,25 +4117,25 @@
         <v>SCN-010</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>참여·결제</v>
       </c>
       <c r="C104" t="str">
-        <v/>
+        <v>참여 결제</v>
       </c>
       <c r="D104" t="str">
-        <v/>
+        <v>JO-02</v>
       </c>
       <c r="E104" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F104" t="str">
-        <v>결제 수단 선택</v>
+        <v>참여 상품</v>
       </c>
       <c r="G104" t="str">
-        <v>'참여 결제'에서 결제 수단 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 결제' 화면에서 참여 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H104" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4161,13 +4161,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의</v>
+        <v>옵션</v>
       </c>
       <c r="G105" t="str">
-        <v>'참여 결제'에서 조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 결제' 화면에서 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H105" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4193,13 +4193,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>개인정보 제3자 제공(진행자) 동의</v>
+        <v>수량 요약</v>
       </c>
       <c r="G106" t="str">
-        <v>'참여 결제'의 개인정보 제3자 제공(진행자) 동의가 실제 데이터와 같은지 대조한다.</v>
+        <v>'참여 결제' 화면에서 수량 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H106" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -4225,13 +4225,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>최종 금액과 예상 성사 시 추가할인 안내</v>
+        <v>배송지 입력/선택</v>
       </c>
       <c r="G107" t="str">
-        <v>'참여 결제'의 최종 금액과 예상 성사 시 추가할인 안내가 실제 데이터와 같은지 대조한다.</v>
+        <v>'참여 결제'의 배송지 입력/선택에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H107" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4257,13 +4257,13 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>결제 버튼</v>
+        <v>쿠폰</v>
       </c>
       <c r="G108" t="str">
-        <v>'참여 결제'에서 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H108" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4274,25 +4274,25 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B109" t="str">
-        <v>참여·결제</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>참여 완료</v>
+        <v/>
       </c>
       <c r="D109" t="str">
-        <v>JO-03</v>
+        <v/>
       </c>
       <c r="E109" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F109" t="str">
-        <v>참여 완료 메시지와 참여 번호</v>
+        <v>적립금 적용</v>
       </c>
       <c r="G109" t="str">
-        <v>'참여 완료' 화면에서 참여 완료 메시지와 참여 번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 결제' 화면에서 적립금 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H109" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B110" t="str">
         <v/>
@@ -4321,13 +4321,13 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>갱신된 달성률과 남은 시간</v>
+        <v>결제 수단 선택</v>
       </c>
       <c r="G110" t="str">
-        <v>'참여 완료'의 갱신된 달성률과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
+        <v>'참여 결제'에서 결제 수단 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H110" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B111" t="str">
         <v/>
@@ -4353,13 +4353,13 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>'친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내</v>
+        <v>조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의</v>
       </c>
       <c r="G111" t="str">
-        <v>'참여 완료'에서 '친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내를 눌러 본다.</v>
+        <v>'참여 결제'에서 조건부 결제 고지(지금 결제·미달 시 자동 전액 환불) 필수 동의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H111" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B112" t="str">
         <v/>
@@ -4385,13 +4385,13 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>성사/미달 시 각각 어떻게 되는지 안내</v>
+        <v>개인정보 제3자 제공(진행자) 동의</v>
       </c>
       <c r="G112" t="str">
-        <v>'참여 완료' 화면에서 성사/미달 시 각각 어떻게 되는지 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 결제'의 개인정보 제3자 제공(진행자) 동의가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H112" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B113" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>내 참여 상세로 이동</v>
+        <v>최종 금액과 예상 성사 시 추가할인 안내</v>
       </c>
       <c r="G113" t="str">
-        <v>'참여 완료'에서 내 참여 상세로 이동을 눌러 본다.</v>
+        <v>'참여 결제'의 최종 금액과 예상 성사 시 추가할인 안내가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H113" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B114" t="str">
         <v/>
@@ -4449,13 +4449,13 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>다른 공구 추천</v>
+        <v>결제 버튼</v>
       </c>
       <c r="G114" t="str">
-        <v>'참여 완료' 화면에서 다른 공구 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 결제'에서 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H114" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4466,28 +4466,28 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B115" t="str">
         <v>참여·결제</v>
       </c>
       <c r="C115" t="str">
-        <v>결제 실패</v>
+        <v>참여 완료</v>
       </c>
       <c r="D115" t="str">
-        <v>JO-04</v>
+        <v>JO-03</v>
       </c>
       <c r="E115" t="str">
-        <v>예외·상태</v>
+        <v>기본</v>
       </c>
       <c r="F115" t="str">
-        <v>실패 사유를 쉬운 문장으로 안내</v>
+        <v>참여 완료 메시지와 참여 번호</v>
       </c>
       <c r="G115" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 사유를 쉬운 문장으로 안내가 보이는지 확인한다.</v>
+        <v>'참여 완료' 화면에서 참여 완료 메시지와 참여 번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H115" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B116" t="str">
         <v/>
@@ -4513,13 +4513,13 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>참여 정보 유지 안내</v>
+        <v>갱신된 달성률과 남은 시간</v>
       </c>
       <c r="G116" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 참여 정보 유지 안내가 보이는지 확인한다.</v>
+        <v>'참여 완료'의 갱신된 달성률과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H116" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B117" t="str">
         <v/>
@@ -4545,13 +4545,13 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>다시 시도 버튼</v>
+        <v>'친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내</v>
       </c>
       <c r="G117" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
+        <v>'참여 완료'에서 '친구를 초대해 성사에 힘 보태기' 공유 링크(카톡·URL 복사)와 초대 보상 안내를 눌러 본다.</v>
       </c>
       <c r="H117" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B118" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>다른 결제 수단 선택</v>
+        <v>성사/미달 시 각각 어떻게 되는지 안내</v>
       </c>
       <c r="G118" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 선택이 보이는지 확인한다.</v>
+        <v>'참여 완료' 화면에서 성사/미달 시 각각 어떻게 되는지 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H118" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B119" t="str">
         <v/>
@@ -4609,13 +4609,13 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>마감 임박 시 서두름 안내</v>
+        <v>내 참여 상세로 이동</v>
       </c>
       <c r="G119" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 마감 임박 시 서두름 안내가 보이는지 확인한다.</v>
+        <v>'참여 완료'에서 내 참여 상세로 이동을 눌러 본다.</v>
       </c>
       <c r="H119" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B120" t="str">
         <v/>
@@ -4641,13 +4641,13 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>문의 링크</v>
+        <v>다른 공구 추천</v>
       </c>
       <c r="G120" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
+        <v>'참여 완료' 화면에서 다른 공구 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H120" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4658,28 +4658,28 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B121" t="str">
-        <v>내 공구함</v>
+        <v>참여·결제</v>
       </c>
       <c r="C121" t="str">
-        <v>내 공구함</v>
+        <v>결제 실패</v>
       </c>
       <c r="D121" t="str">
-        <v>MY-01</v>
+        <v>JO-04</v>
       </c>
       <c r="E121" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F121" t="str">
-        <v>상태 탭(진행 중·성사·불발·배송/완료)</v>
+        <v>실패 사유를 쉬운 문장으로 안내</v>
       </c>
       <c r="G121" t="str">
-        <v>'내 공구함'에서 상태 탭(진행 중·성사·불발·배송/완료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 사유를 쉬운 문장으로 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H121" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B122" t="str">
         <v/>
@@ -4705,13 +4705,13 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)</v>
+        <v>참여 정보 유지 안내</v>
       </c>
       <c r="G122" t="str">
-        <v>'내 공구함'의 참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 참여 정보 유지 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H122" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B123" t="str">
         <v/>
@@ -4737,13 +4737,13 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>진행 중은 달성률</v>
+        <v>다시 시도 버튼</v>
       </c>
       <c r="G123" t="str">
-        <v>'내 공구함' 화면에서 진행 중은 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H123" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B124" t="str">
         <v/>
@@ -4769,13 +4769,13 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>공유 유도</v>
+        <v>다른 결제 수단 선택</v>
       </c>
       <c r="G124" t="str">
-        <v>'내 공구함' 화면에서 공유 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 선택이 보이는지 확인한다.</v>
       </c>
       <c r="H124" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B125" t="str">
         <v/>
@@ -4801,13 +4801,13 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>불발은 환불 상태</v>
+        <v>마감 임박 시 서두름 안내</v>
       </c>
       <c r="G125" t="str">
-        <v>'내 공구함'에서 불발은 환불 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 마감 임박 시 서두름 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H125" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B126" t="str">
         <v/>
@@ -4833,13 +4833,13 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>배송은 송장</v>
+        <v>문의 링크</v>
       </c>
       <c r="G126" t="str">
-        <v>'내 공구함' 화면에서 배송은 송장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 문의 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H126" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4853,25 +4853,25 @@
         <v>SCN-013</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C127" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="D127" t="str">
-        <v/>
+        <v>MY-01</v>
       </c>
       <c r="E127" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F127" t="str">
-        <v>배송 조회</v>
+        <v>상태 탭(진행 중·성사·불발·배송/완료)</v>
       </c>
       <c r="G127" t="str">
-        <v>'내 공구함' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함'에서 상태 탭(진행 중·성사·불발·배송/완료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H127" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4897,13 +4897,13 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>후기 미작성 알림</v>
+        <v>참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)</v>
       </c>
       <c r="G128" t="str">
-        <v>'내 공구함'의 후기 미작성 알림에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 공구함'의 참여 공구 카드(상품·현재 달성률·남은 시간·내 결제액·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H128" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -4929,13 +4929,13 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>정렬</v>
+        <v>진행 중은 달성률</v>
       </c>
       <c r="G129" t="str">
-        <v>'내 공구함'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 공구함' 화면에서 진행 중은 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H129" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -4961,13 +4961,13 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>검색</v>
+        <v>공유 유도</v>
       </c>
       <c r="G130" t="str">
-        <v>'내 공구함'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 공구함' 화면에서 공유 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H130" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -4978,28 +4978,28 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B131" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C131" t="str">
-        <v>참여 상세</v>
+        <v/>
       </c>
       <c r="D131" t="str">
-        <v>MY-02</v>
+        <v/>
       </c>
       <c r="E131" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F131" t="str">
-        <v>공구</v>
+        <v>불발은 환불 상태</v>
       </c>
       <c r="G131" t="str">
-        <v>'참여 상세' 화면에서 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함'에서 불발은 환불 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H131" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B132" t="str">
         <v/>
@@ -5025,10 +5025,10 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>상품 요약</v>
+        <v>배송은 송장</v>
       </c>
       <c r="G132" t="str">
-        <v>'참여 상세' 화면에서 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함' 화면에서 배송은 송장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H132" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B133" t="str">
         <v/>
@@ -5057,13 +5057,13 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>내 참여 정보(옵션·수량·결제액·참여일)</v>
+        <v>배송 조회</v>
       </c>
       <c r="G133" t="str">
-        <v>'참여 상세'의 내 참여 정보(옵션·수량·결제액·참여일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 공구함' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H133" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B134" t="str">
         <v/>
@@ -5089,13 +5089,13 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)</v>
+        <v>후기 미작성 알림</v>
       </c>
       <c r="G134" t="str">
-        <v>'참여 상세'의 진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 공구함'의 후기 미작성 알림에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H134" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B135" t="str">
         <v/>
@@ -5121,13 +5121,13 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>현재 달성률과 남은 시간(진행 중)</v>
+        <v>정렬</v>
       </c>
       <c r="G135" t="str">
-        <v>'참여 상세'의 현재 달성률과 남은 시간(진행 중)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 공구함'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H135" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B136" t="str">
         <v/>
@@ -5153,13 +5153,13 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>성사 시 차액 환급 내역</v>
+        <v>검색</v>
       </c>
       <c r="G136" t="str">
-        <v>'참여 상세' 화면에서 성사 시 차액 환급 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 공구함'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H136" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5173,22 +5173,22 @@
         <v>SCN-014</v>
       </c>
       <c r="B137" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C137" t="str">
-        <v/>
+        <v>참여 상세</v>
       </c>
       <c r="D137" t="str">
-        <v/>
+        <v>MY-02</v>
       </c>
       <c r="E137" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F137" t="str">
-        <v>배송 조회</v>
+        <v>공구</v>
       </c>
       <c r="G137" t="str">
-        <v>'참여 상세' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세' 화면에서 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H137" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5217,13 +5217,13 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>취소</v>
+        <v>상품 요약</v>
       </c>
       <c r="G138" t="str">
-        <v>'참여 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H138" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -5249,13 +5249,13 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>환불 요청</v>
+        <v>내 참여 정보(옵션·수량·결제액·참여일)</v>
       </c>
       <c r="G139" t="str">
-        <v>'참여 상세'에서 환불 요청을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세'의 내 참여 정보(옵션·수량·결제액·참여일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H139" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5281,13 +5281,13 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>영수증</v>
+        <v>진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)</v>
       </c>
       <c r="G140" t="str">
-        <v>'참여 상세' 화면에서 영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세'의 진행 상태 타임라인(참여→마감→성사/불발→발주→배송→완료)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H140" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -5313,13 +5313,13 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>문의</v>
+        <v>현재 달성률과 남은 시간(진행 중)</v>
       </c>
       <c r="G141" t="str">
-        <v>'참여 상세' 화면에서 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세'의 현재 달성률과 남은 시간(진행 중)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H141" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5330,28 +5330,28 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B142" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C142" t="str">
-        <v>참여 취소·환불 요청</v>
+        <v/>
       </c>
       <c r="D142" t="str">
-        <v>MY-03</v>
+        <v/>
       </c>
       <c r="E142" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F142" t="str">
-        <v>취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)</v>
+        <v>성사 시 차액 환급 내역</v>
       </c>
       <c r="G142" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 성사 시 차액 환급 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H142" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B143" t="str">
         <v/>
@@ -5377,13 +5377,13 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>취소 시 달성률 영향 안내</v>
+        <v>배송 조회</v>
       </c>
       <c r="G143" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 시 달성률 영향 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세' 화면에서 배송 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H143" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B144" t="str">
         <v/>
@@ -5409,10 +5409,10 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>취소 사유 선택</v>
+        <v>취소</v>
       </c>
       <c r="G144" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H144" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B145" t="str">
         <v/>
@@ -5441,10 +5441,10 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>환불 예정 금액과 수단</v>
+        <v>환불 요청</v>
       </c>
       <c r="G145" t="str">
-        <v>'참여 취소·환불 요청'에서 환불 예정 금액과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 상세'에서 환불 요청을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H145" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -5473,10 +5473,10 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>시점</v>
+        <v>영수증</v>
       </c>
       <c r="G146" t="str">
-        <v>'참여 취소·환불 요청' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세' 화면에서 영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H146" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -5505,10 +5505,10 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>성사 후 반품은 배송 규정 안내</v>
+        <v>문의</v>
       </c>
       <c r="G147" t="str">
-        <v>'참여 취소·환불 요청' 화면에서 성사 후 반품은 배송 규정 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여 상세' 화면에서 문의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H147" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5525,22 +5525,22 @@
         <v>SCN-015</v>
       </c>
       <c r="B148" t="str">
-        <v/>
+        <v>내 공구함</v>
       </c>
       <c r="C148" t="str">
-        <v/>
+        <v>참여 취소·환불 요청</v>
       </c>
       <c r="D148" t="str">
-        <v/>
+        <v>MY-03</v>
       </c>
       <c r="E148" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F148" t="str">
-        <v>취소 확정 버튼(확인 모달)</v>
+        <v>취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)</v>
       </c>
       <c r="G148" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 확정 버튼(확인 모달)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 가능 여부 안내(마감 전 자유 취소·성사 후 규정 적용)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H148" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -5569,10 +5569,10 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>취소 대신 유지 유도</v>
+        <v>취소 시 달성률 영향 안내</v>
       </c>
       <c r="G149" t="str">
-        <v>'참여 취소·환불 요청'에서 취소 대신 유지 유도를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 시 달성률 영향 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H149" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -5586,28 +5586,28 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B150" t="str">
-        <v>내 공구함</v>
+        <v/>
       </c>
       <c r="C150" t="str">
-        <v>내 공구함 - 비어 있음</v>
+        <v/>
       </c>
       <c r="D150" t="str">
-        <v>MY-04</v>
+        <v/>
       </c>
       <c r="E150" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F150" t="str">
-        <v>참여 내역 없음 안내와 일러스트</v>
+        <v>취소 사유 선택</v>
       </c>
       <c r="G150" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 참여 내역 없음 안내와 일러스트가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H150" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -5633,13 +5633,13 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>공구 둘러보기 CTA</v>
+        <v>환불 예정 금액과 수단</v>
       </c>
       <c r="G151" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 공구 둘러보기 CTA가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 환불 예정 금액과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H151" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -5665,13 +5665,13 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>첫 참여 할인 쿠폰 안내</v>
+        <v>시점</v>
       </c>
       <c r="G152" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 첫 참여 할인 쿠폰 안내가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H152" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -5697,13 +5697,13 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>인기</v>
+        <v>성사 후 반품은 배송 규정 안내</v>
       </c>
       <c r="G153" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 인기가 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청' 화면에서 성사 후 반품은 배송 규정 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H153" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -5729,13 +5729,13 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>마감 임박 공구 추천</v>
+        <v>취소 확정 버튼(확인 모달)</v>
       </c>
       <c r="G154" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 마감 임박 공구 추천이 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 확정 버튼(확인 모달)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H154" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -5761,13 +5761,13 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>관심 공구로 이동</v>
+        <v>취소 대신 유지 유도</v>
       </c>
       <c r="G155" t="str">
-        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 관심 공구로 이동이 보이는지 확인한다.</v>
+        <v>'참여 취소·환불 요청'에서 취소 대신 유지 유도를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H155" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -5778,28 +5778,28 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B156" t="str">
-        <v>후기·문의·알림</v>
+        <v>내 공구함</v>
       </c>
       <c r="C156" t="str">
-        <v>후기 작성·목록</v>
+        <v>내 공구함 - 비어 있음</v>
       </c>
       <c r="D156" t="str">
-        <v>RV-01</v>
+        <v>MY-04</v>
       </c>
       <c r="E156" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F156" t="str">
-        <v>별점 선택</v>
+        <v>참여 내역 없음 안내와 일러스트</v>
       </c>
       <c r="G156" t="str">
-        <v>'후기 작성·목록' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 참여 내역 없음 안내와 일러스트가 보이는지 확인한다.</v>
       </c>
       <c r="H156" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -5825,13 +5825,13 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>포토</v>
+        <v>공구 둘러보기 CTA</v>
       </c>
       <c r="G157" t="str">
-        <v>'후기 작성·목록' 화면에서 포토가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 공구 둘러보기 CTA가 보이는지 확인한다.</v>
       </c>
       <c r="H157" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -5857,13 +5857,13 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>동영상 첨부</v>
+        <v>첫 참여 할인 쿠폰 안내</v>
       </c>
       <c r="G158" t="str">
-        <v>'후기 작성·목록'의 동영상 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 첫 참여 할인 쿠폰 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H158" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -5889,13 +5889,13 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>옵션 선택 정보 자동 표시</v>
+        <v>인기</v>
       </c>
       <c r="G159" t="str">
-        <v>'후기 작성·목록'의 옵션 선택 정보 자동 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 인기가 보이는지 확인한다.</v>
       </c>
       <c r="H159" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -5921,13 +5921,13 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>후기 본문</v>
+        <v>마감 임박 공구 추천</v>
       </c>
       <c r="G160" t="str">
-        <v>'후기 작성·목록' 화면에서 후기 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 마감 임박 공구 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H160" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>재구매 의사</v>
+        <v>관심 공구로 이동</v>
       </c>
       <c r="G161" t="str">
-        <v>'후기 작성·목록' 화면에서 재구매 의사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '내 공구함 - 비어 있음' 화면이 나오게 한 뒤, 관심 공구로 이동이 보이는지 확인한다.</v>
       </c>
       <c r="H161" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -5973,22 +5973,22 @@
         <v>SCN-017</v>
       </c>
       <c r="B162" t="str">
-        <v/>
+        <v>후기·문의·알림</v>
       </c>
       <c r="C162" t="str">
-        <v/>
+        <v>후기 작성·목록</v>
       </c>
       <c r="D162" t="str">
-        <v/>
+        <v>RV-01</v>
       </c>
       <c r="E162" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F162" t="str">
-        <v>도움돼요 추천</v>
+        <v>별점 선택</v>
       </c>
       <c r="G162" t="str">
-        <v>'후기 작성·목록' 화면에서 도움돼요 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H162" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6017,13 +6017,13 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>후기 목록(별점 분포·정렬·포토후기 필터)</v>
+        <v>포토</v>
       </c>
       <c r="G163" t="str">
-        <v>'후기 작성·목록'의 후기 목록(별점 분포·정렬·포토후기 필터)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 포토가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H163" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6049,13 +6049,13 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>진행자 답글</v>
+        <v>동영상 첨부</v>
       </c>
       <c r="G164" t="str">
-        <v>'후기 작성·목록' 화면에서 진행자 답글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록'의 동영상 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H164" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -6081,13 +6081,13 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>신고</v>
+        <v>옵션 선택 정보 자동 표시</v>
       </c>
       <c r="G165" t="str">
-        <v>'후기 작성·목록' 화면에서 신고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록'의 옵션 선택 정보 자동 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H165" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -6113,13 +6113,13 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>후기 작성 보상 안내</v>
+        <v>후기 본문</v>
       </c>
       <c r="G166" t="str">
-        <v>'후기 작성·목록'의 후기 작성 보상 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 작성·목록' 화면에서 후기 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H166" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -6130,28 +6130,28 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B167" t="str">
-        <v>후기·문의·알림</v>
+        <v/>
       </c>
       <c r="C167" t="str">
-        <v>상품 문의(Q&amp;A)</v>
+        <v/>
       </c>
       <c r="D167" t="str">
-        <v>RV-02</v>
+        <v/>
       </c>
       <c r="E167" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F167" t="str">
-        <v>문의 작성(유형 선택·비공개 옵션)</v>
+        <v>재구매 의사</v>
       </c>
       <c r="G167" t="str">
-        <v>'상품 문의(Q&amp;A)'의 문의 작성(유형 선택·비공개 옵션)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 작성·목록' 화면에서 재구매 의사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H167" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B168" t="str">
         <v/>
@@ -6177,13 +6177,13 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>문의 목록(질문·답변·상태 배지)</v>
+        <v>도움돼요 추천</v>
       </c>
       <c r="G168" t="str">
-        <v>'상품 문의(Q&amp;A)'의 문의 목록(질문·답변·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 도움돼요 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H168" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>자주 묻는 질문 상단 노출</v>
+        <v>후기 목록(별점 분포·정렬·포토후기 필터)</v>
       </c>
       <c r="G169" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 자주 묻는 질문 상단 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록'의 후기 목록(별점 분포·정렬·포토후기 필터)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H169" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B170" t="str">
         <v/>
@@ -6241,10 +6241,10 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>답변 알림 안내</v>
+        <v>진행자 답글</v>
       </c>
       <c r="G170" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 답변 알림 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성·목록' 화면에서 진행자 답글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H170" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B171" t="str">
         <v/>
@@ -6273,13 +6273,13 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>검색</v>
+        <v>신고</v>
       </c>
       <c r="G171" t="str">
-        <v>'상품 문의(Q&amp;A)'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 작성·목록' 화면에서 신고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H171" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B172" t="str">
         <v/>
@@ -6305,13 +6305,13 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>진행자 답변 대기 표시</v>
+        <v>후기 작성 보상 안내</v>
       </c>
       <c r="G172" t="str">
-        <v>'상품 문의(Q&amp;A)'의 진행자 답변 대기 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'후기 작성·목록'의 후기 작성 보상 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H172" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -6325,25 +6325,25 @@
         <v>SCN-018</v>
       </c>
       <c r="B173" t="str">
-        <v/>
+        <v>후기·문의·알림</v>
       </c>
       <c r="C173" t="str">
-        <v/>
+        <v>상품 문의(Q&amp;A)</v>
       </c>
       <c r="D173" t="str">
-        <v/>
+        <v>RV-02</v>
       </c>
       <c r="E173" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F173" t="str">
-        <v>성사</v>
+        <v>문의 작성(유형 선택·비공개 옵션)</v>
       </c>
       <c r="G173" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 성사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'의 문의 작성(유형 선택·비공개 옵션)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H173" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -6369,13 +6369,13 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>배송 관련 문의 분류</v>
+        <v>문의 목록(질문·답변·상태 배지)</v>
       </c>
       <c r="G174" t="str">
-        <v>'상품 문의(Q&amp;A)' 화면에서 배송 관련 문의 분류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'의 문의 목록(질문·답변·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H174" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -6386,28 +6386,28 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B175" t="str">
-        <v>후기·문의·알림</v>
+        <v/>
       </c>
       <c r="C175" t="str">
-        <v>관심 공구·알림함</v>
+        <v/>
       </c>
       <c r="D175" t="str">
-        <v>RV-03</v>
+        <v/>
       </c>
       <c r="E175" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F175" t="str">
-        <v>찜한 공구 목록(달성률·남은 시간·상태 변화 표시)</v>
+        <v>자주 묻는 질문 상단 노출</v>
       </c>
       <c r="G175" t="str">
-        <v>'관심 공구·알림함'의 찜한 공구 목록(달성률·남은 시간·상태 변화 표시)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 자주 묻는 질문 상단 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -6433,13 +6433,13 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>오픈 예정 공구 알림 신청 목록</v>
+        <v>답변 알림 안내</v>
       </c>
       <c r="G176" t="str">
-        <v>'관심 공구·알림함'의 오픈 예정 공구 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 답변 알림 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -6465,13 +6465,13 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>알림 내역(성사·마감 임박·재오픈·배송)</v>
+        <v>검색</v>
       </c>
       <c r="G177" t="str">
-        <v>'관심 공구·알림함' 화면에서 알림 내역(성사·마감 임박·재오픈·배송)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H177" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B178" t="str">
         <v/>
@@ -6497,13 +6497,13 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>읽음 처리</v>
+        <v>진행자 답변 대기 표시</v>
       </c>
       <c r="G178" t="str">
-        <v>'관심 공구·알림함' 화면에서 읽음 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)'의 진행자 답변 대기 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H178" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6514,7 +6514,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B179" t="str">
         <v/>
@@ -6529,10 +6529,10 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>관심 공구에서 바로 참여</v>
+        <v>성사</v>
       </c>
       <c r="G179" t="str">
-        <v>'관심 공구·알림함' 화면에서 관심 공구에서 바로 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 성사가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H179" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B180" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>알림 설정 링크</v>
+        <v>배송 관련 문의 분류</v>
       </c>
       <c r="G180" t="str">
-        <v>'관심 공구·알림함'에서 알림 설정 링크를 눌러 본다.</v>
+        <v>'상품 문의(Q&amp;A)' 화면에서 배송 관련 문의 분류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H180" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -6578,28 +6578,28 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B181" t="str">
-        <v>계정</v>
+        <v>후기·문의·알림</v>
       </c>
       <c r="C181" t="str">
-        <v>로그인·회원가입</v>
+        <v>관심 공구·알림함</v>
       </c>
       <c r="D181" t="str">
-        <v>AC-01</v>
+        <v>RV-03</v>
       </c>
       <c r="E181" t="str">
         <v>기본</v>
       </c>
       <c r="F181" t="str">
-        <v>소셜 로그인(카카오·네이버·구글)</v>
+        <v>찜한 공구 목록(달성률·남은 시간·상태 변화 표시)</v>
       </c>
       <c r="G181" t="str">
-        <v>'로그인·회원가입'에서 소셜 로그인(카카오·네이버·구글)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'관심 공구·알림함'의 찜한 공구 목록(달성률·남은 시간·상태 변화 표시)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H181" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B182" t="str">
         <v/>
@@ -6625,13 +6625,13 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>이메일 로그인</v>
+        <v>오픈 예정 공구 알림 신청 목록</v>
       </c>
       <c r="G182" t="str">
-        <v>'로그인·회원가입'에서 이메일 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'관심 공구·알림함'의 오픈 예정 공구 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H182" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B183" t="str">
         <v/>
@@ -6657,13 +6657,13 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>회원가입 전환</v>
+        <v>알림 내역(성사·마감 임박·재오픈·배송)</v>
       </c>
       <c r="G183" t="str">
-        <v>'로그인·회원가입'에서 회원가입 전환을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'관심 공구·알림함' 화면에서 알림 내역(성사·마감 임박·재오픈·배송)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H183" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B184" t="str">
         <v/>
@@ -6689,10 +6689,10 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>휴대폰 인증</v>
+        <v>읽음 처리</v>
       </c>
       <c r="G184" t="str">
-        <v>'로그인·회원가입' 화면에서 휴대폰 인증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'관심 공구·알림함' 화면에서 읽음 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H184" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,10 +6721,10 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>약관</v>
+        <v>관심 공구에서 바로 참여</v>
       </c>
       <c r="G185" t="str">
-        <v>'로그인·회원가입' 화면에서 약관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'관심 공구·알림함' 화면에서 관심 공구에서 바로 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H185" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B186" t="str">
         <v/>
@@ -6753,13 +6753,13 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>개인정보</v>
+        <v>알림 설정 링크</v>
       </c>
       <c r="G186" t="str">
-        <v>'로그인·회원가입'의 개인정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'관심 공구·알림함'에서 알림 설정 링크를 눌러 본다.</v>
       </c>
       <c r="H186" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -6773,25 +6773,25 @@
         <v>SCN-020</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C187" t="str">
-        <v/>
+        <v>로그인·회원가입</v>
       </c>
       <c r="D187" t="str">
-        <v/>
+        <v>AC-01</v>
       </c>
       <c r="E187" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F187" t="str">
-        <v>마케팅 수신 동의</v>
+        <v>소셜 로그인(카카오·네이버·구글)</v>
       </c>
       <c r="G187" t="str">
-        <v>'로그인·회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'에서 소셜 로그인(카카오·네이버·구글)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H187" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6817,13 +6817,13 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>첫 가입 쿠폰 안내</v>
+        <v>이메일 로그인</v>
       </c>
       <c r="G188" t="str">
-        <v>'로그인·회원가입' 화면에서 첫 가입 쿠폰 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'에서 이메일 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H188" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -6849,13 +6849,13 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>비회원 주문 조회</v>
+        <v>회원가입 전환</v>
       </c>
       <c r="G189" t="str">
-        <v>'로그인·회원가입' 화면에서 비회원 주문 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'에서 회원가입 전환을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H189" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -6881,10 +6881,10 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>비밀번호 찾기</v>
+        <v>휴대폰 인증</v>
       </c>
       <c r="G190" t="str">
-        <v>'로그인·회원가입' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 휴대폰 인증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H190" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6898,25 +6898,25 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B191" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C191" t="str">
-        <v>내 정보·배송지</v>
+        <v/>
       </c>
       <c r="D191" t="str">
-        <v>AC-02</v>
+        <v/>
       </c>
       <c r="E191" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F191" t="str">
-        <v>프로필(닉네임·프로필 사진)</v>
+        <v>약관</v>
       </c>
       <c r="G191" t="str">
-        <v>'내 정보·배송지' 화면에서 프로필(닉네임·프로필 사진)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 약관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H191" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B192" t="str">
         <v/>
@@ -6945,13 +6945,13 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>휴대폰</v>
+        <v>개인정보</v>
       </c>
       <c r="G192" t="str">
-        <v>'내 정보·배송지' 화면에서 휴대폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입'의 개인정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H192" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -6977,10 +6977,10 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>이메일</v>
+        <v>마케팅 수신 동의</v>
       </c>
       <c r="G193" t="str">
-        <v>'내 정보·배송지' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H193" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B194" t="str">
         <v/>
@@ -7009,13 +7009,13 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)</v>
+        <v>첫 가입 쿠폰 안내</v>
       </c>
       <c r="G194" t="str">
-        <v>'내 정보·배송지'의 배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 첫 가입 쿠폰 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H194" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -7041,13 +7041,13 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>결제 수단 관리</v>
+        <v>비회원 주문 조회</v>
       </c>
       <c r="G195" t="str">
-        <v>'내 정보·배송지'에서 결제 수단 관리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'로그인·회원가입' 화면에서 비회원 주문 조회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H195" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -7058,7 +7058,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B196" t="str">
         <v/>
@@ -7073,10 +7073,10 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>쿠폰</v>
+        <v>비밀번호 찾기</v>
       </c>
       <c r="G196" t="str">
-        <v>'내 정보·배송지' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인·회원가입' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H196" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7093,22 +7093,22 @@
         <v>SCN-021</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C197" t="str">
-        <v/>
+        <v>내 정보·배송지</v>
       </c>
       <c r="D197" t="str">
-        <v/>
+        <v>AC-02</v>
       </c>
       <c r="E197" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F197" t="str">
-        <v>적립금 잔액</v>
+        <v>프로필(닉네임·프로필 사진)</v>
       </c>
       <c r="G197" t="str">
-        <v>'내 정보·배송지' 화면에서 적립금 잔액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 프로필(닉네임·프로필 사진)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H197" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7137,10 +7137,10 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>참여</v>
+        <v>휴대폰</v>
       </c>
       <c r="G198" t="str">
-        <v>'내 정보·배송지' 화면에서 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 휴대폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H198" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7169,13 +7169,13 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>후기 통계</v>
+        <v>이메일</v>
       </c>
       <c r="G199" t="str">
-        <v>'내 정보·배송지'의 후기 통계가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 정보·배송지' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H199" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7201,13 +7201,13 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>진행자 전환/진행자 페이지 진입</v>
+        <v>배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)</v>
       </c>
       <c r="G200" t="str">
-        <v>'내 정보·배송지' 화면에서 진행자 전환/진행자 페이지 진입이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지'의 배송지 목록 관리(기본 배송지 지정·추가·수정·삭제)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H200" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -7233,13 +7233,13 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>회원 탈퇴 안내</v>
+        <v>결제 수단 관리</v>
       </c>
       <c r="G201" t="str">
-        <v>'내 정보·배송지' 화면에서 회원 탈퇴 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지'에서 결제 수단 관리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H201" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7250,25 +7250,25 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B202" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C202" t="str">
-        <v>알림 설정</v>
+        <v/>
       </c>
       <c r="D202" t="str">
-        <v>AC-03</v>
+        <v/>
       </c>
       <c r="E202" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F202" t="str">
-        <v>알림 채널(앱 푸시·카카오·문자·이메일) 토글</v>
+        <v>쿠폰</v>
       </c>
       <c r="G202" t="str">
-        <v>'알림 설정' 화면에서 알림 채널(앱 푸시·카카오·문자·이메일) 토글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H202" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B203" t="str">
         <v/>
@@ -7297,10 +7297,10 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)</v>
+        <v>적립금 잔액</v>
       </c>
       <c r="G203" t="str">
-        <v>'알림 설정' 화면에서 알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 적립금 잔액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H203" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -7329,10 +7329,10 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>야간 방해금지 시간</v>
+        <v>참여</v>
       </c>
       <c r="G204" t="str">
-        <v>'알림 설정' 화면에서 야간 방해금지 시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 참여가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B205" t="str">
         <v/>
@@ -7361,13 +7361,13 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>마케팅 수신 동의와 철회</v>
+        <v>후기 통계</v>
       </c>
       <c r="G205" t="str">
-        <v>'알림 설정' 화면에서 마케팅 수신 동의와 철회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지'의 후기 통계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H205" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B206" t="str">
         <v/>
@@ -7393,10 +7393,10 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>관심 카테고리 알림</v>
+        <v>진행자 전환/진행자 페이지 진입</v>
       </c>
       <c r="G206" t="str">
-        <v>'알림 설정' 화면에서 관심 카테고리 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 진행자 전환/진행자 페이지 진입이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H206" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B207" t="str">
         <v/>
@@ -7425,10 +7425,10 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>저장</v>
+        <v>회원 탈퇴 안내</v>
       </c>
       <c r="G207" t="str">
-        <v>'알림 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보·배송지' 화면에서 회원 탈퇴 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H207" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7442,25 +7442,25 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B208" t="str">
-        <v>공구 개설(진행자)</v>
+        <v>계정</v>
       </c>
       <c r="C208" t="str">
-        <v>진행자 시작 안내</v>
+        <v>알림 설정</v>
       </c>
       <c r="D208" t="str">
-        <v>HS-01</v>
+        <v>AC-03</v>
       </c>
       <c r="E208" t="str">
         <v>기본</v>
       </c>
       <c r="F208" t="str">
-        <v>공구 진행자가 하는 일 소개</v>
+        <v>알림 채널(앱 푸시·카카오·문자·이메일) 토글</v>
       </c>
       <c r="G208" t="str">
-        <v>'진행자 시작 안내' 화면에서 공구 진행자가 하는 일 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 알림 채널(앱 푸시·카카오·문자·이메일) 토글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H208" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B209" t="str">
         <v/>
@@ -7489,10 +7489,10 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>수익 구조와 수수료 안내</v>
+        <v>알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)</v>
       </c>
       <c r="G209" t="str">
-        <v>'진행자 시작 안내' 화면에서 수익 구조와 수수료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 알림 유형별 수신(찜한 공구 마감 임박·성사·불발 환불·오픈 예정·배송·혜택)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H209" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B210" t="str">
         <v/>
@@ -7521,13 +7521,13 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>정산 방식</v>
+        <v>야간 방해금지 시간</v>
       </c>
       <c r="G210" t="str">
-        <v>'진행자 시작 안내'에서 정산 방식을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'알림 설정' 화면에서 야간 방해금지 시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H210" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B211" t="str">
         <v/>
@@ -7553,10 +7553,10 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>시점</v>
+        <v>마케팅 수신 동의와 철회</v>
       </c>
       <c r="G211" t="str">
-        <v>'진행자 시작 안내' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 마케팅 수신 동의와 철회가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H211" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B212" t="str">
         <v/>
@@ -7585,10 +7585,10 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>성공 사례와 팁</v>
+        <v>관심 카테고리 알림</v>
       </c>
       <c r="G212" t="str">
-        <v>'진행자 시작 안내' 화면에서 성공 사례와 팁이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 관심 카테고리 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H212" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B213" t="str">
         <v/>
@@ -7617,10 +7617,10 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>필요한 준비물(상품·공급처·사업자 여부)</v>
+        <v>저장</v>
       </c>
       <c r="G213" t="str">
-        <v>'진행자 시작 안내' 화면에서 필요한 준비물(상품·공급처·사업자 여부)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H213" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7637,22 +7637,22 @@
         <v>SCN-023</v>
       </c>
       <c r="B214" t="str">
-        <v/>
+        <v>공구 개설(진행자)</v>
       </c>
       <c r="C214" t="str">
-        <v/>
+        <v>진행자 시작 안내</v>
       </c>
       <c r="D214" t="str">
-        <v/>
+        <v>HS-01</v>
       </c>
       <c r="E214" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F214" t="str">
-        <v>자격 요건과 신뢰 등급</v>
+        <v>공구 진행자가 하는 일 소개</v>
       </c>
       <c r="G214" t="str">
-        <v>'진행자 시작 안내' 화면에서 자격 요건과 신뢰 등급이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 공구 진행자가 하는 일 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H214" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7681,13 +7681,13 @@
         <v/>
       </c>
       <c r="F215" t="str">
-        <v>시작하기 CTA</v>
+        <v>수익 구조와 수수료 안내</v>
       </c>
       <c r="G215" t="str">
-        <v>'진행자 시작 안내'에서 시작하기 CTA를 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 수익 구조와 수수료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H215" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7713,13 +7713,13 @@
         <v/>
       </c>
       <c r="F216" t="str">
-        <v>자주 묻는 질문</v>
+        <v>정산 방식</v>
       </c>
       <c r="G216" t="str">
-        <v>'진행자 시작 안내' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내'에서 정산 방식을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H216" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7730,25 +7730,25 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B217" t="str">
-        <v>공구 개설(진행자)</v>
+        <v/>
       </c>
       <c r="C217" t="str">
-        <v>공구 개설 폼</v>
+        <v/>
       </c>
       <c r="D217" t="str">
-        <v>HS-02</v>
+        <v/>
       </c>
       <c r="E217" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F217" t="str">
-        <v>상품명</v>
+        <v>시점</v>
       </c>
       <c r="G217" t="str">
-        <v>'공구 개설 폼' 화면에서 상품명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 시점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H217" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B218" t="str">
         <v/>
@@ -7777,10 +7777,10 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>카테고리</v>
+        <v>성공 사례와 팁</v>
       </c>
       <c r="G218" t="str">
-        <v>'공구 개설 폼' 화면에서 카테고리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 성공 사례와 팁이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H218" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B219" t="str">
         <v/>
@@ -7809,13 +7809,13 @@
         <v/>
       </c>
       <c r="F219" t="str">
-        <v>이미지 업로드</v>
+        <v>필요한 준비물(상품·공급처·사업자 여부)</v>
       </c>
       <c r="G219" t="str">
-        <v>'공구 개설 폼'의 이미지 업로드에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 필요한 준비물(상품·공급처·사업자 여부)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H219" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -7826,7 +7826,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B220" t="str">
         <v/>
@@ -7841,10 +7841,10 @@
         <v/>
       </c>
       <c r="F220" t="str">
-        <v>상세 설명 에디터</v>
+        <v>자격 요건과 신뢰 등급</v>
       </c>
       <c r="G220" t="str">
-        <v>'공구 개설 폼' 화면에서 상세 설명 에디터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 자격 요건과 신뢰 등급이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H220" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B221" t="str">
         <v/>
@@ -7873,13 +7873,13 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v>정가와 단계별 가격 설정(인원 구간별 할인가)</v>
+        <v>시작하기 CTA</v>
       </c>
       <c r="G221" t="str">
-        <v>'공구 개설 폼'의 정가와 단계별 가격 설정(인원 구간별 할인가)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'진행자 시작 안내'에서 시작하기 CTA를 눌러 본다.</v>
       </c>
       <c r="H221" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -7890,7 +7890,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B222" t="str">
         <v/>
@@ -7905,10 +7905,10 @@
         <v/>
       </c>
       <c r="F222" t="str">
-        <v>목표 인원</v>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="G222" t="str">
-        <v>'공구 개설 폼' 화면에서 목표 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 시작 안내' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H222" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7925,22 +7925,22 @@
         <v>SCN-024</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>공구 개설(진행자)</v>
       </c>
       <c r="C223" t="str">
-        <v/>
+        <v>공구 개설 폼</v>
       </c>
       <c r="D223" t="str">
-        <v/>
+        <v>HS-02</v>
       </c>
       <c r="E223" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F223" t="str">
-        <v>최소 성사 조건</v>
+        <v>상품명</v>
       </c>
       <c r="G223" t="str">
-        <v>'공구 개설 폼' 화면에서 최소 성사 조건이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 상품명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H223" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7969,10 +7969,10 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>모집 기간(시작·마감일시)</v>
+        <v>카테고리</v>
       </c>
       <c r="G224" t="str">
-        <v>'공구 개설 폼' 화면에서 모집 기간(시작·마감일시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 카테고리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H224" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8001,13 +8001,13 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>1인 최대 수량</v>
+        <v>이미지 업로드</v>
       </c>
       <c r="G225" t="str">
-        <v>'공구 개설 폼' 화면에서 1인 최대 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼'의 이미지 업로드에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H225" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -8033,10 +8033,10 @@
         <v/>
       </c>
       <c r="F226" t="str">
-        <v>총 수량 한도</v>
+        <v>상세 설명 에디터</v>
       </c>
       <c r="G226" t="str">
-        <v>'공구 개설 폼' 화면에서 총 수량 한도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 상세 설명 에디터가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H226" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8065,13 +8065,13 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>옵션 관리</v>
+        <v>정가와 단계별 가격 설정(인원 구간별 할인가)</v>
       </c>
       <c r="G227" t="str">
-        <v>'공구 개설 폼' 화면에서 옵션 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼'의 정가와 단계별 가격 설정(인원 구간별 할인가)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H227" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -8097,10 +8097,10 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>배송비</v>
+        <v>목표 인원</v>
       </c>
       <c r="G228" t="str">
-        <v>'공구 개설 폼' 화면에서 배송비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 목표 인원이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H228" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8129,10 +8129,10 @@
         <v/>
       </c>
       <c r="F229" t="str">
-        <v>발송 일정</v>
+        <v>최소 성사 조건</v>
       </c>
       <c r="G229" t="str">
-        <v>'공구 개설 폼' 화면에서 발송 일정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 최소 성사 조건이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H229" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8161,10 +8161,10 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>지역 제한</v>
+        <v>모집 기간(시작·마감일시)</v>
       </c>
       <c r="G230" t="str">
-        <v>'공구 개설 폼' 화면에서 지역 제한이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 모집 기간(시작·마감일시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H230" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8193,13 +8193,13 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>조건부 환불 정책 확인</v>
+        <v>1인 최대 수량</v>
       </c>
       <c r="G231" t="str">
-        <v>'공구 개설 폼'에서 조건부 환불 정책 확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구 개설 폼' 화면에서 1인 최대 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H231" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8225,10 +8225,10 @@
         <v/>
       </c>
       <c r="F232" t="str">
-        <v>공급가</v>
+        <v>총 수량 한도</v>
       </c>
       <c r="G232" t="str">
-        <v>'공구 개설 폼' 화면에서 공급가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 총 수량 한도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H232" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8257,10 +8257,10 @@
         <v/>
       </c>
       <c r="F233" t="str">
-        <v>예상 수익 계산</v>
+        <v>옵션 관리</v>
       </c>
       <c r="G233" t="str">
-        <v>'공구 개설 폼' 화면에서 예상 수익 계산이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 옵션 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H233" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8289,10 +8289,10 @@
         <v/>
       </c>
       <c r="F234" t="str">
-        <v>임시 저장</v>
+        <v>배송비</v>
       </c>
       <c r="G234" t="str">
-        <v>'공구 개설 폼' 화면에서 임시 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 배송비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H234" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8321,10 +8321,10 @@
         <v/>
       </c>
       <c r="F235" t="str">
-        <v>검수 제출</v>
+        <v>발송 일정</v>
       </c>
       <c r="G235" t="str">
-        <v>'공구 개설 폼' 화면에서 검수 제출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구 개설 폼' 화면에서 발송 일정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H235" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8338,28 +8338,28 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B236" t="str">
-        <v>공구 개설(진행자)</v>
+        <v/>
       </c>
       <c r="C236" t="str">
-        <v>개설 검수 대기·반려</v>
+        <v/>
       </c>
       <c r="D236" t="str">
-        <v>HS-03</v>
+        <v/>
       </c>
       <c r="E236" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F236" t="str">
-        <v>제출한 공구 미리보기</v>
+        <v>지역 제한</v>
       </c>
       <c r="G236" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 제출한 공구 미리보기가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 지역 제한이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H236" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B237" t="str">
         <v/>
@@ -8385,13 +8385,13 @@
         <v/>
       </c>
       <c r="F237" t="str">
-        <v>검수 상태(대기·승인·반려) 표시</v>
+        <v>조건부 환불 정책 확인</v>
       </c>
       <c r="G237" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 상태(대기·승인·반려) 표시가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼'에서 조건부 환불 정책 확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H237" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B238" t="str">
         <v/>
@@ -8417,13 +8417,13 @@
         <v/>
       </c>
       <c r="F238" t="str">
-        <v>반려 사유와 수정 안내</v>
+        <v>공급가</v>
       </c>
       <c r="G238" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 반려 사유와 수정 안내가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 공급가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H238" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I238" t="str">
         <v/>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B239" t="str">
         <v/>
@@ -8449,13 +8449,13 @@
         <v/>
       </c>
       <c r="F239" t="str">
-        <v>예상 검수 소요 시간</v>
+        <v>예상 수익 계산</v>
       </c>
       <c r="G239" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 예상 검수 소요 시간이 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 예상 수익 계산이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H239" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -8481,13 +8481,13 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>승인 시 자동 오픈 예약 안내</v>
+        <v>임시 저장</v>
       </c>
       <c r="G240" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 승인 시 자동 오픈 예약 안내가 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 임시 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H240" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I240" t="str">
         <v/>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B241" t="str">
         <v/>
@@ -8513,13 +8513,13 @@
         <v/>
       </c>
       <c r="F241" t="str">
-        <v>수정 후 재제출</v>
+        <v>검수 제출</v>
       </c>
       <c r="G241" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 수정 후 재제출이 보이는지 확인한다.</v>
+        <v>'공구 개설 폼' 화면에서 검수 제출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H241" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I241" t="str">
         <v/>
@@ -8533,22 +8533,22 @@
         <v>SCN-025</v>
       </c>
       <c r="B242" t="str">
-        <v/>
+        <v>공구 개설(진행자)</v>
       </c>
       <c r="C242" t="str">
-        <v/>
+        <v>개설 검수 대기·반려</v>
       </c>
       <c r="D242" t="str">
-        <v/>
+        <v>HS-03</v>
       </c>
       <c r="E242" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F242" t="str">
-        <v>진행자 대시보드로 이동</v>
+        <v>제출한 공구 미리보기</v>
       </c>
       <c r="G242" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 진행자 대시보드로 이동이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 제출한 공구 미리보기가 보이는지 확인한다.</v>
       </c>
       <c r="H242" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8577,10 +8577,10 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>검수 가이드 링크</v>
+        <v>검수 상태(대기·승인·반려) 표시</v>
       </c>
       <c r="G243" t="str">
-        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 가이드 링크가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 상태(대기·승인·반려) 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H243" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8594,28 +8594,28 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B244" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C244" t="str">
-        <v>진행자 대시보드</v>
+        <v/>
       </c>
       <c r="D244" t="str">
-        <v>HM-01</v>
+        <v/>
       </c>
       <c r="E244" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F244" t="str">
-        <v>요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)</v>
+        <v>반려 사유와 수정 안내</v>
       </c>
       <c r="G244" t="str">
-        <v>'진행자 대시보드' 화면에서 요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 반려 사유와 수정 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H244" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I244" t="str">
         <v/>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B245" t="str">
         <v/>
@@ -8641,13 +8641,13 @@
         <v/>
       </c>
       <c r="F245" t="str">
-        <v>내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)</v>
+        <v>예상 검수 소요 시간</v>
       </c>
       <c r="G245" t="str">
-        <v>'진행자 대시보드'의 내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 예상 검수 소요 시간이 보이는지 확인한다.</v>
       </c>
       <c r="H245" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B246" t="str">
         <v/>
@@ -8673,13 +8673,13 @@
         <v/>
       </c>
       <c r="F246" t="str">
-        <v>마감 임박/미달 위험 공구 강조</v>
+        <v>승인 시 자동 오픈 예약 안내</v>
       </c>
       <c r="G246" t="str">
-        <v>'진행자 대시보드' 화면에서 마감 임박/미달 위험 공구 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 승인 시 자동 오픈 예약 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H246" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I246" t="str">
         <v/>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B247" t="str">
         <v/>
@@ -8705,13 +8705,13 @@
         <v/>
       </c>
       <c r="F247" t="str">
-        <v>처리 필요 항목(발주 대기·배송 대기·문의 미답변)</v>
+        <v>수정 후 재제출</v>
       </c>
       <c r="G247" t="str">
-        <v>'진행자 대시보드' 화면에서 처리 필요 항목(발주 대기·배송 대기·문의 미답변)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 수정 후 재제출이 보이는지 확인한다.</v>
       </c>
       <c r="H247" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B248" t="str">
         <v/>
@@ -8737,13 +8737,13 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>신규 공구 개설 버튼</v>
+        <v>진행자 대시보드로 이동</v>
       </c>
       <c r="G248" t="str">
-        <v>'진행자 대시보드'에서 신규 공구 개설 버튼을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 진행자 대시보드로 이동이 보이는지 확인한다.</v>
       </c>
       <c r="H248" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -8769,13 +8769,13 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>성사율</v>
+        <v>검수 가이드 링크</v>
       </c>
       <c r="G249" t="str">
-        <v>'진행자 대시보드' 화면에서 성사율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '개설 검수 대기·반려' 화면이 나오게 한 뒤, 검수 가이드 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H249" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -8789,22 +8789,22 @@
         <v>SCN-026</v>
       </c>
       <c r="B250" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C250" t="str">
-        <v/>
+        <v>진행자 대시보드</v>
       </c>
       <c r="D250" t="str">
-        <v/>
+        <v>HM-01</v>
       </c>
       <c r="E250" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F250" t="str">
-        <v>후기 평점</v>
+        <v>요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)</v>
       </c>
       <c r="G250" t="str">
-        <v>'진행자 대시보드' 화면에서 후기 평점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드' 화면에서 요약 지표(진행 중 공구·총 참여자·이번 달 매출·정산 예정액)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H250" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8818,28 +8818,28 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B251" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C251" t="str">
-        <v>공구별 참여 현황</v>
+        <v/>
       </c>
       <c r="D251" t="str">
-        <v>HM-02</v>
+        <v/>
       </c>
       <c r="E251" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F251" t="str">
-        <v>선택 공구 실시간 달성률</v>
+        <v>내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)</v>
       </c>
       <c r="G251" t="str">
-        <v>'공구별 참여 현황' 화면에서 선택 공구 실시간 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드'의 내 공구 목록(상태·달성률·남은 시간·참여 인원·매출)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H251" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -8850,7 +8850,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B252" t="str">
         <v/>
@@ -8865,10 +8865,10 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v>목표 대비 그래프</v>
+        <v>마감 임박/미달 위험 공구 강조</v>
       </c>
       <c r="G252" t="str">
-        <v>'공구별 참여 현황' 화면에서 목표 대비 그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드' 화면에서 마감 임박/미달 위험 공구 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H252" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B253" t="str">
         <v/>
@@ -8897,10 +8897,10 @@
         <v/>
       </c>
       <c r="F253" t="str">
-        <v>시간대별 참여 추이</v>
+        <v>처리 필요 항목(발주 대기·배송 대기·문의 미답변)</v>
       </c>
       <c r="G253" t="str">
-        <v>'공구별 참여 현황' 화면에서 시간대별 참여 추이가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'진행자 대시보드' 화면에서 처리 필요 항목(발주 대기·배송 대기·문의 미답변)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H253" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B254" t="str">
         <v/>
@@ -8929,13 +8929,13 @@
         <v/>
       </c>
       <c r="F254" t="str">
-        <v>현재 단계와 다음 단계까지 남은 인원</v>
+        <v>신규 공구 개설 버튼</v>
       </c>
       <c r="G254" t="str">
-        <v>'공구별 참여 현황'의 현재 단계와 다음 단계까지 남은 인원이 실제 데이터와 같은지 대조한다.</v>
+        <v>'진행자 대시보드'에서 신규 공구 개설 버튼을 눌러 본다.</v>
       </c>
       <c r="H254" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B255" t="str">
         <v/>
@@ -8961,13 +8961,13 @@
         <v/>
       </c>
       <c r="F255" t="str">
-        <v>참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)</v>
+        <v>성사율</v>
       </c>
       <c r="G255" t="str">
-        <v>'공구별 참여 현황'의 참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'진행자 대시보드' 화면에서 성사율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H255" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B256" t="str">
         <v/>
@@ -8993,13 +8993,13 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>검색</v>
+        <v>후기 평점</v>
       </c>
       <c r="G256" t="str">
-        <v>'공구별 참여 현황'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'진행자 대시보드' 화면에서 후기 평점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H256" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9013,25 +9013,25 @@
         <v>SCN-027</v>
       </c>
       <c r="B257" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C257" t="str">
-        <v/>
+        <v>공구별 참여 현황</v>
       </c>
       <c r="D257" t="str">
-        <v/>
+        <v>HM-02</v>
       </c>
       <c r="E257" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F257" t="str">
-        <v>필터</v>
+        <v>선택 공구 실시간 달성률</v>
       </c>
       <c r="G257" t="str">
-        <v>'공구별 참여 현황'에서 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 선택 공구 실시간 달성률이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H257" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9057,13 +9057,13 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>취소</v>
+        <v>목표 대비 그래프</v>
       </c>
       <c r="G258" t="str">
-        <v>'공구별 참여 현황'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 목표 대비 그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H258" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9089,13 +9089,13 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v>환불 참여 표시</v>
+        <v>시간대별 참여 추이</v>
       </c>
       <c r="G259" t="str">
-        <v>'공구별 참여 현황'에서 환불 참여 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 시간대별 참여 추이가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H259" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9121,13 +9121,13 @@
         <v/>
       </c>
       <c r="F260" t="str">
-        <v>참여자에게 공지 발송</v>
+        <v>현재 단계와 다음 단계까지 남은 인원</v>
       </c>
       <c r="G260" t="str">
-        <v>'공구별 참여 현황' 화면에서 참여자에게 공지 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'의 현재 단계와 다음 단계까지 남은 인원이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H260" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -9153,13 +9153,13 @@
         <v/>
       </c>
       <c r="F261" t="str">
-        <v>엑셀 내보내기</v>
+        <v>참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)</v>
       </c>
       <c r="G261" t="str">
-        <v>'공구별 참여 현황' 화면에서 엑셀 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'의 참여자 목록(닉네임·옵션·수량·금액·참여시각·상태)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H261" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I261" t="str">
         <v/>
@@ -9170,28 +9170,28 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B262" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C262" t="str">
-        <v>마감·성사 처리</v>
+        <v/>
       </c>
       <c r="D262" t="str">
-        <v>HM-03</v>
+        <v/>
       </c>
       <c r="E262" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F262" t="str">
-        <v>마감 임박 공구 요약과 최종 달성 여부 판정</v>
+        <v>검색</v>
       </c>
       <c r="G262" t="str">
-        <v>'마감·성사 처리' 화면에서 마감 임박 공구 요약과 최종 달성 여부 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H262" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I262" t="str">
         <v/>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B263" t="str">
         <v/>
@@ -9217,13 +9217,13 @@
         <v/>
       </c>
       <c r="F263" t="str">
-        <v>성사 확정 처리</v>
+        <v>필터</v>
       </c>
       <c r="G263" t="str">
-        <v>'마감·성사 처리' 화면에서 성사 확정 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'에서 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H263" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I263" t="str">
         <v/>
@@ -9234,7 +9234,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B264" t="str">
         <v/>
@@ -9249,13 +9249,13 @@
         <v/>
       </c>
       <c r="F264" t="str">
-        <v>목표 근접 시 마감 연장 옵션</v>
+        <v>취소</v>
       </c>
       <c r="G264" t="str">
-        <v>'마감·성사 처리' 화면에서 목표 근접 시 마감 연장 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H264" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B265" t="str">
         <v/>
@@ -9281,10 +9281,10 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>미달 시 불발 처리와 자동 환불 실행 안내</v>
+        <v>환불 참여 표시</v>
       </c>
       <c r="G265" t="str">
-        <v>'마감·성사 처리'에서 미달 시 불발 처리와 자동 환불 실행 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공구별 참여 현황'에서 환불 참여 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H265" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B266" t="str">
         <v/>
@@ -9313,10 +9313,10 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>참여자 일괄 알림(성사/환불)</v>
+        <v>참여자에게 공지 발송</v>
       </c>
       <c r="G266" t="str">
-        <v>'마감·성사 처리' 화면에서 참여자 일괄 알림(성사/환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 참여자에게 공지 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H266" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B267" t="str">
         <v/>
@@ -9345,10 +9345,10 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>성사분 수량 집계와 발주 준비</v>
+        <v>엑셀 내보내기</v>
       </c>
       <c r="G267" t="str">
-        <v>'마감·성사 처리' 화면에서 성사분 수량 집계와 발주 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공구별 참여 현황' 화면에서 엑셀 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H267" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9365,22 +9365,22 @@
         <v>SCN-028</v>
       </c>
       <c r="B268" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C268" t="str">
-        <v/>
+        <v>마감·성사 처리</v>
       </c>
       <c r="D268" t="str">
-        <v/>
+        <v>HM-03</v>
       </c>
       <c r="E268" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F268" t="str">
-        <v>처리 확인 모달</v>
+        <v>마감 임박 공구 요약과 최종 달성 여부 판정</v>
       </c>
       <c r="G268" t="str">
-        <v>'마감·성사 처리' 화면에서 처리 확인 모달이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 마감 임박 공구 요약과 최종 달성 여부 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H268" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9394,25 +9394,25 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B269" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C269" t="str">
-        <v>발주·배송 관리</v>
+        <v/>
       </c>
       <c r="D269" t="str">
-        <v>HM-04</v>
+        <v/>
       </c>
       <c r="E269" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F269" t="str">
-        <v>성사분 총 수량</v>
+        <v>성사 확정 처리</v>
       </c>
       <c r="G269" t="str">
-        <v>'발주·배송 관리' 화면에서 성사분 총 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 성사 확정 처리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H269" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9426,7 +9426,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B270" t="str">
         <v/>
@@ -9441,10 +9441,10 @@
         <v/>
       </c>
       <c r="F270" t="str">
-        <v>옵션별 집계</v>
+        <v>목표 근접 시 마감 연장 옵션</v>
       </c>
       <c r="G270" t="str">
-        <v>'발주·배송 관리' 화면에서 옵션별 집계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 목표 근접 시 마감 연장 옵션이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H270" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B271" t="str">
         <v/>
@@ -9473,13 +9473,13 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>공급처 발주서 생성</v>
+        <v>미달 시 불발 처리와 자동 환불 실행 안내</v>
       </c>
       <c r="G271" t="str">
-        <v>'발주·배송 관리' 화면에서 공급처 발주서 생성이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리'에서 미달 시 불발 처리와 자동 환불 실행 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H271" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9490,7 +9490,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B272" t="str">
         <v/>
@@ -9505,10 +9505,10 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v>다운로드</v>
+        <v>참여자 일괄 알림(성사/환불)</v>
       </c>
       <c r="G272" t="str">
-        <v>'발주·배송 관리' 화면에서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'마감·성사 처리' 화면에서 참여자 일괄 알림(성사/환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H272" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B273" t="str">
         <v/>
@@ -9537,13 +9537,13 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v>배송 상태 관리(준비·발송·완료)</v>
+        <v>성사분 수량 집계와 발주 준비</v>
       </c>
       <c r="G273" t="str">
-        <v>'발주·배송 관리'의 배송 상태 관리(준비·발송·완료)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'마감·성사 처리' 화면에서 성사분 수량 집계와 발주 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H273" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I273" t="str">
         <v/>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B274" t="str">
         <v/>
@@ -9569,13 +9569,13 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v>참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)</v>
+        <v>처리 확인 모달</v>
       </c>
       <c r="G274" t="str">
-        <v>'발주·배송 관리'의 참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'마감·성사 처리' 화면에서 처리 확인 모달이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H274" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -9589,22 +9589,22 @@
         <v>SCN-029</v>
       </c>
       <c r="B275" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C275" t="str">
-        <v/>
+        <v>발주·배송 관리</v>
       </c>
       <c r="D275" t="str">
-        <v/>
+        <v>HM-04</v>
       </c>
       <c r="E275" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F275" t="str">
-        <v>배송 출발 알림 발송</v>
+        <v>성사분 총 수량</v>
       </c>
       <c r="G275" t="str">
-        <v>'발주·배송 관리' 화면에서 배송 출발 알림 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 성사분 총 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H275" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9633,10 +9633,10 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>반품</v>
+        <v>옵션별 집계</v>
       </c>
       <c r="G276" t="str">
-        <v>'발주·배송 관리' 화면에서 반품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 옵션별 집계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H276" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9665,10 +9665,10 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v>교환 접수</v>
+        <v>공급처 발주서 생성</v>
       </c>
       <c r="G277" t="str">
-        <v>'발주·배송 관리' 화면에서 교환 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 공급처 발주서 생성이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H277" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9697,10 +9697,10 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v>배송 지연 공지</v>
+        <v>다운로드</v>
       </c>
       <c r="G278" t="str">
-        <v>'발주·배송 관리' 화면에서 배송 지연 공지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H278" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9729,10 +9729,10 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>진행률 표시</v>
+        <v>배송 상태 관리(준비·발송·완료)</v>
       </c>
       <c r="G279" t="str">
-        <v>'발주·배송 관리'의 진행률 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'발주·배송 관리'의 배송 상태 관리(준비·발송·완료)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H279" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -9746,28 +9746,28 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B280" t="str">
-        <v>공구 관리(진행자)</v>
+        <v/>
       </c>
       <c r="C280" t="str">
-        <v>참여자 공지·알림 발송</v>
+        <v/>
       </c>
       <c r="D280" t="str">
-        <v>HM-05</v>
+        <v/>
       </c>
       <c r="E280" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F280" t="str">
-        <v>대상 공구</v>
+        <v>참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)</v>
       </c>
       <c r="G280" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 대상 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리'의 참여자별 배송지 목록과 송장번호 일괄 등록(엑셀 업로드)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H280" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -9778,7 +9778,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B281" t="str">
         <v/>
@@ -9793,10 +9793,10 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v>참여자 세그먼트 선택</v>
+        <v>배송 출발 알림 발송</v>
       </c>
       <c r="G281" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 참여자 세그먼트 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 배송 출발 알림 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H281" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B282" t="str">
         <v/>
@@ -9825,10 +9825,10 @@
         <v/>
       </c>
       <c r="F282" t="str">
-        <v>공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)</v>
+        <v>반품</v>
       </c>
       <c r="G282" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 반품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H282" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B283" t="str">
         <v/>
@@ -9857,10 +9857,10 @@
         <v/>
       </c>
       <c r="F283" t="str">
-        <v>템플릿 불러오기와 치환 변수</v>
+        <v>교환 접수</v>
       </c>
       <c r="G283" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 템플릿 불러오기와 치환 변수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 교환 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H283" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9874,7 +9874,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B284" t="str">
         <v/>
@@ -9889,10 +9889,10 @@
         <v/>
       </c>
       <c r="F284" t="str">
-        <v>발송 채널(앱 알림·카톡·문자)</v>
+        <v>배송 지연 공지</v>
       </c>
       <c r="G284" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 발송 채널(앱 알림·카톡·문자)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리' 화면에서 배송 지연 공지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H284" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B285" t="str">
         <v/>
@@ -9921,13 +9921,13 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>예상 도달 수</v>
+        <v>진행률 표시</v>
       </c>
       <c r="G285" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 예상 도달 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'발주·배송 관리'의 진행률 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H285" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -9941,22 +9941,22 @@
         <v>SCN-030</v>
       </c>
       <c r="B286" t="str">
-        <v/>
+        <v>공구 관리(진행자)</v>
       </c>
       <c r="C286" t="str">
-        <v/>
+        <v>참여자 공지·알림 발송</v>
       </c>
       <c r="D286" t="str">
-        <v/>
+        <v>HM-05</v>
       </c>
       <c r="E286" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F286" t="str">
-        <v>비용</v>
+        <v>대상 공구</v>
       </c>
       <c r="G286" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 비용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 대상 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H286" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9985,10 +9985,10 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>미리보기</v>
+        <v>참여자 세그먼트 선택</v>
       </c>
       <c r="G287" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 참여자 세그먼트 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H287" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10017,10 +10017,10 @@
         <v/>
       </c>
       <c r="F288" t="str">
-        <v>즉시</v>
+        <v>공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)</v>
       </c>
       <c r="G288" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 즉시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 공지 유형(마감 임박 독려·성사 안내·배송 지연·감사)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H288" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10049,10 +10049,10 @@
         <v/>
       </c>
       <c r="F289" t="str">
-        <v>예약 발송</v>
+        <v>템플릿 불러오기와 치환 변수</v>
       </c>
       <c r="G289" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 예약 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 템플릿 불러오기와 치환 변수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H289" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10081,10 +10081,10 @@
         <v/>
       </c>
       <c r="F290" t="str">
-        <v>발송 이력</v>
+        <v>발송 채널(앱 알림·카톡·문자)</v>
       </c>
       <c r="G290" t="str">
-        <v>'참여자 공지·알림 발송' 화면에서 발송 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 발송 채널(앱 알림·카톡·문자)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H290" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10098,28 +10098,28 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B291" t="str">
-        <v>정산(진행자)</v>
+        <v/>
       </c>
       <c r="C291" t="str">
-        <v>정산 내역</v>
+        <v/>
       </c>
       <c r="D291" t="str">
-        <v>SE-01</v>
+        <v/>
       </c>
       <c r="E291" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F291" t="str">
-        <v>정산 요약(정산 예정·정산 완료·보류 금액)</v>
+        <v>예상 도달 수</v>
       </c>
       <c r="G291" t="str">
-        <v>'정산 내역'에서 정산 요약(정산 예정·정산 완료·보류 금액)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 예상 도달 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H291" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B292" t="str">
         <v/>
@@ -10145,13 +10145,13 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>공구별 정산 표(매출·수수료·환불·순정산액·상태)</v>
+        <v>비용</v>
       </c>
       <c r="G292" t="str">
-        <v>'정산 내역'에서 공구별 정산 표(매출·수수료·환불·순정산액·상태)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 비용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H292" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I292" t="str">
         <v/>
@@ -10162,7 +10162,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B293" t="str">
         <v/>
@@ -10177,13 +10177,13 @@
         <v/>
       </c>
       <c r="F293" t="str">
-        <v>정산 주기</v>
+        <v>미리보기</v>
       </c>
       <c r="G293" t="str">
-        <v>'정산 내역'에서 정산 주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H293" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B294" t="str">
         <v/>
@@ -10209,10 +10209,10 @@
         <v/>
       </c>
       <c r="F294" t="str">
-        <v>예정일 안내</v>
+        <v>즉시</v>
       </c>
       <c r="G294" t="str">
-        <v>'정산 내역' 화면에서 예정일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 즉시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H294" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B295" t="str">
         <v/>
@@ -10241,13 +10241,13 @@
         <v/>
       </c>
       <c r="F295" t="str">
-        <v>기간 필터</v>
+        <v>예약 발송</v>
       </c>
       <c r="G295" t="str">
-        <v>'정산 내역'에서 기간 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 예약 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H295" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B296" t="str">
         <v/>
@@ -10273,13 +10273,13 @@
         <v/>
       </c>
       <c r="F296" t="str">
-        <v>정산 상세로 이동</v>
+        <v>발송 이력</v>
       </c>
       <c r="G296" t="str">
-        <v>'정산 내역'에서 정산 상세로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'참여자 공지·알림 발송' 화면에서 발송 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H296" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10293,25 +10293,25 @@
         <v>SCN-031</v>
       </c>
       <c r="B297" t="str">
-        <v/>
+        <v>정산(진행자)</v>
       </c>
       <c r="C297" t="str">
-        <v/>
+        <v>정산 내역</v>
       </c>
       <c r="D297" t="str">
-        <v/>
+        <v>SE-01</v>
       </c>
       <c r="E297" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F297" t="str">
-        <v>세금계산서</v>
+        <v>정산 요약(정산 예정·정산 완료·보류 금액)</v>
       </c>
       <c r="G297" t="str">
-        <v>'정산 내역' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역'에서 정산 요약(정산 예정·정산 완료·보류 금액)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H297" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I297" t="str">
         <v/>
@@ -10337,13 +10337,13 @@
         <v/>
       </c>
       <c r="F298" t="str">
-        <v>명세서</v>
+        <v>공구별 정산 표(매출·수수료·환불·순정산액·상태)</v>
       </c>
       <c r="G298" t="str">
-        <v>'정산 내역' 화면에서 명세서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역'에서 공구별 정산 표(매출·수수료·환불·순정산액·상태)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H298" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -10369,10 +10369,10 @@
         <v/>
       </c>
       <c r="F299" t="str">
-        <v>정산 계좌 설정 링크</v>
+        <v>정산 주기</v>
       </c>
       <c r="G299" t="str">
-        <v>'정산 내역'에서 정산 계좌 설정 링크를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역'에서 정산 주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H299" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10401,10 +10401,10 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>내보내기</v>
+        <v>예정일 안내</v>
       </c>
       <c r="G300" t="str">
-        <v>'정산 내역' 화면에서 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역' 화면에서 예정일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H300" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10418,28 +10418,28 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B301" t="str">
-        <v>정산(진행자)</v>
+        <v/>
       </c>
       <c r="C301" t="str">
-        <v>정산 계좌·세금 설정</v>
+        <v/>
       </c>
       <c r="D301" t="str">
-        <v>SE-02</v>
+        <v/>
       </c>
       <c r="E301" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F301" t="str">
-        <v>정산 받을 계좌 등록(은행·계좌·예금주 인증)</v>
+        <v>기간 필터</v>
       </c>
       <c r="G301" t="str">
-        <v>'정산 계좌·세금 설정'에서 정산 받을 계좌 등록(은행·계좌·예금주 인증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역'에서 기간 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H301" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B302" t="str">
         <v/>
@@ -10465,13 +10465,13 @@
         <v/>
       </c>
       <c r="F302" t="str">
-        <v>사업자/개인 구분과 사업자등록증</v>
+        <v>정산 상세로 이동</v>
       </c>
       <c r="G302" t="str">
-        <v>'정산 계좌·세금 설정'의 사업자/개인 구분과 사업자등록증에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'정산 내역'에서 정산 상세로 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H302" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B303" t="str">
         <v/>
@@ -10497,10 +10497,10 @@
         <v/>
       </c>
       <c r="F303" t="str">
-        <v>세금 유형(과세·간이·면세)</v>
+        <v>세금계산서</v>
       </c>
       <c r="G303" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 세금 유형(과세·간이·면세)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B304" t="str">
         <v/>
@@ -10529,10 +10529,10 @@
         <v/>
       </c>
       <c r="F304" t="str">
-        <v>원천징수</v>
+        <v>명세서</v>
       </c>
       <c r="G304" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 원천징수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역' 화면에서 명세서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10546,7 +10546,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B305" t="str">
         <v/>
@@ -10561,13 +10561,13 @@
         <v/>
       </c>
       <c r="F305" t="str">
-        <v>부가세 안내</v>
+        <v>정산 계좌 설정 링크</v>
       </c>
       <c r="G305" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 부가세 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역'에서 정산 계좌 설정 링크를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H305" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I305" t="str">
         <v/>
@@ -10578,7 +10578,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B306" t="str">
         <v/>
@@ -10593,13 +10593,13 @@
         <v/>
       </c>
       <c r="F306" t="str">
-        <v>세금계산서 발행 정보</v>
+        <v>내보내기</v>
       </c>
       <c r="G306" t="str">
-        <v>'정산 계좌·세금 설정'의 세금계산서 발행 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 내역' 화면에서 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H306" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I306" t="str">
         <v/>
@@ -10613,22 +10613,22 @@
         <v>SCN-032</v>
       </c>
       <c r="B307" t="str">
-        <v/>
+        <v>정산(진행자)</v>
       </c>
       <c r="C307" t="str">
-        <v/>
+        <v>정산 계좌·세금 설정</v>
       </c>
       <c r="D307" t="str">
-        <v/>
+        <v>SE-02</v>
       </c>
       <c r="E307" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F307" t="str">
-        <v>정산 주기 선택</v>
+        <v>정산 받을 계좌 등록(은행·계좌·예금주 인증)</v>
       </c>
       <c r="G307" t="str">
-        <v>'정산 계좌·세금 설정'에서 정산 주기 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정'에서 정산 받을 계좌 등록(은행·계좌·예금주 인증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H307" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10657,13 +10657,13 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>저장</v>
+        <v>사업자/개인 구분과 사업자등록증</v>
       </c>
       <c r="G308" t="str">
-        <v>'정산 계좌·세금 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정'의 사업자/개인 구분과 사업자등록증에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H308" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I308" t="str">
         <v/>
@@ -10689,13 +10689,13 @@
         <v/>
       </c>
       <c r="F309" t="str">
-        <v>민감정보 보안 안내</v>
+        <v>세금 유형(과세·간이·면세)</v>
       </c>
       <c r="G309" t="str">
-        <v>'정산 계좌·세금 설정'의 민감정보 보안 안내가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 세금 유형(과세·간이·면세)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H309" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I309" t="str">
         <v/>
@@ -10706,28 +10706,28 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B310" t="str">
-        <v>정산(진행자)</v>
+        <v/>
       </c>
       <c r="C310" t="str">
-        <v>정산 상세</v>
+        <v/>
       </c>
       <c r="D310" t="str">
-        <v>SE-03</v>
+        <v/>
       </c>
       <c r="E310" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F310" t="str">
-        <v>선택 공구 정산 상세 내역</v>
+        <v>원천징수</v>
       </c>
       <c r="G310" t="str">
-        <v>'정산 상세'에서 선택 공구 정산 상세 내역을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 원천징수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H310" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I310" t="str">
         <v/>
@@ -10738,7 +10738,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B311" t="str">
         <v/>
@@ -10753,10 +10753,10 @@
         <v/>
       </c>
       <c r="F311" t="str">
-        <v>매출 구성(참여 건별 결제액 합계)</v>
+        <v>부가세 안내</v>
       </c>
       <c r="G311" t="str">
-        <v>'정산 상세' 화면에서 매출 구성(참여 건별 결제액 합계)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 부가세 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H311" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10770,7 +10770,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B312" t="str">
         <v/>
@@ -10785,13 +10785,13 @@
         <v/>
       </c>
       <c r="F312" t="str">
-        <v>차감 항목(수수료·환불·배송비·쿠폰 분담)</v>
+        <v>세금계산서 발행 정보</v>
       </c>
       <c r="G312" t="str">
-        <v>'정산 상세' 화면에서 차감 항목(수수료·환불·배송비·쿠폰 분담)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정'의 세금계산서 발행 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H312" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I312" t="str">
         <v/>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B313" t="str">
         <v/>
@@ -10817,10 +10817,10 @@
         <v/>
       </c>
       <c r="F313" t="str">
-        <v>최종 순정산액</v>
+        <v>정산 주기 선택</v>
       </c>
       <c r="G313" t="str">
-        <v>'정산 상세'에서 최종 순정산액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정'에서 정산 주기 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H313" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B314" t="str">
         <v/>
@@ -10849,13 +10849,13 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>정산 상태 타임라인</v>
+        <v>저장</v>
       </c>
       <c r="G314" t="str">
-        <v>'정산 상세'에서 정산 상태 타임라인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 계좌·세금 설정' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H314" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I314" t="str">
         <v/>
@@ -10866,7 +10866,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B315" t="str">
         <v/>
@@ -10881,13 +10881,13 @@
         <v/>
       </c>
       <c r="F315" t="str">
-        <v>세금계산서</v>
+        <v>민감정보 보안 안내</v>
       </c>
       <c r="G315" t="str">
-        <v>'정산 상세' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 계좌·세금 설정'의 민감정보 보안 안내가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H315" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I315" t="str">
         <v/>
@@ -10901,25 +10901,25 @@
         <v>SCN-033</v>
       </c>
       <c r="B316" t="str">
-        <v/>
+        <v>정산(진행자)</v>
       </c>
       <c r="C316" t="str">
-        <v/>
+        <v>정산 상세</v>
       </c>
       <c r="D316" t="str">
-        <v/>
+        <v>SE-03</v>
       </c>
       <c r="E316" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F316" t="str">
-        <v>거래명세서 다운로드</v>
+        <v>선택 공구 정산 상세 내역</v>
       </c>
       <c r="G316" t="str">
-        <v>'정산 상세' 화면에서 거래명세서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세'에서 선택 공구 정산 상세 내역을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H316" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I316" t="str">
         <v/>
@@ -10945,13 +10945,13 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v>정산 문의</v>
+        <v>매출 구성(참여 건별 결제액 합계)</v>
       </c>
       <c r="G317" t="str">
-        <v>'정산 상세'에서 정산 문의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 상세' 화면에서 매출 구성(참여 건별 결제액 합계)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H317" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I317" t="str">
         <v/>
@@ -10977,13 +10977,13 @@
         <v/>
       </c>
       <c r="F318" t="str">
-        <v>이전/다음 정산 이동</v>
+        <v>차감 항목(수수료·환불·배송비·쿠폰 분담)</v>
       </c>
       <c r="G318" t="str">
-        <v>'정산 상세'에서 이전/다음 정산 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 상세' 화면에서 차감 항목(수수료·환불·배송비·쿠폰 분담)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H318" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I318" t="str">
         <v/>
@@ -10994,28 +10994,28 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B319" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C319" t="str">
-        <v>이용 안내·자주 묻는 질문</v>
+        <v/>
       </c>
       <c r="D319" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E319" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F319" t="str">
-        <v>공동구매 개념 설명(성사·불발·조건부 결제)</v>
+        <v>최종 순정산액</v>
       </c>
       <c r="G319" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 공동구매 개념 설명(성사·불발·조건부 결제)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세'에서 최종 순정산액을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H319" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I319" t="str">
         <v/>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B320" t="str">
         <v/>
@@ -11041,13 +11041,13 @@
         <v/>
       </c>
       <c r="F320" t="str">
-        <v>참여자용 3단계 이용법</v>
+        <v>정산 상태 타임라인</v>
       </c>
       <c r="G320" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면을 열고 참여자용 3단계 이용법이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'정산 상세'에서 정산 상태 타임라인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H320" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I320" t="str">
         <v/>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B321" t="str">
         <v/>
@@ -11073,10 +11073,10 @@
         <v/>
       </c>
       <c r="F321" t="str">
-        <v>진행자용 이용법</v>
+        <v>세금계산서</v>
       </c>
       <c r="G321" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 진행자용 이용법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H321" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B322" t="str">
         <v/>
@@ -11105,10 +11105,10 @@
         <v/>
       </c>
       <c r="F322" t="str">
-        <v>카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)</v>
+        <v>거래명세서 다운로드</v>
       </c>
       <c r="G322" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세' 화면에서 거래명세서 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H322" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B323" t="str">
         <v/>
@@ -11137,13 +11137,13 @@
         <v/>
       </c>
       <c r="F323" t="str">
-        <v>검색</v>
+        <v>정산 문의</v>
       </c>
       <c r="G323" t="str">
-        <v>'이용 안내·자주 묻는 질문'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'정산 상세'에서 정산 문의를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H323" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I323" t="str">
         <v/>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B324" t="str">
         <v/>
@@ -11169,13 +11169,13 @@
         <v/>
       </c>
       <c r="F324" t="str">
-        <v>인기 질문</v>
+        <v>이전/다음 정산 이동</v>
       </c>
       <c r="G324" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 인기 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 상세'에서 이전/다음 정산 이동을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H324" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I324" t="str">
         <v/>
@@ -11189,22 +11189,22 @@
         <v>SCN-034</v>
       </c>
       <c r="B325" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C325" t="str">
-        <v/>
+        <v>이용 안내·자주 묻는 질문</v>
       </c>
       <c r="D325" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E325" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F325" t="str">
-        <v>해결 안 되면 1:1 문의 유도</v>
+        <v>공동구매 개념 설명(성사·불발·조건부 결제)</v>
       </c>
       <c r="G325" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 해결 안 되면 1:1 문의 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 공동구매 개념 설명(성사·불발·조건부 결제)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H325" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11233,13 +11233,13 @@
         <v/>
       </c>
       <c r="F326" t="str">
-        <v>용어 설명</v>
+        <v>참여자용 3단계 이용법</v>
       </c>
       <c r="G326" t="str">
-        <v>'이용 안내·자주 묻는 질문' 화면에서 용어 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면을 열고 참여자용 3단계 이용법이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H326" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I326" t="str">
         <v/>
@@ -11250,25 +11250,25 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B327" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C327" t="str">
-        <v>1:1 문의</v>
+        <v/>
       </c>
       <c r="D327" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E327" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F327" t="str">
-        <v>문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)</v>
+        <v>진행자용 이용법</v>
       </c>
       <c r="G327" t="str">
-        <v>'1:1 문의' 화면에서 문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 진행자용 이용법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H327" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B328" t="str">
         <v/>
@@ -11297,10 +11297,10 @@
         <v/>
       </c>
       <c r="F328" t="str">
-        <v>관련 공구</v>
+        <v>카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)</v>
       </c>
       <c r="G328" t="str">
-        <v>'1:1 문의' 화면에서 관련 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 카테고리별 FAQ(참여·결제·성사/환불·배송·진행자·정산)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H328" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B329" t="str">
         <v/>
@@ -11329,13 +11329,13 @@
         <v/>
       </c>
       <c r="F329" t="str">
-        <v>주문 연결</v>
+        <v>검색</v>
       </c>
       <c r="G329" t="str">
-        <v>'1:1 문의' 화면에서 주문 연결이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문'에서 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H329" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I329" t="str">
         <v/>
@@ -11346,7 +11346,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B330" t="str">
         <v/>
@@ -11361,13 +11361,13 @@
         <v/>
       </c>
       <c r="F330" t="str">
-        <v>내용과 첨부</v>
+        <v>인기 질문</v>
       </c>
       <c r="G330" t="str">
-        <v>'1:1 문의'의 내용과 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 인기 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H330" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I330" t="str">
         <v/>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B331" t="str">
         <v/>
@@ -11393,10 +11393,10 @@
         <v/>
       </c>
       <c r="F331" t="str">
-        <v>연락처</v>
+        <v>해결 안 되면 1:1 문의 유도</v>
       </c>
       <c r="G331" t="str">
-        <v>'1:1 문의' 화면에서 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 해결 안 되면 1:1 문의 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H331" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11410,7 +11410,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B332" t="str">
         <v/>
@@ -11425,10 +11425,10 @@
         <v/>
       </c>
       <c r="F332" t="str">
-        <v>답변 방식 선택</v>
+        <v>용어 설명</v>
       </c>
       <c r="G332" t="str">
-        <v>'1:1 문의' 화면에서 답변 방식 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'이용 안내·자주 묻는 질문' 화면에서 용어 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H332" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11445,22 +11445,22 @@
         <v>SCN-035</v>
       </c>
       <c r="B333" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C333" t="str">
-        <v/>
+        <v>1:1 문의</v>
       </c>
       <c r="D333" t="str">
-        <v/>
+        <v>CS-02</v>
       </c>
       <c r="E333" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F333" t="str">
-        <v>예상 답변 시간 안내</v>
+        <v>문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)</v>
       </c>
       <c r="G333" t="str">
-        <v>'1:1 문의' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 문의 유형 선택(참여·결제·환불·배송·진행자·정산·신고)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H333" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11489,13 +11489,13 @@
         <v/>
       </c>
       <c r="F334" t="str">
-        <v>내 문의 내역과 상태</v>
+        <v>관련 공구</v>
       </c>
       <c r="G334" t="str">
-        <v>'1:1 문의'의 내 문의 내역과 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'1:1 문의' 화면에서 관련 공구가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H334" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I334" t="str">
         <v/>
@@ -11521,10 +11521,10 @@
         <v/>
       </c>
       <c r="F335" t="str">
-        <v>답변 확인</v>
+        <v>주문 연결</v>
       </c>
       <c r="G335" t="str">
-        <v>'1:1 문의' 화면에서 답변 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 주문 연결이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H335" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11553,13 +11553,13 @@
         <v/>
       </c>
       <c r="F336" t="str">
-        <v>챗봇 우선 안내</v>
+        <v>내용과 첨부</v>
       </c>
       <c r="G336" t="str">
-        <v>'1:1 문의' 화면에서 챗봇 우선 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'의 내용과 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H336" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I336" t="str">
         <v/>
@@ -11570,28 +11570,28 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B337" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C337" t="str">
-        <v>공지·이벤트</v>
+        <v/>
       </c>
       <c r="D337" t="str">
-        <v>CS-03</v>
+        <v/>
       </c>
       <c r="E337" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F337" t="str">
-        <v>공지사항 목록(중요 공지 상단 고정)</v>
+        <v>연락처</v>
       </c>
       <c r="G337" t="str">
-        <v>'공지·이벤트'의 공지사항 목록(중요 공지 상단 고정)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H337" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I337" t="str">
         <v/>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B338" t="str">
         <v/>
@@ -11617,10 +11617,10 @@
         <v/>
       </c>
       <c r="F338" t="str">
-        <v>이벤트</v>
+        <v>답변 방식 선택</v>
       </c>
       <c r="G338" t="str">
-        <v>'공지·이벤트' 화면에서 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 답변 방식 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H338" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B339" t="str">
         <v/>
@@ -11649,13 +11649,13 @@
         <v/>
       </c>
       <c r="F339" t="str">
-        <v>기획전 배너</v>
+        <v>예상 답변 시간 안내</v>
       </c>
       <c r="G339" t="str">
-        <v>'공지·이벤트'에서 기획전 배너를 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H339" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I339" t="str">
         <v/>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B340" t="str">
         <v/>
@@ -11681,13 +11681,13 @@
         <v/>
       </c>
       <c r="F340" t="str">
-        <v>점검</v>
+        <v>내 문의 내역과 상태</v>
       </c>
       <c r="G340" t="str">
-        <v>'공지·이벤트' 화면에서 점검이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'의 내 문의 내역과 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H340" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I340" t="str">
         <v/>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B341" t="str">
         <v/>
@@ -11713,10 +11713,10 @@
         <v/>
       </c>
       <c r="F341" t="str">
-        <v>정책 변경 안내</v>
+        <v>답변 확인</v>
       </c>
       <c r="G341" t="str">
-        <v>'공지·이벤트' 화면에서 정책 변경 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 답변 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H341" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B342" t="str">
         <v/>
@@ -11745,13 +11745,13 @@
         <v/>
       </c>
       <c r="F342" t="str">
-        <v>카테고리 필터</v>
+        <v>챗봇 우선 안내</v>
       </c>
       <c r="G342" t="str">
-        <v>'공지·이벤트'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'1:1 문의' 화면에서 챗봇 우선 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H342" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I342" t="str">
         <v/>
@@ -11765,25 +11765,25 @@
         <v>SCN-036</v>
       </c>
       <c r="B343" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C343" t="str">
-        <v/>
+        <v>공지·이벤트</v>
       </c>
       <c r="D343" t="str">
-        <v/>
+        <v>CS-03</v>
       </c>
       <c r="E343" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F343" t="str">
-        <v>상세 보기</v>
+        <v>공지사항 목록(중요 공지 상단 고정)</v>
       </c>
       <c r="G343" t="str">
-        <v>'공지·이벤트' 화면에서 상세 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트'의 공지사항 목록(중요 공지 상단 고정)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H343" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I343" t="str">
         <v/>
@@ -11809,10 +11809,10 @@
         <v/>
       </c>
       <c r="F344" t="str">
-        <v>이벤트 참여 유도</v>
+        <v>이벤트</v>
       </c>
       <c r="G344" t="str">
-        <v>'공지·이벤트' 화면에서 이벤트 참여 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H344" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11841,13 +11841,13 @@
         <v/>
       </c>
       <c r="F345" t="str">
-        <v>신규 진행자 지원 이벤트</v>
+        <v>기획전 배너</v>
       </c>
       <c r="G345" t="str">
-        <v>'공지·이벤트' 화면에서 신규 진행자 지원 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트'에서 기획전 배너를 눌러 본다.</v>
       </c>
       <c r="H345" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I345" t="str">
         <v/>
@@ -11858,28 +11858,28 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B346" t="str">
-        <v>고객지원</v>
+        <v/>
       </c>
       <c r="C346" t="str">
-        <v>환불·분쟁 정책 안내</v>
+        <v/>
       </c>
       <c r="D346" t="str">
-        <v>CS-04</v>
+        <v/>
       </c>
       <c r="E346" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F346" t="str">
-        <v>조건부 결제</v>
+        <v>점검</v>
       </c>
       <c r="G346" t="str">
-        <v>'환불·분쟁 정책 안내'에서 조건부 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트' 화면에서 점검이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H346" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I346" t="str">
         <v/>
@@ -11890,7 +11890,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B347" t="str">
         <v/>
@@ -11905,13 +11905,13 @@
         <v/>
       </c>
       <c r="F347" t="str">
-        <v>자동 환불 원칙 정리</v>
+        <v>정책 변경 안내</v>
       </c>
       <c r="G347" t="str">
-        <v>'환불·분쟁 정책 안내'에서 자동 환불 원칙 정리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트' 화면에서 정책 변경 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H347" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I347" t="str">
         <v/>
@@ -11922,7 +11922,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B348" t="str">
         <v/>
@@ -11937,13 +11937,13 @@
         <v/>
       </c>
       <c r="F348" t="str">
-        <v>상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표</v>
+        <v>카테고리 필터</v>
       </c>
       <c r="G348" t="str">
-        <v>'환불·분쟁 정책 안내'에서 상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H348" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I348" t="str">
         <v/>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B349" t="str">
         <v/>
@@ -11969,13 +11969,13 @@
         <v/>
       </c>
       <c r="F349" t="str">
-        <v>환불 소요 시간과 수단</v>
+        <v>상세 보기</v>
       </c>
       <c r="G349" t="str">
-        <v>'환불·분쟁 정책 안내'에서 환불 소요 시간과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지·이벤트' 화면에서 상세 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H349" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I349" t="str">
         <v/>
@@ -11986,7 +11986,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B350" t="str">
         <v/>
@@ -12001,10 +12001,10 @@
         <v/>
       </c>
       <c r="F350" t="str">
-        <v>진행자-참여자 분쟁 처리 절차</v>
+        <v>이벤트 참여 유도</v>
       </c>
       <c r="G350" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 진행자-참여자 분쟁 처리 절차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 이벤트 참여 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H350" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B351" t="str">
         <v/>
@@ -12033,10 +12033,10 @@
         <v/>
       </c>
       <c r="F351" t="str">
-        <v>소비자 보호</v>
+        <v>신규 진행자 지원 이벤트</v>
       </c>
       <c r="G351" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 소비자 보호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지·이벤트' 화면에서 신규 진행자 지원 이벤트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H351" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12053,25 +12053,25 @@
         <v>SCN-037</v>
       </c>
       <c r="B352" t="str">
-        <v/>
+        <v>고객지원</v>
       </c>
       <c r="C352" t="str">
-        <v/>
+        <v>환불·분쟁 정책 안내</v>
       </c>
       <c r="D352" t="str">
-        <v/>
+        <v>CS-04</v>
       </c>
       <c r="E352" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F352" t="str">
-        <v>에스크로 안내</v>
+        <v>조건부 결제</v>
       </c>
       <c r="G352" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 에스크로 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환불·분쟁 정책 안내'에서 조건부 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H352" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I352" t="str">
         <v/>
@@ -12097,13 +12097,13 @@
         <v/>
       </c>
       <c r="F353" t="str">
-        <v>신고 접수</v>
+        <v>자동 환불 원칙 정리</v>
       </c>
       <c r="G353" t="str">
-        <v>'환불·분쟁 정책 안내' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환불·분쟁 정책 안내'에서 자동 환불 원칙 정리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H353" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I353" t="str">
         <v/>
@@ -12129,24 +12129,216 @@
         <v/>
       </c>
       <c r="F354" t="str">
+        <v>상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표</v>
+      </c>
+      <c r="G354" t="str">
+        <v>'환불·분쟁 정책 안내'에서 상황별 환불(미달 불발·마감 전 취소·성사 후 반품·상품 하자) 기준표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H354" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I354" t="str">
+        <v/>
+      </c>
+      <c r="J354" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B355" t="str">
+        <v/>
+      </c>
+      <c r="C355" t="str">
+        <v/>
+      </c>
+      <c r="D355" t="str">
+        <v/>
+      </c>
+      <c r="E355" t="str">
+        <v/>
+      </c>
+      <c r="F355" t="str">
+        <v>환불 소요 시간과 수단</v>
+      </c>
+      <c r="G355" t="str">
+        <v>'환불·분쟁 정책 안내'에서 환불 소요 시간과 수단을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H355" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I355" t="str">
+        <v/>
+      </c>
+      <c r="J355" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B356" t="str">
+        <v/>
+      </c>
+      <c r="C356" t="str">
+        <v/>
+      </c>
+      <c r="D356" t="str">
+        <v/>
+      </c>
+      <c r="E356" t="str">
+        <v/>
+      </c>
+      <c r="F356" t="str">
+        <v>진행자-참여자 분쟁 처리 절차</v>
+      </c>
+      <c r="G356" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 진행자-참여자 분쟁 처리 절차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H356" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I356" t="str">
+        <v/>
+      </c>
+      <c r="J356" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B357" t="str">
+        <v/>
+      </c>
+      <c r="C357" t="str">
+        <v/>
+      </c>
+      <c r="D357" t="str">
+        <v/>
+      </c>
+      <c r="E357" t="str">
+        <v/>
+      </c>
+      <c r="F357" t="str">
+        <v>소비자 보호</v>
+      </c>
+      <c r="G357" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 소비자 보호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H357" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I357" t="str">
+        <v/>
+      </c>
+      <c r="J357" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B358" t="str">
+        <v/>
+      </c>
+      <c r="C358" t="str">
+        <v/>
+      </c>
+      <c r="D358" t="str">
+        <v/>
+      </c>
+      <c r="E358" t="str">
+        <v/>
+      </c>
+      <c r="F358" t="str">
+        <v>에스크로 안내</v>
+      </c>
+      <c r="G358" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 에스크로 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H358" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I358" t="str">
+        <v/>
+      </c>
+      <c r="J358" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B359" t="str">
+        <v/>
+      </c>
+      <c r="C359" t="str">
+        <v/>
+      </c>
+      <c r="D359" t="str">
+        <v/>
+      </c>
+      <c r="E359" t="str">
+        <v/>
+      </c>
+      <c r="F359" t="str">
+        <v>신고 접수</v>
+      </c>
+      <c r="G359" t="str">
+        <v>'환불·분쟁 정책 안내' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H359" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I359" t="str">
+        <v/>
+      </c>
+      <c r="J359" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B360" t="str">
+        <v/>
+      </c>
+      <c r="C360" t="str">
+        <v/>
+      </c>
+      <c r="D360" t="str">
+        <v/>
+      </c>
+      <c r="E360" t="str">
+        <v/>
+      </c>
+      <c r="F360" t="str">
         <v>관련 문의 링크</v>
       </c>
-      <c r="G354" t="str">
+      <c r="G360" t="str">
         <v>'환불·분쟁 정책 안내'에서 관련 문의 링크를 눌러 본다.</v>
       </c>
-      <c r="H354" t="str">
+      <c r="H360" t="str">
         <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
-      <c r="I354" t="str">
-        <v/>
-      </c>
-      <c r="J354" t="str">
+      <c r="I360" t="str">
+        <v/>
+      </c>
+      <c r="J360" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J354"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J360"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
@@ -1412,10 +1412,10 @@
         <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>브라우저 폭을 390px 로 좁혀 화면을 훑고, 360px 로 한 번 더 훑는다. ⚠ 세로 flex 로 바꾼 상자의 자식이 밀리는 것은 390px 에서는 안 보이고 360px 에서만 나온다.</v>
       </c>
       <c r="H19" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>두 폭 모두에서 가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>

--- a/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/공동구매_디럭스/08_검수시나리오.xlsx
@@ -1572,7 +1572,7 @@
         <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
+        <v>스펙팩 7-9 의 글을 화면에 붙여 넣으면 ⑧번이 잰다(7-9-2 는 파일만 보므로 대비를 재지 않는다). ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
         <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
